--- a/assets/data/azkar.xlsx
+++ b/assets/data/azkar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Zikr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A11770D-98EA-4B53-B315-F9753B7CDB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD359A9-59A7-4E68-9B9B-6EBD72EA087E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="876" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="876" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="أذكار الاستيقاظ(Update) (Final)" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="399">
   <si>
     <t>id</t>
   </si>
@@ -279,147 +279,6 @@
   </si>
   <si>
     <t>آمَنَ الرَّسُولُ بِمَا أُنزِلَ إِلَيْهِ مِن رَّبِّهِ وَالْمُؤْمِنُونَ ۚ كُلٌّ آمَنَ بِاللَّهِ وَمَلَائِكَتِهِ وَكُتُبِهِ وَرُسُلِهِ لَا نُفَرِّقُ بَيْنَ أَحَدٍ مِّن رُّسُلِهِ ۚ وَقَالُوا سَمِعْنَا وَأَطَعْنَا ۖ غُفْرَانَكَ رَبَّنَا وَإِلَيْكَ الْمَصِيرُ ﴿٢٨٥﴾ لَا يُكَلِّفُ اللَّهُ نَفْسًا إِلَّا وُسْعَهَا ۚ لَهَا مَا كَسَبَتْ وَعَلَيْهَا مَا اكْتَسَبَتْ ۗ رَبَّنَا لَا تُؤَاخِذْنَا إِن نَّسِينَا أَوْ أَخْطَأْنَا ۚ رَبَّنَا وَلَا تَحْمِلْ عَلَيْنَا إِصْرًا كَمَا حَمَلْتَهُ عَلَى الَّذِينَ مِن قَبْلِنَا ۚ رَبَّنَا وَلَا تُحَمِّلْنَا مَا لَا طَاقَةَ لَنَا بِهِ ۖ وَاعْفُ عَنَّا وَاغْفِرْ لَنَا وَارْحَمْنَا ۚ أَنتَ مَوْلَانَا فَانصُرْنَا عَلَى الْقَوْمِ الْكَافِرِينَ ﴿٢٨٦﴾</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> الخطوة الثانية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: دخول المسجد الحرام
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>الخطوات العملية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: تقديم الرجل اليمنى عند الدخول.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>دعاء دخول المسجد</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: «بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ»
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>عند رؤية الكعبة لأول مرة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: «اللَّهُمَّ زِدْ هَٰذَا الْبَيْتَ تَشْرِيفًا وَتَعْظِيمًا وَتَكْرِيمًا وَمَهَابَةً»</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> الخطوة الثالثة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: الطواف حول الكعبة (7 أشواط)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>الخطوات العملية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: 
-🕋 جعل الكعبة عن يسارك.
-🕋 استقبال الحجر الأسود لبدء الشوط.
-🕋 عند محاذاة الحجر الأسود (بداية كل شوط): تُشير بيدك قائلاً: «بِسْمِ اللَّهِ وَاللَّهُ أَكْبَرُ»
-🕋 بين الركن اليماني والحجر الأسود (في كل شوط): «رَبَّنَا آتِنَا فِي الدُّنْيَا حَسَنَةً وَفِي الْآخِرَةِ حَسَنَةً وَقِنَا عَذَابَ النَّارِ»
-🕋 أثناء بقية الطواف:
-• ليس هناك دعاء محدد لكل شوط.
-• ادعُ بما تشاء من الاستغفار، والذكر، وقراءة القرآن.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -805,6 +664,1518 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Entering Al-Masjid Al-Haram
+🔹 What to Do? (Action Steps):
+• Enter the mosque stepping with your right foot first.
+🕋  Supplication (Dua) for Entering the Mosque:
+«بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ»
+"Bismillah, was-salatu was-salamu 'ala Rasulillah. Allahumma-ftah li abwaba rahmatik."
+(In the name of Allah, and peace and blessings be upon the Messenger of Allah. O Allah, open the gates of Your mercy for me)
+👁️ Upon Seeing the Kaaba for the First Time:
+«اللَّهُمَّ زِدْ هَٰذَا الْبَيْتَ تَشْرِيفًا وَتَعْظِيمًا وَتَكْرِيمًا وَمَهَابَةً»
+"Allahumma zid hadhal-bayta tashrifan wa ta'dhiman wa takriman wa mahabah."
+(O Allah, increase this House in honor, greatness, respect, and awe)</t>
+    </r>
+  </si>
+  <si>
+    <t>يَبْدَأُ بِرِجْلِهِ الْيُسْرَى، وَيَقُولُ: بِسْمِ اللَّهِ وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ مِنْ فَضْلِكَ، اللَّهُمَّ اعْصِمْنِي مِنَ الشَّيْطَانِ الرَّجِيمِ</t>
+  </si>
+  <si>
+    <t>اللّهُـمَّ ما أَصْبَـَحَ بي مِـنْ نِعْـمَةٍ أَوْ بِأَحَـدٍ مِـنْ خَلْـقِك، فَمِـنْكَ وَحْـدَكَ لا شَرِيكَ لَـك، فَلَـكَ الْحَمْـدُ وَلَـكَ الشُّكْـر</t>
+  </si>
+  <si>
+    <t>لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ</t>
+  </si>
+  <si>
+    <t>الحَمْدُ للهِ الَّذِي عَافَانِي فِي جَسَدِي، وَرَدَّ عَلَيَّ رُوحِي، وَأَذِنَ لِي بِذِكْرِهِ</t>
+  </si>
+  <si>
+    <t>الحَمْدُ للهِ الَّذِي أَحْيَانَا بَعْدَ مَا أَمَاتَنَا وَإِلَيْهِ النُّشُورُ</t>
+  </si>
+  <si>
+    <t>لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، سُبْحَانَ اللهِ، وَالحَمْدُ للهِ، وَلا إِلهَ إِلاَّ اللهُ وَاللهُ أَكْبَرُ، وَلا حَوْلَ وَلا قُوَّةَ إِلاَّ بِاللهِ العَلِيِّ العَظِيمِ رَبِّ اغْفِرْ لِي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللّهُـمَّ ما أَصْبَـَحَ بي مِـنْ نِعْـمَةٍ أَوْ بِأَحَـدٍ مِـنْ خَلْـقِك، فَمِـنْكَ وَحْـدَكَ لا شَرِيكَ لَـك، فَلَـكَ الْحَمْـدُ وَلَـكَ الشُّكْـر  
+Allāhumma mā aṣbaha bī min ni`matin aw bi aḥadin min khalqik, fa minka waḥdaka lā sharīka lak, falaka ‘l-ḥamdu wa lakash-shukr  
+O Allah, whatever blessing has been received by me or anyone of Your creation is from You alone, You have no partner All praise is for you and thanks is to You   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ 
+ Lā 'ilāha 'illallāhu waḥdahu la sharīka lahu lahul-mulku wa lahul-ḥamdu, wa huwa 'alā kulli shay'in qadīr  
+There is none worthy of worship but Allah alone, Who has no partner His is the dominion and to Him belongs all praise and He is able to do all things</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحَمْدُ للهِ الَّذِي عَافَانِي فِي جَسَدِي، وَرَدَّ عَلَيَّ رُوحِي، وَأَذِنَ لِي بِذِكْرِهِ
+  Al-ḥamdu lillāhil-ladhī `āfānī fī jasadī, wa radda `alayya rūḥī, wa 'adhina lī bidhikrihi  
+Praise is to Allah Who gave strength to my body and returned my soul to me and permitted me to remember Him  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحَمْدُ للهِ الَّذِي أَحْيَانَا بَعْدَ مَا أَمَاتَنَا وَإِلَيْهِ النُّشُورُ
+  Alḥamdu lillāhil-ladhī 'aḥyānā ba`da mā 'amātanā wa 'ilayhin-nushūr  
+Praise is to Allah Who gives us life after He has caused us to die and to Him is the return  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، سُبْحَانَ اللهِ، وَالحَمْدُ للهِ، وَلا إِلهَ إِلاَّ اللهُ وَاللهُ أَكْبَرُ، وَلا حَوْلَ وَلا قُوَّةَ إِلاَّ بِاللهِ العَلِيِّ العَظِيمِ رَبِّ اغْفِرْ لِي
+    Lā 'ilāha 'illallāhu waḥdahu la sharīka lahu, lahul-mulku wa lahul-ḥamdu, wa huwa 'alā kulli shay'in qadīr Subḥānallāhi, walḥamdu lillāhi, wa lā 'ilāha 'illallāhu, wallāhu 'akbar, wa lā ḥaula wa lā quwwata 'illā billāhil-`aliyyil-`aẓīm, rabbighfir lī    
+There is none worthy of worship but Allah alone, Who has no partner, His is the dominion and to Him belongs all praise, and He is able to do all things Glory is to Allah Praise is to Allah There is none worthy of worship but Allah Allah is the Most Great There is no might and no power except by Allah's leave the Exalted, the Mighty My Lord forgive me  </t>
+  </si>
+  <si>
+    <t>أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذَا الْيَوْمِ وَخَيْرَ مَا بَعْدَهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذَا الْيَوْمِ وَشَرِّ مَا بَعْدَهُ، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ بِكَ أَصْبَحْنَا، وَبِكَ أَمْسَيْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَنْتَ رَبِّي لَا إِلَٰهَ إِلَّا أَنْتَ، خَلَقْتَنِي وَأَنَا عَبْدُكَ، وَأَنَا عَلَى عَهْدِكَ وَوَعْدِكَ مَا اسْتَطَعْتُ، أَعُوذُ بِكَ مِنْ شَرِّ مَا صَنَعْتُ، أَبُوءُ لَكَ بِنِعْمَتِكَ عَلَيَّ وَأَبُوءُ بِذَنْبِي، فَاغْفِرْ لِي فَإِنَّهُ لَا يَغْفِرُ الذُّنُوبَ إِلَّا أَنْتَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَصْبَحْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ مَا أَصْبَحَ بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ</t>
+  </si>
+  <si>
+    <t>حَسْبِيَ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ عَلَيْهِ تَوَكَّلْتُ وَهُوَ رَبُّ الْعَرْشِ الْعَظِيمِ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ عَالِمَ الْغَيْبِ وَالشَّهَادَةِ فَاطِرَ السَّمَاوَاتِ وَالْأَرْضِ رَبَّ كُلِّ شَيْءٍ وَمَلِيكَهُ، أَشْهَدُ أَنْ لَا إِلَٰهَ إِلَّا أَنْتَ، أَعُوذُ بِكَ مِنْ شَرِّ نَفْسِي وَمِنْ شَرِّ الشَّيْطَانِ وَشِرْكِهِ، وَأَنْ أَقْتَرِفَ عَلَى نَفْسِي سُوءًا أَوْ أَجُرَّهُ إِلَى مُسْلِمٍ</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الَّذِي لَا يَضُرُّ مَعَ اسْمِهِ شَيْءٌ فِي الْأَرْضِ وَلَا فِي السَّمَاءِ وَهُوَ السَّمِيعُ الْعَلِيمُ</t>
+  </si>
+  <si>
+    <t>رَضِيتُ بِاللَّهِ رَبًّا، وَبِالْإِسْلَامِ دِينًا، وَبِمُحَمَّدٍ ﷺ نَبِيًّا</t>
+  </si>
+  <si>
+    <t>أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذَا الْيَوْمِ فَتْحَهُ، وَنَصْرَهُ، وَنُورَهُ، وَبَرَكَتَهُ، وَهُدَاهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهِ وَشَرِّ مَا بَعْدَهُ</t>
+  </si>
+  <si>
+    <t>أَصْبَحْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ</t>
+  </si>
+  <si>
+    <t>سُبْحـانَ اللهِ وَبِحَمْـدِهِ</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ</t>
+  </si>
+  <si>
+    <t>سُبْحَانَ اللَّهِ وَبِحَمْدِهِ عَدَدَ خَلْقِهِ، وَرِضَا نَفْسِهِ، وَزِنَةَ عَرْشِهِ، وَمِدَادَ كَلِمَاتِهِ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ عِلْمًا نَافِعًا، وَرِزْقًا طَيِّبًا، وَعَمَلًا مُتَقَبَّلًا</t>
+  </si>
+  <si>
+    <t>أَعُوذُ بِكَلِمَاتِ اللَّهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ صَلِّ وَسَلِّمْ وَبَارِكْ عَلَى نَبِيِّنَا مُحَمَّدٍ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنَّا نَعُوذُ بِكَ مِنْ أَنْ نُشْرِكَ بِكَ شَيْئًا نَعْلَمُهُ، وَنَسْتَغْفِرُكَ لِمَا لَا نَعْلَمُهُ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْهَمِّ وَالْحَزَنِ، وَأَعُوذُ بِكَ مِنَ الْعَجْزِ وَالْكَسَلِ، وَأَعُوذُ بِكَ مِنَ الْجُبْنِ وَالْبُخْلِ، وَأَعُوذُ بِكَ مِنْ غَلَبَةِ الدَّيْنِ وَقَهْرِ الرِّجَالِ</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ هُوَ اللَّهُ أَحَدٌ ﴿١﴾ اللَّهُ الصَّمَدُ ﴿٢﴾ لَمْ يَلِدْ وَلَمْ يُولَدْ ﴿٣﴾ وَلَمْ يَكُن لَّهُ كُفُوًا أَحَدٌ ﴿٤﴾</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ أَعُوذُ بِرَبِّ الْفَلَقِ ﴿١﴾ مِن شَرِّ مَا خَلَقَ ﴿٢﴾ وَمِن شَرِّ غَاسِقٍ إِذَا وَقَبَ ﴿٣﴾ وَمِن شَرِّ النَّفَّاثَاتِ فِي الْعُقَدِ ﴿٤﴾ وَمِن شَرِّ حَاسِدٍ إِذَا حَسَدَ ﴿٥﴾</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ أَعُوذُ بِرَبِّ النَّاسِ ﴿١﴾ مَلِكِ النَّاسِ ﴿٢﴾ إِلَٰهِ النَّاسِ ﴿٣﴾ مِن شَرِّ الْوَسْوَاسِ الْخَنَّاسِ ﴿٤﴾ الَّذِي يُوَسْوِسُ فِي صُدُورِ النَّاسِ ﴿٥﴾ مِنَ الْجِنَّةِ وَالنَّاسِ ﴿٦﴾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
+ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ.
+</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي، اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي، وأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَ مِنْ تَحْتِي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
+اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ </t>
+  </si>
+  <si>
+    <t>أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذِهِ اللَّيْلَةِ وَخَيْرَ مَا بَعْدَهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذِهِ اللَّيْلَةِ وَشَرِّ مَا بَعْدَهَا، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ بِكَ أَمْسَيْنَا، وَبِكَ أَصْبَحْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَمْسَيْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ مَا أَمْسَى بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ عَافِنِي فِي بَدَنِي، اللَّهُمَّ عَافِنِي فِي سَمْعِي، اللَّهُمَّ عَافِنِي فِي بَصَرِي، لَا إِلَٰهَ إِلَّا أَنْتَ اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْكُفْرِ وَالْفَقْرِ، وَأَعُوذُ بِكَ مِنْ عَذَابِ الْقَبْرِ، لَا إِلَٰهَ إِلَّا أَنْتَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي ووأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَمِنْ تَحْتِي</t>
+  </si>
+  <si>
+    <t>بِسـمِ اللهِ الذي لا يَضُـرُّ مَعَ اسمِـهِ شَيءٌ في الأرْضِ وَلا في السّمـاءِ وَهـوَ السّمـيعُ العَلـيم</t>
+  </si>
+  <si>
+    <t>أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذِهِ اللَّيْلَةِ فَتْحَهَا، وَنَصْرَهَا، وَنُورَهَا، وَبَرَكَتَهَا، وَهُدَاهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهَا وَشَرِّ مَا بَعْدَهَا</t>
+  </si>
+  <si>
+    <t>أَمْسَيْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ</t>
+  </si>
+  <si>
+    <t>أَسْتَغْفِرُ اللَّهَ وَأَتُوبُ إِلَيْهِ</t>
+  </si>
+  <si>
+    <t>سُبْحـانَ اللهِ وَبِحَمْـدِهِ
+Subḥānal-lāhi wa-bi-ḥamdih
+Glory is to Allah and praise is to Him</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ
+Lā ilāha illallāhu waḥdahu lā sharīka lah, lahul-mulku wa-lahul-ḥamd, wa-huwa ‘alā kulli shay’in qadīr
+None has the right to be worshipped except Allah, alone, without partner, to Him belongs all sovereignty and praise, and He is over all things Omnipotent</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ عِلْمًا نَافِعًا، وَرِزْقًا طَيِّبًا، وَعَمَلًا مُتَقَبَّلًا
+Allāhumma innī as'aluka ‘ilman nāfi‘ā, wa-rizqan ṭayyibā, wa-‘amalan mutaqabbalā
+O Allah, I ask You for knowledge that is of benefit, a good provision, and a deed that will be accepted</t>
+  </si>
+  <si>
+    <t>أَسْتَغْفِرُ اللَّهَ وَأَتُوبُ إِلَيْهِ
+Astaghfiru-Llāha wa-atūbu ilayh
+I seek Allah's forgiveness and I turn in repentance to Him</t>
+  </si>
+  <si>
+    <t>أَعُوذُ بِكَلِمَاتِ اللَّهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ
+A‘ūdhu bi-kalimātil-lāhit-tāmmāti min sharri mā khalaq
+I seek refuge in the Perfect Words of Allah from the evil of what He has created</t>
+  </si>
+  <si>
+    <t>أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
+اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ 
+A‘ūdhu billāhi minash-shayṭānir-rajīm
+Allāhu lā ilāha illā huwal-ḥayyul-qayyūm lā ta'khudhuhu sinatun wa lā nawm lahu mā fis-samāwāti wa mā fil-arḍ man dhal-ladhī yashfa‘u ‘indahu illā bi-idhnihi ya‘lamu mā bayna aydīhim wa mā khalfahum wa lā yuḥīṭūna bi-shay'im-min ‘ilmihi illā bimā shā' wasi‘a kursiyyuhus-samāwāti wal-arḍ wa lā ya'ūduhu ḥifẓuhumā wa huwal-‘aliyyul-‘aẓīm
+I seek refuge in Allah from Satan the outcast
+Allah! There is no deity except Him the Ever-Living the Sustainer of all existence Neither drowsiness overtakes Him nor sleep To Him belongs whatever is in the heavens and whatever is on the earth Who is it that can intercede with Him except by His permission? He knows what is before them and what will be after them and they encompass not a thing of His knowledge except for what He wills His Kursi extends over the heavens and the earth and their preservation tires Him not And He is the Most High the Most Great</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ هُوَ اللَّهُ أَحَدٌ ﴿١﴾ اللَّهُ الصَّمَدُ ﴿٢﴾ لَمْ يَلِدْ وَلَمْ يُولَدْ ﴿٣﴾ وَلَمْ يَكُن لَّهُ كُفُوًا أَحَدٌ ﴿٤﴾
+Bismillāhir-raḥmānir-raḥīm
+Qul huwal-Lāhu aḥad Allāhuṣ-ṣamad Lam yalid wa lam yūlad Wa lam yakul-lahu kufuwan aḥad
+In the name of Allah the Beneficent the Merciful
+Say "He is Allah [who is] One Allah the Eternal Refuge He neither begets nor is born Nor is there to Him any equivalent"</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ أَعُوذُ بِرَبِّ الْفَلَقِ ﴿١﴾ مِن شَرِّ مَا خَلَقَ ﴿٢﴾ وَمِن شَرِّ غَاسِقٍ إِذَا وَقَبَ ﴿٣﴾ وَمِن شَرِّ النَّفَّاثَاتِ فِي الْعُقَدِ ﴿٤﴾ وَمِن شَرِّ حَاسِدٍ إِذَا حَسَدَ ﴿٥﴾
+Bismillāhir-raḥmānir-raḥīm
+Qul a‘ūdhu bi-rabbil-falaq Min sharri mā khalaq Wa min sharri ghāsiqin idhā waqab Wa min sharrin-naffāthāti fil-‘uqad Wa min sharri ḥāsidin idhā ḥasad
+In the name of Allah the Beneficent the Merciful
+Say "I seek refuge in the Lord of daybreak From the evil of that which He created And from the evil of darkness when it settles And from the evil of the blowers in knots And from the evil of an envier when he envies"</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ أَعُوذُ بِرَبِّ النَّاسِ ﴿١﴾ مَلِكِ النَّاسِ ﴿٢﴾ إِلَٰهِ النَّاسِ ﴿٣﴾ مِن شَرِّ الْوَسْوَاسِ الْخَنَّاسِ ﴿٤﴾ الَّذِي يُوَسْوِسُ فِي صُدُورِ النَّاسِ ﴿٥﴾ مِنَ الْجِنَّةِ وَالنَّاسِ ﴿٦﴾
+Bismillāhir-raḥmānir-raḥīm
+Qul a‘ūdhu bi-rabbin-nās Malikin-nās Ilāhin-nās Min sharril-waswāsil-khannās Alladhī yuwaswisu fī ṣudūrin-nās Minal-jinnati wan-nās
+In the name of Allah the Beneficent the Merciful
+Say "I seek refuge in the Lord of mankind The Sovereign of mankind The God of mankind From the evil of the retreating whisperer - Who whispers [evil] into the breasts of mankind - From among the jinn and mankind"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذِهِ اللَّيْلَةِ وَخَيْرَ مَا بَعْدَهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذِهِ اللَّيْلَةِ وَشَرِّ مَا بَعْدَهَا، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ
+Amsaynā wa-amsal-mulku lillāhi wal-ḥamdu lillāh lā ilāha illallāhu waḥdahu lā sharīka lah lahul-mulku wa-lahul-ḥamd wa-huwa ‘alā kulli shay’in qadīr Rabbi as’aluka khayra mā fī hādhihil-laylati wa-khayra mā ba‘dahā wa-a‘ūdhu bika min sharri mā fī hādhihil-laylati wa-sharri mā ba‘dahā Rabbi a‘ūdhu bika minal-kasali wa-sū’il-kibar Rabbi a‘ūdhu bika min ‘adhābin fin-nāri wa-‘adhābin fil-qabr
+We have reached the evening and at this very time unto Allah belongs all sovereignty and all praise is for Allah None has the right to be worshipped except Allah alone without partner to Him belongs all sovereignty and praise and He is over all things Omnipotent My Lord I ask You for the good of this night and the good of what follows it and I take refuge in You from the evil of this night and the evil of what follows it My Lord I take refuge in You from laziness and senility My Lord I take refuge in You from torment in the Fire and punishment in the grave
+</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ بِكَ أَمْسَيْنَا، وَبِكَ أَصْبَحْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ
+Allāhumma bika amsaynā wa-bika aṣbaḥnā wa-bika naḥyā wa-bika namūtu wa-ilaykal-maṣīr
+O Allah by Your leave we have reached the evening and by Your leave we have reached the morning by Your leave we live and by Your leave we die and unto You is our return</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَنْتَ رَبِّي لَا إِلَٰهَ إِلَّا أَنْتَ، خَلَقْتَنِي وَأَنَا عَبْدُكَ، وَأَنَا عَلَى عَهْدِكَ وَوَعْدِكَ مَا اسْتَطَعْتُ، أَعُوذُ بِكَ مِنْ شَرِّ مَا صَنَعْتُ، أَبُوءُ لَكَ بِنِعْمَتِكَ عَلَيَّ وَأَبُوءُ بِذَنْبِي، فَاغْفِرْ لِي فَإِنَّهُ لَا يَغْفِرُ الذُّنُوبَ إِلَّا أَنْتَ
+Allāhumma anta rabbī lā ilāha illā ant khalaqtanī wa-anā ‘abduk wa-anā ‘alā ‘ahdika wa-wa‘dika mas-taṭa‘t a‘ūdhu bika min sharri mā ṣana‘t abū’u laka bi-ni‘matika ‘alayya wa-abū’u bi-dhanbī fagh-fir lī fa-innahu lā yaghfirudh-dhunūba illā ant
+O Allah You are my Lord there is no deity except You You created me and I am Your servant and I am faithful to my covenant and my promise to You as much as I am able I seek refuge in You from the evil of what I have done I acknowledge before You Your favor upon me and I acknowledge my sin so forgive me for indeed no one forgets/forgives sins except You</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَمْسَيْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ
+Allāhumma innī amsaytu ush-hiduka wa-ush-hidu ḥamalata ‘arshika wa-malā'ikataka wa-jamī‘a khalqika annaka anta-Llāhu lā ilāha illā anta waḥdaka lā sharīka laka wa-anna Muḥhammadan ‘abduka wa-rasūluk
+O Allah I have entered the evening and I call upon You the bearers of Your Throne Your angels and all of Your creation to witness that You are Allah there is no deity except You alone without partner and that Muhammad is Your servant and Your Messenger</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ مَا أَمْسَى بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ
+Allāhumma mā amsā bī min ni‘matin aw bi-aḥadin min khalqika faminka waḥdaka lā sharīka laka falakal-ḥamdu wa-lakash-shukr
+O Allah whatever blessing has befallen me or any of Your creation this evening is from You alone without partner so for You is all praise and unto You is all thanks</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ عَافِنِي فِي بَدَنِي، اللَّهُمَّ عَافِنِي فِي سَمْعِي، اللَّهُمَّ عَافِنِي فِي بَصَرِي، لَا إِلَٰهَ إِلَّا أَنْتَ اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْكُفْرِ وَالْفَقْرِ، وَأَعُوذُ بِكَ مِنْ عَذَابِ الْقَبْرِ، لَا إِلَٰهَ إِلَّا أَنْتَ
+Allāhumma ‘āfinī fī badanī Allāhumma ‘āfinī fī sam‘ī Allāhumma ‘āfinī fī baṣarī lā ilāha illā ant Allāhumma innī a‘ūdhu bika minal-kufri wal-faqr wa-a‘ūdhu bika min ‘adhābil-qabr lā ilāha illā ant
+O Allah grant me health in my body O Allah grant me health in my hearing O Allah grant me health in my sight There is no deity except You O Allah I seek refuge in You from disbelief and poverty and I seek refuge in You from the punishment of the grave There is no deity except You</t>
+  </si>
+  <si>
+    <t>حَسْبِيَ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ عَلَيْهِ تَوَكَّلْتُ وَهُوَ رَبُّ الْعَرْشِ الْعَظِيمِ
+Ḥasbiyal-Lāhu lā ilāha illā huwa ‘alayhi tawakkaltu wa-huwa rabbul-‘arshil-‘aẓīm
+Allah is sufficient for me There is no deity except Him As for Him I have put my trust and He is the Lord of the Mighty Throne</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي ووأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَمِنْ تَحْتِي
+Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fi 'd-dunyā wa 'l-ākhirah Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fī dīnī wa dunyāya wa ahlī wa mālī Allāhumma-stur ‘awrātī wa āmin raw‘ātī Allāhumma-ḥfaẓnī min bayni yadayya wa min khalfī wa ‘an yamīnī wa ‘an shimālī wa min fawqī wa a‘ūdhu bi-‘aẓamatika an ughtāla min taḥtī
+O Allah I ask You for pardon and well-being in this world and the next O Allah I ask You for pardon and well-being in my religious and worldly affairs and in my family and my wealth O Allah conceal my faults and keep me safe from the things which I fear O Allah guard me from the front and from behind and from my right and from my left and from above me I seek refuge in Your greatness from being struck from beneath me</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ عَالِمَ الْغَيْبِ وَالشَّهَادَةِ فَاطِرَ السَّمَاوَاتِ وَالْأَرْضِ رَبَّ كُلِّ شَيْءٍ وَمَلِيكَهُ، أَشْهَدُ أَنْ لَا إِلَٰهَ إِلَّا أَنْتَ، أَعُوذُ بِكَ مِنْ شَرِّ نَفْسِي وَمِنْ شَرِّ الشَّيْطَانِ وَشِرْكِهِ، وَأَنْ أَقْتَرِفَ عَلَى نَفْسِي سُوءًا أَوْ أَجُرَّهُ إِلَى مُسْلِمٍ
+Allāhumma ‘ālimal-ghaybi wash-shahādah fāṭiras-samāwāti wal-arḍ rabba kulli shay’in wa-malīkah ash-hadu an lā ilāha illā ant a‘ūdhu bika min sharri nafsī wa-min sharrish-shayṭāni wa-shirkih wa-an aqtarifa ‘alā nafsī sū’an aw ajurrahu ilā muslim
+O Allah Knower of the unseen and the evident Creator of the heavens and the earth Lord of everything and its Possessor I bear witness that there is no deity except You I seek refuge in You from the evil of my soul and from the evil of Satan and his helper/ascribing partners to Allah and from committing any evil against myself or dragging it upon another Muslim</t>
+  </si>
+  <si>
+    <t>بِسـمِ اللهِ الذي لا يَضُـرُّ مَعَ اسمِـهِ شَيءٌ في الأرْضِ وَلا في السّمـاءِ وَهـوَ السّمـيعُ العَلـيم
+Bismillāhil-ladhī lā yaḍurru ma‘as-mihi shay’un fil-arḍi wa-lā fis-samā’i wa-huwas-samī‘ul-‘alīm
+In the name of Allah with Whose name nothing can cause harm on earth or in the heaven and He is the All-Hearing the All-Knowing</t>
+  </si>
+  <si>
+    <t>رَضِيتُ بِاللَّهِ رَبًّا، وَبِالْإِسْلَامِ دِينًا، وَبِمُحَمَّدٍ ﷺ نَبِيًّا
+Raḍītu billāhi rabban wa-bil-islāmi dīnan wa-bi-Muḥammadin ṣallallāhu ‘alayhi wa-sallama nabiyyā
+I am pleased with Allah as my Lord with Islam as my religion and with Muhammad (peace and blessings of Allah be upon him) as my Prophet</t>
+  </si>
+  <si>
+    <t>يَا حَيُّ يَا قَيُّومُ بِرَحْمَتِكَ أَسْتَغِيثُ، أَصْلِحْ لِي شَأْنِي كُلَّهُ، وَلَا تَكِلْنِي إِلَى نَفْسِي طَرْفَةَ عَيْنٍ
+Yā ḥayyu yā qayyūmu bi-raḥmatika astaghīth aṣliḥ lī sha’nī kullahu wa-lā takilnī ilā nafsī ṭarfata ‘ayn
+O Ever Living One O Sustainer of all by Your mercy I seek assistance rectify for me all of my affairs and do not leave me to myself even for the blink of an eye</t>
+  </si>
+  <si>
+    <t>أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذِهِ اللَّيْلَةِ فَتْحَهَا، وَنَصْرَهَا، وَنُورَهَا، وَبَرَكَتَهَا، وَهُدَاهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهَا وَشَرِّ مَا بَعْدَهَا
+Amsaynā wa-amsal-mulku lillāhi rabbil-‘ālamīn Allāhumma innī as’aluka khayra hādhihil-laylah: fatḥahā wa-naṣrahā wa-nūrahā wa-barakatahā wa-hudāhā wa-a‘ūdhu bika min sharri mā fīhā wa-sharri mā ba‘dahā
+We have reached the evening and at this very time all sovereignty belongs to Allah Lord of the worlds O Allah I ask You for the good of this night its triumphs its victories its light its blessings and its guidance and I take refuge in You from the evil of this night and the evil that follows it</t>
+  </si>
+  <si>
+    <t>أَمْسَيْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ
+Amsaynā ‘alā fiṭratil-islām wa-‘alā kalimatil-ikhlāṣ wa-‘alā dīni nabiyyinā Muḥammadin ṣallallāhu ‘alayhi wa-sallam wa-‘alā millati abīnā Ibrāhīma ḥanīfan musliman wa-mā kāna minal-mushrikīn
+We have reached the evening upon the natural religion of Islam and the word of sincere devotion and the religion of our Prophet Muhammad (peace and blessings of Allah be upon him) and the creed of our father Ibrahim a man of pure faith and a Muslim and he was not of those who associate partners with Allah</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ
+Lā ilāha illallāhu waḥdahu lā sharīka lah lahul-mulku wa-lahul-ḥamd wa-huwa ‘alā kulli shay’in qadīr
+None has the right to be worshipped except Allah alone without partner to Him belongs all sovereignty and praise and He is over all things Omnipotent</t>
+  </si>
+  <si>
+    <t>سُبْحَانَ اللَّهِ وَبِحَمْدِهِ عَدَدَ خَلْقِهِ، وَرِضَا نَفْسِهِ، وَزِنَةَ عَرْشِهِ، وَمِدَادَ كَلِمَاتِهِ
+Subḥānal-lāhi wa-bi-ḥamdih ‘adada khalqih wa-riḍā nafsih wa-zinata ‘arshih wa-midāda kalimātih
+Glory is to Allah and praise is to Him by the number of His creation and His pleasure and by the weight of His Throne and the ink of His words</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ عِلْمًا نَافِعًا، وَرِزْقًا طَيِّبًا، وَعَمَلًا مُتَقَبَّلًا
+Allāhumma innī as'aluka ‘ilman nāfi‘ā wa-rizqan ṭayyibā wa-‘amalan mutaqabbalā
+O Allah I ask You for knowledge that is of benefit a good provision and a deed that will be accepted</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ صَلِّ وَسَلِّمْ وَبَارِكْ عَلَى نَبِيِّنَا مُحَمَّدٍ
+Allāhumma ṣalli wa-sallim wa-bārik ‘alā nabiyyinā Muḥammad
+O Allah send Your praise peace and blessings upon our Prophet Muhammad</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنَّا نَعُوذُ بِكَ مِنْ أَنْ نُشْرِكَ بِكَ شَيْئًا نَعْلَمُهُ، وَنَسْتَغْفِرُكَ لِمَا لَا نَعْلَمُهُ
+Allāhumma innā na‘ūdhu bika min an nushrika bika shay’an na‘lamuh wa-nastaghfiruka limā lā na‘lamuh
+O Allah we seek refuge in You from ascribing anything to You knowingly and we seek Your forgiveness for that which we do not know</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْهَمِّ وَالْحَزَنِ، وَأَعُوذُ بِكَ مِنَ الْعَجْزِ وَالْكَسَلِ، وَأَعُوذُ بِكَ مِنَ الْجُبْنِ وَالْبُخْلِ، وَأَعُوذُ بِكَ مِنْ غَلَبَةِ الدَّيْنِ وَقَهْرِ الرِّجَالِ
+Allāhumma innī a‘ūdhu bika minal-hammi wal-ḥazan wa-a‘ūdhu bika minal-‘ajzi wal-kasal wa-a‘ūdhu bika minal-jubni wal-bukhl wa-a‘ūdhu bika min ghalabatid-dayni wa-qahrir-rijāl
+O Allah I seek refuge in You from anxiety and sorrow and I seek refuge in You from inability and laziness and I seek refuge in You from cowardice and miserliness and I seek refuge in You from the burden of debt and from being overpowered by men</t>
+  </si>
+  <si>
+    <t>أَسْتَغْفِرُ اللَّهَ الْعَظِيمَ الَّذِي لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ وَأَتُوبُ إِلَيْهِ
+Astaghfiru-Llāhal-‘aẓīmal-ladhī lā ilāha illā huwal-ḥayyul-qayyūmu wa-atūbu ilayh
+I seek the forgiveness of Allah the Mighty Whom there is no deity except Him the Ever-Living the Sustainer of all existence and I turn to Him in repentance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
+اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ
+A`ūdhu billāhi min ash-shaytāni 'r-rajīm
+ Allāhu lā ilāha illā huwal-ḥayyul-qayyūm lā ta'khudhuhu sinatun wa lā nawm lahu mā fis-samāwāti wa mā fil-arḍ man dhal-ladhī yashfa‘u ‘indahu illā bi-idhnihi ya‘lamu mā bayna aydīhim wa mā khalfahum wa lā yuḥīṭūna bi-shay'im-min ‘ilmihi illā bimā shā' wasi‘a kursiyyuhus-samāwāti wal-arḍ wa lā ya'ūduhu ḥifẓuhumā wa huwal-‘aliyyul-‘aẓīm
+O Allah! There is no deity except Him the Ever-Living the Sustainer of all existence Neither drowsiness overtakes Him nor sleep To Him belongs whatever is in the heavens and whatever is on the earth Who is it that can intercede with Him except by His permission? He knows what is before them and what will be after them and they encompass not a thing of His knowledge except for what He wills His Kursi extends over the heavens and the earth and their preservation tires Him not And He is the Most High the Most Great </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ هُوَ اللَّهُ أَحَدٌ ﴿١﴾ اللَّهُ الصَّمَدُ ﴿٢﴾ لَمْ يَلِدْ وَلَمْ يُولَدْ ﴿٣﴾ وَلَمْ يَكُن لَّهُ كُفُوًا أَحَدٌ ﴿٤﴾
+Bismillāhir-raḥmānir-raḥīm
+Qul huwal-Lāhu aḥad Allāhuṣ-ṣamad Lam yalid wa lam yūlad Wa lam yakul-lahu kufuwan aḥad 
+In the name of Allah the Beneficent the Merciful
+Say "He is Allah [who is] One Allah the Eternal Refuge He neither begets nor is born Nor is there to Him any equivalent
+</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
+قُلْ أَعُوذُ بِرَبِّ الْفَلَقِ ﴿١﴾ مِن شَرِّ مَا خَلَقَ ﴿٢﴾ وَمِن شَرِّ غَاسِقٍ إِذَا وَقَبَ ﴿٣﴾ وَمِن شَرِّ النَّفَّاثَاتِ فِي الْعُقَدِ ﴿٤﴾ وَمِن شَرِّ حَاسِدٍ إِذَا حَسَدَ ﴿٥﴾
+Bismillāhir-raḥmānir-raḥīm
+Qul a‘ūdhu bi-rabbil-falaq Min sharri mā khalaq Wa min sharri ghāsiqin idhā waqab Wa min sharrin-naffāthāti fil-‘uqad Wa min sharri ḥāsidin idhā ḥasad
+In the name of Allah the Beneficent the Merciful
+Say I seek refuge in the Lord of daybreak From the evil of that which He created And from the evil of darkness when it settles And from the evil of the blowers in knots And from the evil of an envier when he envies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذَا الْيَوْمِ وَخَيْرَ مَا بَعْدَهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذَا الْيَوْمِ وَشَرِّ مَا بَعْدَهُ، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ
+Aṣbaḥnā wa-aṣbaḥal-mulku lillāhi wal-ḥamdu lillāh lā ilāha illallāhu waḥdahu lā sharīka lah lahul-mulku wa-lahul-ḥamd wa-huwa ‘alā kulli shay’in qadīr Rabbi as’aluka khayra mā fī hādhal-yawmi wa-khayra mā ba‘dah wa-a‘ūdhu bika min sharri mā fī hādhal-yawmi wa-sharri mā ba‘dah Rabbi a‘ūdhu bika minal-kasali wa-sū’il-kibar Rabbi a‘ūdhu bika min ‘adhābin fin-nāri wa-‘adhābin fil-qabr
+We have reached the morning and at this very time unto Allah belongs all sovereignty and all praise is for Allah None has the right to be worshipped except Allah alone without partner to Him belongs all sovereignty and praise and He is over all things Omnipotent My Lord I ask You for the good of this day and the good of what follows it and I take refuge in You from the evil of this day and the evil of what follows it My Lord I take refuge in You from laziness and senility My Lord I take refuge in You from torment in the Fire and punishment in the grave </t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ بِكَ أَصْبَحْنَا، وَبِكَ أَمْسَيْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ
+Allāhumma bika aṣbaḥnā wa-bika amsaynā wa-bika naḥyā wa-bika namūtu wa-ilaykan-nushūr
+O Allah by Your leave we have reached the morning and by Your leave we have reached the evening by Your leave we live and by Your leave we die and unto You is our resurrection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللَّهُمَّ أَنْتَ رَبِّي لَا إِلَٰهَ إِلَّا أَنْتَ، خَلَقْتَنِي وَأَنَا عَبْدُكَ، وَأَنَا عَلَى عَهْدِكَ وَوَعْدِكَ مَا اسْتَطَعْتُ، أَعُوذُ بِكَ مِنْ شَرِّ مَا صَنَعْتُ، أَبُوءُ لَكَ بِنِعْمَتِكَ عَلَيَّ وَأَبُوءُ بِذَنْبِي، فَاغْفِرْ لِي فَإِنَّهُ لَا يَغْفِرُ الذُّنُوبَ إِلَّا أَنْتَ
+Allāhumma anta rabbī lā ilāha illā ant khalaqtanī wa-anā ‘abduk wa-anā ‘alā ‘ahdika wa-wa‘dika mas-taṭa‘t a‘ūdhu bika min sharri mā ṣana‘t abū’u laka bi-ni‘matika ‘alayya wa-abū’u bi-dhanbī fagh-fir lī fa-innahu lā yaghfirudh-dhunūba illā ant 
+O Allah You are my Lord there is no deity except You You created me and I am Your servant and I am faithful to my covenant and my promise to You as much as I am able I seek refuge in You from the evil of what I have done I acknowledge before You Your favor upon me and I acknowledge my sin so forgive me for indeed no one forgives sins except You
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللَّهُمَّ إِنِّي أَصْبَحْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ
+Allāhumma innī aṣbaḥtu ush-hiduka wa-ush-hidu ḥamalata ‘arshika wa-malā'ikataka wa-jamī‘a khalqika annaka anta-Llāhu lā ilāha illā anta waḥdaka lā sharīka laka wa-anna Muḥhammadan ‘abduka wa-rasūluk 
+O Allah I have entered a new morning and I call upon You the bearers of Your Throne Your angels and all of Your creation to witness that You are Allah there is no deity except You alone without partner and that Muhammad is Your servant and Your Messenger  </t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ مَا أَصْبَحَ بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ
+ Allāhumma mā aṣbaḥa bī min ni‘matin aw bi-aḥadin min khalqika faminka waḥdaka lā sharīka laka falakal-ḥamdu wa-lakash-shukr 
+O Allah whatever blessing has befallen me or any of Your creation this morning is from You alone without partner so for You is all praise and unto You is all thanks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللَّهُمَّ عَافِنِي فِي بَدَنِي، اللَّهُمَّ عَافِنِي فِي سَمْعِي، اللَّهُمَّ عَافِنِي فِي بَصَرِي، لَا إِلَٰهَ إِلَّا أَنْتَ
+اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْكُفْرِ وَالْفَقْرِ، وَأَعُوذُ بِكَ مِنْ عَذَابِ الْقَبْرِ، لَا إِلَٰهَ إِلَّا أَنْتَ
+Allāhumma ‘āfinī fī badanī Allāhumma ‘āfinī fī sam‘ī Allāhumma ‘āfinī fī baṣarī lā ilāha illā ant Allāhumma innī a‘ūdhu bika minal-kufri wal-faqr wa-a‘ūdhu bika min ‘adhābil-qabr lā ilāha illā ant 
+O Allah grant me health in my body O Allah grant me health in my hearing O Allah grant me health in my sight There is no deity except You O Allah I seek refuge in You from disbelief and poverty and I seek refuge in You from the punishment of the grave There is no deity except You  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">حَسْبِيَ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ عَلَيْهِ تَوَكَّلْتُ وَهُوَ رَبُّ الْعَرْشِ الْعَظِيمِ
+Ḥasbiyal-Lāhu lā ilāha illā huwa ‘alayhi tawakkaltu wa-huwa rabbul-‘arshil-‘aẓīm 
+Allah is sufficient for me There is no deity except Him As for Him I have put my trust and He is the Lord of the Mighty Throne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي، اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي، وأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَ مِنْ تَحْتِي
+ Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fi 'd-dunyā wa 'l-ākhirah Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fī dīnī wa dunyāya wa ahlī wa mālī Allāhumma-stur ‘awrātī wa āmin raw‘ātī Allāhumma-ḥfaẓnī min bayni yadayya wa min khalfī wa ‘an yamīnī wa ‘an shimālī wa min fawqī wa a‘ūdhu bi-‘aẓamatika an ughtāla min taḥtī
+O Allah I ask You for pardon and well-being in this world and the next O Allah I ask You for pardon and well-being in my religious and worldly affairs and in my family and my wealth O Allah conceal my faults and keep me safe from the things which I fear O Allah guard me from the front and from behind and from my right and from my left and from above me I seek refuge in Your greatness from being struck from beneath me </t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللَّهُمَّ عَالِمَ الْغَيْبِ وَالشَّهَادَةِ فَاطِرَ السَّمَاوَاتِ وَالْأَرْضِ رَبَّ كُلِّ شَيْءٍ وَمَلِيكَهُ، أَشْهَدُ أَنْ لَا إِلَٰهَ إِلَّا أَنْتَ، أَعُوذُ بِكَ مِنْ شَرِّ نَفْسِي وَمِنْ شَرِّ الشَّيْطَانِ وَشِرْكِهِ، وَأَنْ أَقْتَرِفَ عَلَى نَفْسِي سُوءًا أَوْ أَجُرَّهُ إِلَى مُسْلِمٍ
+Allāhumma ‘ālimal-ghaybi wash-shahādah fāṭiras-samāwāti wal-arḍ rabba kulli shay’in wa-malīkah ash-hadu an lā ilāha illā ant a‘ūdhu bika min sharri nafsī wa-min sharrish-shayṭāni wa-shirkih wa-an aqtarifa ‘alā nafsī sū’an aw ajurrahu ilā muslim
+O Allah Knower of the unseen and the evident Creator of the heavens and the earth Lord of everything and its Possessor I bear witness that there is no deity except You I seek refuge in You from the evil of my soul and from the evil of Satan and his helper/ascribing partners to Allah and from committing any evil against myself or dragging it upon another Muslim
+</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الَّذِي لَا يَضُرُّ مَعَ اسْمِهِ شَيْءٌ فِي الْأَرْضِ وَلَا فِي السَّمَاءِ وَهُوَ السَّمِيعُ الْعَلِيمُ
+Bismillāhil-ladhī lā yaḍurru ma‘as-mihi shay’un fil-arḍi wa-lā fis-samā’i wa-huwas-samī‘ul-‘alīm
+In the name of Allah with Whose name nothing can cause harm on earth or in the heaven and He is the All-Hearing the All-Knowing</t>
+  </si>
+  <si>
+    <t>أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذَا الْيَوْمِ فَتْحَهُ، وَنَصْرَهُ، وَنُورَهُ، وَبَرَكَتَهُ، وَهُدَاهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهِ وَشَرِّ مَا بَعْدَهُ
+Aṣbaḥnā wa-aṣbaḥal-mulku lillāhi rabbil-‘ālamīn Allāhumma innī as’aluka khayra hādhal-yawm: fatḥahu wa-naṣrahu wa-nūrahu wa-barakatahu wa-hudāh wa-a‘ūdhu bika min sharri mā fīhi wa-sharri mā ba‘dah
+We have reached the morning and at this very time all sovereignty belongs to Allah Lord of the worlds O Allah I ask You for the good of this day its triumphs its victories its light its blessings and its guidance and I take refuge in You from the evil of this day and the evil that follows it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أَصْبَحْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ Aṣbahnā `alā fiṭrati ‘l-Islām wa `alā kalimati ‘l-ikhlās wa `alā dīni nabiyyinā Muḥammadin (ṣallallāhu `alayhi wa sallam) wa `alā millati abīnā Ibrāhīm ḥanīfan Musliman wa mā kāna mina ‘l-mushrikīn We have entered a new day upon the natural religion of Islam the word of sincere devotion the religion of our Prophet Muhammad (peace and blessings of Allah be upon him) and the faith of our father Ibrahim He was upright (in worshipping Allah) and a Muslim He was not of those who worship others besides Allah
+</t>
+  </si>
+  <si>
+    <t>أسْتَغْفِرُ اللهَ وَأتُوبُ إلَيْهِ
+Astaghfiru-Llāha wa-atūbu ilayh
+I seek Allah's forgiveness and I turn in repentance to Him</t>
+  </si>
+  <si>
+    <t>بِاسْمِكَ رَبِّي وَضَعْتُ جَنْبِي وَبِكَ أَرْفَعُهُ، فَإِنْ أَمْسَكْتَ نَفْسِي فَارْحَمْهَا، وَإِنْ أَرْسَلْتَهَا فَاحْفَظْهَا بِمَا تَحْفَظُ بِهِ عِبَادَكَ الصَّالِحِينَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنَّكَ خَلَقْتَ نَفْسِي وَأَنْتَ تَوَفَّاهَا، لَكَ مَمَاتُهَا وَمَحْيَاهَا، إِنْ أَحْيَيْتَهَا فَاحْفَظْهَا، وَإِنْ أَمَتَّهَا فَاغْفِرْ لَهَا اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَافِيَةَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ قِنِي عَذَابَكَ يَوْمَ تَبْعَثُ عِبَادَكَ</t>
+  </si>
+  <si>
+    <t>بِاسْمِكَ اللَّهُمَّ أَمُوتُ وَأَحْيَا</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ رَبَّ السَّمَاوَاتِ السَّبْعِ وَرَبَّ الْعَرْشِ الْعَظِيمِ، رَبَّنَا وَرَبَّ كُلِّ شَيْءٍ، فَالِقَ الْحَبِّ وَالنَّوَى، وَمُنْزِلَ التَّوْرَاةِ وَالْإِنجِيلِ وَالْفُرْقَانِ، أَعُوذُ بِكَ مِنْ شَرِّ كُلِّ شَيْءٍ أَنْتَ آخِذٌ بِنَاصِيَتِهِ</t>
+  </si>
+  <si>
+    <t>للَّهُمَّ أَنْتَ الْأَوَّلُ فَلَيْسَ قَبْلَكَ شَيْءٌ، وَأَنْتَ الْآخِرُ فَلَيْسَ بَعْدَكَ شَيْءٌ، وَأَنْتَ الظَّاهِرُ فَلَيْسَ فَوْقَكَ شَيْءٌ، وَأَنْتَ الْبَاطِنُ فَلَيْسَ دُونَكَ شَيْءٌ، اقْضِ عَنَّا الدَّيْنِ وَأَغْنِنَا مِنَ الْفَقْرِ</t>
+  </si>
+  <si>
+    <t>الْحَمْدُ لِلَّهِ الَّذِي أَطْعَمَنَا وَسَقَانَا، وَكَفَانَا وَآوَانَا، فَكَمْ مِمَّنْ لَا كَافِيَ لَهُ وَلَا مُؤْوِيَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَسْلَمْتُ نَفْسِي إِلَيْكَ، وَفَوَّضْتُ أَمْرِي إِلَيْكَ، وَوَجَّهْتُ وَجْهِي إِلَيْكَ، وَأَلْجَأْتُ ظَهْرِي إِلَيْكَ، رَغْبَةً وَرَهْبَةً إِلَيْكَ، لَا مَلْجَأَ وَلَا مَنْجَى مِنْكَ إِلَّا إِلَيْكَ، آمَنْتُ بِكِتَابِكَ الَّذِي أَنْزَلْتَ، وَبِنَبِيِّكَ الَّذِي أَرْسَلْتَ</t>
+  </si>
+  <si>
+    <t>سُبْحَانَ اللَّهِ</t>
+  </si>
+  <si>
+    <t>الْحَمْدُ لِلَّهِ</t>
+  </si>
+  <si>
+    <t>اللَّهُ أَكْبَرُ</t>
+  </si>
+  <si>
+    <t>سُبْحَانَ اللَّهِ
+Subḥānal-lāh
+Glory is to Allah</t>
+  </si>
+  <si>
+    <t>الْحَمْدُ لِلَّهِ
+Al-ḥamdu lillāh
+All praise is to Allah</t>
+  </si>
+  <si>
+    <t>اللَّهُ أَكْبَرُ
+Allāhu Akbar
+Allah is the Most Great</t>
+  </si>
+  <si>
+    <t>آمَنَ الرَّسُولُ بِمَا أُنزِلَ إِلَيْهِ مِن رَّبِّهِ وَالْمُؤْمِنُونَ ۚ كُلٌّ آمَنَ بِاللَّهِ وَمَلَائِكَتِهِ وَكُتُبِهِ وَرُسُلِهِ لَا نُفَرِّقُ بَيْنَ أَحَدٍ مِّن رُّسُلِهِ ۚ وَقَالُوا سَمِعْنَا وَأَطَعْنَا ۖ غُفْرَانَكَ رَبَّنَا وَإِلَيْكَ الْمَصِيرُ ﴿٢٨٥﴾ لَا يُكَلِّفُ اللَّهُ نَفْسًا إِلَّا وُسْعَهَا ۚ لَهَا مَا كَسَبَتْ وَعَلَيْهَا مَا اكْتَسَبَتْ ۗ رَبَّنَا لَا تُؤَاخِذْنَا إِن نَّسِينَا أَوْ أَخْطَأْنَا ۚ رَبَّنَا وَلَا تَحْمِلْ عَلَيْنَا إِصْرًا كَمَا حَمَلْتَهُ عَلَى الَّذِينَ مِن قَبْلِنَا ۚ رَبَّنَا وَلَا تُحَمِّلْنَا مَا لَا طَاقَةَ لَنَا بِهِ ۖ وَاعْفُ عَنَّا وَاغْفِرْ لَنَا وَارْحَمْنَا ۚ أَنتَ مَوْلَانَا فَانصُرْنَا عَلَى الْقَوْمِ الْكَافِرِينَ ﴿٢٨٦﴾
+Āmanar-rasūlu bimā unzila ilayhi mir-rabbihi wal-mu'minūn kullun āmana billāhi wa-malā'ikatihi wa-kutubihi wa-rusulih lā nufarriqu bayna aḥadim-mir-rusulih wa-qālū sami‘nā wa-aṭa‘nā ghufrānaka rabbanā wa-ilaykal-maṣīr Lā yukalliful-lāhu nafsan illā wus‘ahā lahā mā kasabat wa-‘alayhā maktasabat rabbanā lā tu'ākhidhnā in-nasīnā aw akhṭa'nā rabbanā walā taḥmil ‘alaynā iṣran kamā ḥamaltahu ‘alalladhīna min qablinā rabbanā walā tuḥammilnā mā lā ṭāqata lanā bih wa‘fu ‘annā waghfir lanā warḥamnā anta mawlānā fanṣurnā ‘alal-qawmil-kāfirīn
+The Messenger has believed in what was revealed to him from his Lord and [so have] the believers All of them have believed in Allah and His angels and His books and His messengers [saying] "We make no distinction between any of His messengers" And they say "We hear and we obey [We seek] Your forgiveness our Lord and to You is the [final] destination" Allah does not charge a soul except [with that within] its capacity It will have [the consequence of] what [good] it has gained and it will bear [the consequence of] what [evil] it has earned "Our Lord do not impose blame upon us if we have forgotten or erred Our Lord and lay not upon us a burden like that which You laid upon those before us Our Lord and burden us not with that which we have no ability to bear And pardon us; and forgive us; and have mercy upon us You are our protector so give us victory over the disbelieving people"</t>
+  </si>
+  <si>
+    <t>بِاسْمِكَ رَبِّي وَضَعْتُ جَنْبِي وَبِكَ أَرْفَعُهُ، فَإِنْ أَمْسَكْتَ نَفْسِي فَارْحَمْهَا، وَإِنْ أَرْسَلْتَهَا فَاحْفَظْهَا بِمَا تَحْفَظُ بِهِ عِبَادَكَ الصَّالِحِينَ
+Bismika Rabbī waḍa‘tu janbī wa-bika arfa‘uh fa-in amsakta nafsī farḥamhā wa-in arsaltahā faḥfaẓhā bimā taḥfaẓu bihi ‘ibādakas-ṣāliḥīn
+In Your name my Lord I lie down and in Your name I rise If You should take my soul then have mercy upon it and if You should return it then protect it as You protect Your righteous servants</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ إِنَّكَ خَلَقْتَ نَفْسِي وَأَنْتَ تَوَفَّاهَا، لَكَ مَمَاتُهَا وَمَحْيَاهَا، إِنْ أَحْيَيْتَهَا فَاحْفَظْهَا، وَإِنْ أَمَتَّهَا فَاغْفِرْ لَهَا اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَافِيَةَ
+Allāhumma innaka khalaqta nafsī wa-anta tawaffāhā laka mamātuhā wa-maḥyāhā in aḥyaytahā faḥfaẓhā wa-in amattahā faghfir lahā Allāhumma innī as'aluka 'l-āfiyah
+O Allah You have created my soul and You take its life Unto You belongs its death and its life If You should keep it alive then protect it and if You should take its life then forgive it O Allah I ask You for well-being</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ قِنِي عَذَابَكَ يَوْمَ تَبْعَثُ عِبَادَكَ
+Allāhumma qinī ‘adhābaka yawma tab‘athu ‘ibādak
+O Allah save me from Your punishment on the Day that You resurrect Your servants</t>
+  </si>
+  <si>
+    <t>بِاسْمِكَ اللَّهُمَّ أَمُوتُ وَأَحْيَا
+Bismika-Llāhumma amūtu wa-aḥyā
+In Your name O Allah I die and I live</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ رَبَّ السَّمَاوَاتِ السَّبْعِ وَرَبَّ الْعَرْشِ الْعَظِيمِ، رَبَّنَا وَرَبَّ كُلِّ شَيْءٍ، فَالِقَ الْحَبِّ وَالنَّوَى، وَمُنْزِلَ التَّوْرَاةِ وَالْإِنجِيلِ وَالْفُرْقَانِ، أَعُوذُ بِكَ مِنْ شَرِّ كُلِّ شَيْءٍ أَنْتَ آخِذٌ بِنَاصِيَتِهِ
+Allāhumma rabbas-samāwātis-sab‘i wa-rabbal-arshil-aẓīm rabbanā wa-rabba kulli shay’ fāliqal-ḥabbi wan-nawā wa-munzilat-tawrāti wal-injīli wal-furqān a‘ūdhu bika min sharri kulli shay’in anta ākhidhun bi-nāṣiyatih
+O Allah Lord of the seven heavens and Lord of the Magnificent Throne our Lord and Lord of everything Splitter of the grain and the date-stone Revealer of the Torah the Gospel and the Criterion (the Quran) I seek refuge in You from the evil of everything whose forehead You hold</t>
+  </si>
+  <si>
+    <t>للَّهُمَّ أَنْتَ الْأَوَّلُ فَلَيْسَ قَبْلَكَ شَيْءٌ، وَأَنْتَ الْآخِرُ فَلَيْسَ بَعْدَكَ شَيْءٌ، وَأَنْتَ الظَّاهِرُ فَلَيْسَ فَوْقَكَ شَيْءٌ، وَأَنْتَ الْبَاطِنُ فَلَيْسَ دُونَكَ شَيْءٌ، اقْضِ عَنَّا الدَّيْنِ وَأَغْنِنَا مِنَ الْفَقْرِ
+Allāhumma antal-awwalu falaysa qablaka shay' wa-antal-ākhiru falaysa ba‘daka shay' wa-antaz-ẓāhiru falaysa fawqaka shay' wa-antal-bāṭinu falaysa dūnaka shay' iqḍi ‘annad-dayna wa-aghninā minal-faqr
+O Allah You are the First and there is nothing before You and You are the Last and there is nothing after You You are the Manifest and there is nothing above You and You are the Hidden and there is nothing beyond You Decide our debt for us and remove our poverty</t>
+  </si>
+  <si>
+    <t>الْحَمْدُ لِلَّهِ الَّذِي أَطْعَمَنَا وَسَقَانَا، وَكَفَانَا وَآوَانَا، فَكَمْ مِمَّنْ لَا كَافِيَ لَهُ وَلَا مُؤْوِيَ
+Al-ḥamdu lillāhil-ladhī aṭ‘amanā wa-saqānā wa-kafānā wa-āwānā fakam mimman lā kāfiya lahu wa-lā mu'wī
+Praise is to Allah Who has fed us and given us drink and Who has sufficed us and given us shelter for how many are there who have no one to suffice them and no one to give them shelter</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَسْلَمْتُ نَفْسِي إِلَيْكَ، وَفَوَّضْتُ أَمْرِي إِلَيْكَ، وَوَجَّهْتُ وَجْهِي إِلَيْكَ، وَأَلْجَأْتُ ظَهْرِي إِلَيْكَ، رَغْبَةً وَرَهْبَةً إِلَيْكَ، لَا مَلْجَأَ وَلَا مَنْجَى مِنْكَ إِلَّا إِلَيْكَ، آمَنْتُ بِكِتَابِكَ الَّذِي أَنْزَلْتَ، وَبِنَبِيِّكَ الَّذِي أَرْسَلْتَ
+Allāhumma aslamtu nafsī ilayk wa-fawwaḍtu amrī ilayk wa-wajjahtu wajhī ilayk wa-alja'tu ẓahrī ilayk raghbatan wa-rahbatan ilayk lā malja'a wa-lā manjan minka illā ilayk āmantu bi-kitābikal-ladhī anzalt wa-bi-nabiyyikal-ladhī arsalt
+O Allah I submit myself to You entrust my affairs to You turn my face to You and lay myself down depending upon You out of hope and fear of You There is no refuge and no escape from You except to You I believe in Your Book which You have revealed and in Your Prophet whom You have sent</t>
+  </si>
+  <si>
+    <t>أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ اللَّهُمَّ أَنْتَ السَّلَامُ وَمِنْكَ السَّلَامُ، تَبَارَكْتَ يَا ذَا الْجَلَالِ وَالْإِكْرَامِ</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، اللَّهُمَّ لَا مَانِعَ لِمَا أَعْطَيْتَ، وَلَا مُعْطِيَ لِمَا مَنَعْتَ، وَلَا يَنْفَعُ ذَا الْجَدِّ مِنْكَ الْجَدُّ</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، لَا حَوْلَ وَلَا قُوَّةَ إِلَّا بِاللَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَلَا نَعْبُدُ إِلَّا إِيَّاهُ، لَهُ النِّعْمَةُ وَلَهُ الْفَضْلُ وَلَهُ الثَّنَاءُ الْحَسَنُ، لَا إِلَٰهَ إِلَّا اللَّهُ مُخْلِصِينَ لَهُ الدِّينَ وَلَوْ كَرِهَ الْكَافِرُونَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَجِرْنِي مِنْ النَّار</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَعِنِّي عَلَى ذِكْرِكَ وَشُكْرِكَ وَحُسْنِ عِبَادَتِكَ</t>
+  </si>
+  <si>
+    <t>أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ اللَّهُمَّ أَنْتَ السَّلَامُ وَمِنْكَ السَّلَامُ، تَبَارَكْتَ يَا ذَا الْجَلَالِ وَالْإِكْرَامِ
+Astaghfiru-Llāh, Astaghfiru-Llāh, Astaghfiru-Llāh Allāhumma antas-salāmu wa-minkas-salām, tabārakta yā dhal-jalāli wal-ikrām
+I seek Allah's forgiveness (three times) O Allah, You are Peace and from You comes peace Blessed are You, O Owner of majesty and honor</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، اللَّهُمَّ لَا مَانِعَ لِمَا أَعْطَيْتَ، وَلَا مُعْطِيَ لِمَا مَنَعْتَ، وَلَا يَنْفَعُ ذَا الْجَدِّ مِنْكَ الْجَدُّ
+Lā ilāha illallāhu waḥdahu lā sharīka lah, lahul-mulku wa-lahul-ḥamd, wa-huwa ‘alā kulli shay’in qadīr Allāhumma lā māni‘a limā aṭayt, wa-lā mu‘ṭiya limā mana‘t, wa-lā yanfa‘u dhal-jaddi minkal-jadd
+None has the right to be worshipped except Allah, alone, without partner, to Him belongs all sovereignty and praise, and He is over all things Omnipotent O Allah, none can prevent what You lead to give, and none can give what You prevent, and no wealth or majesty can benefit anyone against Your will</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، لَا حَوْلَ وَلَا قُوَّةَ إِلَّا بِاللَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَلَا نَعْبُدُ إِلَّا إِيَّاهُ، لَهُ النِّعْمَةُ وَلَهُ الْفَضْلُ وَلَهُ الثَّنَاءُ الْحَسَنُ، لَا إِلَٰهَ إِلَّا اللَّهُ مُخْلِصِينَ لَهُ الدِّينَ وَلَوْ كَرِهَ الْكَافِرُونَ
+Lā ilāha illallāhu waḥdahu lā sharīka lah, lahul-mulku wa-lahul-ḥamd, wa-huwa ‘alā kulli shay’in qadīr Lā ḥawla wa-lā quwwata illā billāh Lā ilāha illallāhu wa-lā na‘budu illā iyyāh, lahun-ni‘matu wa-lahul-faḍlu wa-lahuth-thanā’ul-ḥasan Lā ilāha illallāhu mukhliṣīna lahud-dīna wa-law karihal-kāfirūn
+None has the right to be worshipped except Allah, alone, without partner, to Him belongs all sovereignty and praise and He is over all things Omnipotent There is no might nor power except with Allah None has the right to be worshipped except Allah and we worship none other than Him From Him comes all favor and to Him belongs all grace and to Him belongs all good praise None has the right to be worshipped except Allah, we are sincere in our devotion to Him even though the disbelievers may detest it</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَجِرْنِي مِنْ النَّار
+Allāhumma ajirnī minan-nār
+O Allah, protect me from the Fire</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ أَعِنِّي عَلَى ذِكْرِكَ وَشُكْرِكَ وَحُسْنِ عِبَادَتِكَ
+Allāhumma a‘innī ‘alā dhikrika, wa-shukrika, wa-ḥusni ‘ibādatik
+O Allah, help me to remember You, to give You thanks, and to worship You in the best of manners</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ اجْعَلْ فِي قَلْبِي نُوراً، وَفِي لِسَانِي نُوراً، وَاجْعَلْ فِي سَمْعِي نُوراً، وَاجْعَلْ فِي بَصَرِي نُوراً، وَاجْعَلْ مِنْ خَلْفِي نُوراً، وَمِنْ أَمَامِي نُوراً، وَاجْعَلْ مِنْ فَوْقِي نُوراً، وَمِنْ تَحْتِي نُوراً، اللَّهُمَّ أَعْطِنِي نُوراً</t>
+  </si>
+  <si>
+    <t>يَبْدَأُ بِرِجْلِهِ اليُمْنَى، وَيَقُولُ: أَعُوذُ بِاللَّهِ الْعَظِيمِ، وَبِوَجْهِهِ الْكَرِيمِ، وَسُلْطَانِهِ الْقَدِيمِ، مِنَ الشَّيْطَانِ الرَّجِيمِ [بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ]، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ اجْعَلْ فِي قَلْبِي نُوراً، وَفِي لِسَانِي نُوراً، وَاجْعَلْ فِي سَمْعِي نُوراً، وَاجْعَلْ فِي بَصَرِي نُوراً، وَاجْعَلْ مِنْ خَلْفِي نُوراً، وَمِنْ أَمَامِي نُوراً، وَاجْعَلْ مِنْ فَوْقِي نُوراً، وَمِنْ تَحْتِي نُوراً، اللَّهُمَّ أَعْطِنِي نُوراً
+Allāhumma-j‘al fī qalbī nūrā wa-fī lisānī nūrā wa-j‘al fī sam‘ī nūrā wa-j‘al fī baṣarī nūrā wa-j‘al min khalfī nūrā wa-min amāmī nūrā wa-j‘al min fawqī nūrā wa-min taḥtī nūrā Allāhumma a‘ṭinī nūrā
+O Allah place light in my heart and on my tongue light and place light in my hearing and place light in my seeing and place light behind me and light before me and place light above me and light beneath me O Allah grant me light</t>
+  </si>
+  <si>
+    <t>يَبْدَأُ بِرِجْلِهِ اليُمْنَى، وَيَقُولُ: أَعُوذُ بِاللَّهِ الْعَظِيمِ، وَبِوَجْهِهِ الْكَرِيمِ، وَسُلْطَانِهِ الْقَدِيمِ، مِنَ الشَّيْطَانِ الرَّجِيمِ [بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ]، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ
+A‘ūdhu billāhil-‘aẓīm wa-bi-wajhihil-karīm wa-sulṭānihil-qadīm minash-shayṭānir-rajīm Bismillāhi waṣ-ṣalātu was-salāmu ‘alā rasūlillāh Allāhummaf-taḥ lī abwāba raḥmatik
+I seek refuge in Allah the Almighty in His Noble Face and in His Eternal Dominion from Satan the outcast In the name of Allah and blessings and peace be upon the Messenger of Allah O Allah open for me the gates of Your mercy</t>
+  </si>
+  <si>
+    <t>يَبْدَأُ بِرِجْلِهِ الْيُسْرَى، وَيَقُولُ: بِسْمِ اللَّهِ وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ مِنْ فَضْلِكَ، اللَّهُمَّ اعْصِمْنِي مِنَ الشَّيْطَانِ الرَّجِيمِ
+Bismillāhi waṣ-ṣalātu was-salāmu ‘alā rasūlillāh Allāhumma innī as’aluka min faḍlik Allāhumma‘-ṣimnī minash-shayṭānir-rajīm
+In the name of Allah and peace and blessings be upon the Messenger of Allah O Allah I ask You from Your favor O Allah guard me from Satan the outcast</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ ﴿١﴾
+الْحَمْدُ لِلَّهِ رَبِّ الْعَالَمِينَ ﴿٢﴾ الرَّحْمَٰنِ الرَّحِيمِ ﴿٣﴾ مَالِكِ يَوْمِ الدِّينِ ﴿٤﴾ إِيَّاكَ نَعْبُدُ وَإِيَّاكَ نَسْتَعِينُ ﴿٥﴾ اهْدِنَا الصِّرَاطَ الْمُسْتَقِيمَ ﴿٦﴾ صِرَاطَ الَّذِينَ أَنْعَمْتَ عَلَيْهِمْ غَيْرِ الْمَغْضُوبِ عَلَيْهِمْ وَلَا الضَّالِّينَ ﴿٧﴾</t>
+  </si>
+  <si>
+    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ ﴿١﴾ 
+الْحَمْدُ لِلَّهِ رَبِّ الْعَالَمِينَ ﴿٢﴾ الرَّحْمَٰنِ الرَّحِيمِ ﴿٣﴾ مَالِكِ يَوْمِ الدِّينِ ﴿٤﴾ إِيَّاكَ نَعْبُدُ وَإِيَّاكَ نَسْتَعِينُ ﴿٥﴾ اهْدِنَا الصِّرَاطَ الْمُسْتَقِيمَ ﴿٦﴾ صِرَاطَ الَّذِينَ أَنْعَمْتَ عَلَيْهِمْ غَيْرِ الْمَغْضُوبِ عَلَيْهِمْ وَلَا الضَّالِّينَ ﴿٧﴾
+Bismillāhir-raḥmānir-raḥīm 
+Al-ḥamdu lillāhi rabbil-‘ālamīn Ar-raḥmānir-raḥīm Mālikiyawmid-dīn Iyyāka na‘budu wa-iyyāka nasta‘īn Ihdinaṣ-ṣirāṭal-mustaqīm Ṣirāṭal-ladhīna an‘amta ‘alayhim ghayril-maghḍūbi ‘alayhim walad-ḍāllīn
+In the name of Allah the Beneficent the Merciful 
+Praise is to Allah Lord of the worlds The Beneficent the Merciful Owner of the Day of Judgment You alone we worship and You alone we ask for help Guide us to the straight path The path of those upon whom You have bestowed favor not of those who have evoked [Your] anger or of those who are astray</t>
+  </si>
+  <si>
+    <t>اللهُ اللهُ رَبِّي لَا أُشْرِكُ بِهِ شَيْئًا
+Allāhu Allāhu rabbī lā ushriku bihi shay'ā
+Allah Allah is my Lord I do not associate anything with Him</t>
+  </si>
+  <si>
+    <t>لَّا إِلَٰهَ إِلَّا أَنتَ سُبْحَانَكَ إِنِّي كُنتُ مِنَ الظَّالِمِينَ
+Lā ilāha illā anta subḥānaka innī kuntu minaz-ẓālimīn
+There is no deity except You; exalted are You Indeed I have been of the wrongdoers</t>
+  </si>
+  <si>
+    <t>حَسْبُنَا اللَّهُ وَنِعْمَ الْوَكِيلُ
+Ḥasbunāl-Lāhu wa-ni‘mal-wakīl
+Allah is sufficient for us and He is the best Disposer of affairs</t>
+  </si>
+  <si>
+    <t>لَا حَوْلَ وَلَا قُوَّةَ إِلَّا بِاللَّهِ الْعَلِيِّ الْعَظِيمِ
+Lā ḥawla wa-lā quwwata illā billāhil-‘aliyyil-‘aẓīm
+There is no might nor power except with Allah the Most High the Most Great</t>
+  </si>
+  <si>
+    <t>لَا إِلَٰهَ إِلَّا اللَّهُ الْعَظِيمُ الْحَلِيمُ، لَا إِلَٰهَ إِلَّا اللَّهُ رَبُّ الْعَرْشِ الْعَظِيمِ، لَا إِلَٰهَ إِلَّا اللَّهُ رَبُّ السَّمَاوَاتِ وَرَبُّ الْأَرْضِ وَرَبُّ الْعَرْشِ الْكَرِيمِ
+Lā ilāha illallāhul-‘Aẓīmul-Ḥalīm lā ilāha illallāhu Rabbul-‘Arshil-‘aẓīm lā ilāha illallāhu Rabbus-samāwāti wa-Rabbul-arḍi wa-Rabbul-‘Arshil-karīm
+There is no deity except Allah the Magnificent the Forbearing There is no deity except Allah Lord of the Magnificent Throne There is no deity except Allah Lord of the heavens and Lord of the earth and Lord of the Noble Throne</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ رَحْمَتَكَ أَرْجُو فَلَا تَكِلْنِي إِلَى نَفْسِي طَرْفَةَ عَيْنٍ، وَأَصْلِحْ لِي شَأْنِي كُلَّهُ، لَا إِلَٰهَ إِلَّا أَنْتَ
+Allāhumma raḥmataka arjū falā takilnī ilā nafsī ṭarfata ‘ayn wa-aṣliḥ lī sha’nī kullahu lā ilāha illā ant
+O Allah it is Your mercy that I hope for so do not leave me to myself even for the blink of an eye and rectify for me all of my affairs There is no deity except You</t>
+  </si>
+  <si>
+    <t>اللَّهُمَّ صَلِّ وَسَلِّيمْ عَلَى نَبِيِّنَا مُحَمَّدٍ
+Allāhumma ṣalli wa-sallim ‘alā nabiyyinā Muḥammad
+O Allah send Your praise and peace upon our Prophet Muhammad</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 75
+Primary Hadith Authorities: Al-Hakim (1/562), An-Nasa'i, and At-Tabarani
+Authentication: Authenticated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273), noting that At-Tabarani's chain of transmission is Jayyid (Reliable/Good)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الحماية والإجارة من الجن: من قرأها حين يصبح كان في حفظ الله وأمانه من أذى الشياطين والجن حتى يمسي، ومن قرأها حين يمسي كان محمياً منهم حتى يصبح
+📚 التوثيق المعتمد
+المصدر: أخرجه الحاكم (1/ 562)، وصححه الألباني في صحيح الترغيب والترهيب برقم (1/ 273)، وعزاه إلى النسائي والطبراني
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 76
+Primary Hadith Authorities: Jami' at-Tirmidhi (5/567) and Sunan Abu Dawud (4/322)
+Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/182)
+Whoever recites these three times in the morning and in the evening, they will suffice him (as a protection) against everything</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الكفاية التامة: تكفي العبد من كل شر، وضُر، وسوء، وتغنيه عن أي حماية أو رقية أخرى في يومه وليلته
+📚 التوثيق المعتمد
+المصدر: رواه الترمذي، وأبو داود، والنسائي
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 78 / 79
+Primary Hadith Authorities: Sahih Muslim (4/2088)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 78
+Primary Hadith Authorities: Jami' at-Tirmidhi
+Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/142)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 79 (Sayyid al-Istighfar)
+Primary Hadith Authorities: Sahih al-Bukhari (7/150), Sunan an-Nasa'i, and Jami' at-Tirmidhi
+Authentication: Structurally authenticated and universally accepted within Sahih al-Bukhari</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 80
+Primary Hadith Authorities: Sunan Abu Dawud (4/317), Al-Bukhari (Al-Adab al-Mufrad), An-Nasa'i ('Amalul-Yawm wal-Laylah), and Ibn As-Sunni
+Authentication: Chains of transmission from An-Nasa'i and Abu Dawud graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 23)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 81
+Primary Hadith Authorities: Sunan Abu Dawud (4/318), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 7), Ibn As-Sunni (No 41), and Sahih Ibn Hibban (No 2361)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 24)
+Please paste the next citatio</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 82
+Primary Hadith Authorities: Sunan Abu Dawud (4/324), Musnad Ahmad (5/42), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 22), Ibn As-Sunni (No 69), and Al-Bukhari (Al-Adab al-Mufrad)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 26)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 83
+Primary Hadith Authorities: Ibn As-Sunni (No 71) and Sunan Abu Dawud (4/321)
+Authentication: Both reports are traced directly back to the Prophet ﷺ (Marfu'), with the chain of transmission from Ibn As-Sunni graded Sahih (Sound)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 84
+Primary Hadith Authorities: Sunan Abu Dawud and Sunan Ibn Majah
+Authentication: Authenticated in Sheikh Al-Albani's Sahih Sunan Ibn Majah (2/332)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 85
+Primary Hadith Authorities: Jami' at-Tirmidhi and Sunan Abu Dawud
+Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/142)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الاستعاذة من مصادر الشرور: تحصين كامل للعبد من شر نفسه الأمارة بالسوء، ومن وساوس الشيطان وحبائله وشِركه
+الوقاية من الأذى المتعدي: حماية المسلم من أن يرتكب ذنباً يضر به نفسه، أو يتسبب في إلحاق الضرر والأذى بغيره من المسلمين
+📚 التوثيق المعتمد
+المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح الترمذي (3/142)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)، الذِّكْر رقم (85)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 86
+Primary Hadith Authorities: Sunan Abu Dawud (4/323), Jami' at-Tirmidhi (5/465), Sunan Ibn Majah (2/332), and Musnad Ahmad
+Authentication: Ibn Majah's chain of transmission is graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 39)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 87
+Primary Hadith Authorities: Musnad Ahmad (4/337), An-Nasa'i ('Amalul-Yawm wal-Laylah, p 4), Ibn As-Sunni (No 68), and Jami' at-Tirmidhi (5/465)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 39)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 88
+Primary Hadith Authorities: Mustadrak Al-Hakim (1/545)
+Authentication: Chain of transmission graded Sahih (Sound) by Al-Hakim, as corroborated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 89
+Primary Hadith Authorities: Sunan Abu Dawud (4/322) and Ibn al-Qayyim (Zad al-Ma'ad, 2/273)
+Authentication: Chain of transmission graded Hasan (Good)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 90
+Primary Hadith Authorities: Musnad Ahmad (3/406-407, 5/123), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 34), and Jami' at-Tirmidhi (4/209)
+Authentication: Traced through early authoritative prophetic traditions and traditionally preserved across key Sunan and Musnad compilations</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 91
+Primary Hadith Authorities: Sahih al-Bukhari (4/2071)
+Authentication: Structurally authenticated and universally accepted within Sahih al-Bukhari</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 92
+Primary Hadith Authorities: An-Nasa'i ('Amalul-Yawm wal-Laylah, No 24)
+Authentication: Chain of transmission graded Sahih (Sound) by Sheikh Al-Albani (Sahih al-Jami', 1/272)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الأجور الأربعة العظيمة: كتب الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
+الحفظ من الشيطان: حماية للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
+📚 التوثيق المعتمد
+المصدر: أخرجه النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 94
+Primary Hadith Authorities: Sahih Muslim (4/2090)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 95
+Primary Hadith Authorities: Sunan Ibn Majah (No 925) and Ibn As-Sunni (No 54)
+Authentication: Chain of transmission graded Hasan (Good) by Ibn al-Qayyim (Zad al-Ma'ad, 2/375)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 96
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/101) and Sahih Muslim (4/2075)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 97
+Primary Hadith Authorities: Musnad Ahmad (2/290), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 590), Jami' at-Tirmidhi (3/187), Ibn As-Sunni (No 68), and Sunan Ibn Majah (2/266)
+Authentication: Sunan Ibn Majah's chain is graded Sahih (Sound) by Sheikh Al-Albani, and Jami' at-Tirmidhi's report is graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 45)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 98
+Primary Hadith Authorities: Al-Mu'jam al-Kabir by At-Tabarani
+Authentication: Reported via two transmission chains, with one graded Jayyid (Reliable/Good) Verified by Al-Haythami in Majma' uz-Zawa'id (10/120) and authenticated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening)
+Primary Hadith Authorities: Musnad Ahmad (Hadith No 19606) and Al-Bukhari (Al-Adab al-Mufrad, Hadith No 716)
+Authentication: Graded Sahih (Authentic) by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (Hadith No 36)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+السلامة من الشرك: وقاية العبد وحمايته من الوقوع في الشرك الأكبر والأصغر (كالرياء وخفاء المقاصد)
+تطهير السريرة: إظهار العجز والافتقار إلى الله بطلب المغفرة عن الذنوب والخطايا غير المتعمدة التي لا يعلمها الإنسان
+📚 التوثيق المعتمد
+المصدر: خرّجه الإمام أحمد في المسند (حديث رقم 19606)، وخرّجه الإمام البخاري في الأدب المفرد (حديث رقم 716)، وصححه الإمام الألباني في صحيح الترغيب والترهيب (حديث رقم 36)
+الكتاب المتداول: حصن المسلم، باب: ما يقول من خاف الشرك</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening)
+Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 2893, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 11/173) and Sunan Abi Dawud (Hadith No 1555)
+Authentication &amp; Textual Origin: The foundational narration originates in Sahih al-Bukhari via Anas bin Malik (ra) with highly similar wording The explicit, famous wording preserved in this specific text is recorded by Sunan Abi Dawud within the narrative of Abu Umamah (ra)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+تفريج الهموم والكروب: التماس النجاة والوقاية من أمهات الآفات النفسية والبدنية والمالية والاجتماعية التي تُقعد العبد عن دينه ودنياه
+التحصن من قهر الدَّيْن: حماية للمسلم من ضيق المداين وغلبة الرجال وتسلّط الأعداء، وبث الطمأنينة والانشراح في الصدر والقلب
+📚 التوثيق المعتمد
+المصدر: أصله في صحيح البخاري (حديث رقم 2893، وانظر فتح الباري 11/173) من حديث أنس بن مالك رضي الله عنه بلفظ متقارب واللفظ المشهور المذكور أعلاه رواه أبو داود في سننه (رقم 1555) في قصة أبي أمامة رضي الله عنه
+الكتاب المتداول: حصن المسلم، باب: أذكار الصباح والمساء / الكرب ودفع الهم</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening)
+Primary Hadith Authorities: Sunan Abi Dawud (Hadith No 1517) and Jami' at-Tirmidhi (Hadith No 3577)
+Authentication: Graded Sahih (Authentic) by Sheikh Al-Albani in Sahih Jami' at-Tirmidhi (3/182) and in Mishkat al-Masabih (No 2353)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+مغفرة الكبائر والذنوب العظام: نيل مغفرة الله الشاملة للذنوب، حتى وإن ارتكب العبد ذنباً عظيماً كالفرار من الزحف (الهروب من معركة القتال)
+التوسل بالاسم الأعظم: يجمع الاستغفار بين إعلان التوبة الصادقة والاعتراف بربوبية الله المتضمنة لصفات الحياة والقيومية
+📚 التوثيق المعتمد
+المصدر: خرّجه الإمام أبو داود في سننه (حديث رقم 1517)، وخرّجه الإمام الترمذي في سننه (حديث رقم 3577)، وصححه الإمام الألباني في صحيح الترمذي (3/182)، وفي مشكاة المصابيح (رقم 2353)
+الكتاب المتداول: حصن المسلم، باب: أذكار الاستغفار والتوبة</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 81
+Primary Hadith Authorities: Sunan Abu Dawud (4/318), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 7), Ibn As-Sunni (No 41), and Sahih Ibn Hibban (No 2361)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 24)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 101
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 9/94) and Sahih Muslim (1/554)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>"If any of you rises from his bed and later returns to it, let him dust off his bed with his waist garment three times and mention the Name of Allah, for he does not know what may have entered the bed after him, and when he lies down he should say   " 
+Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 102
+Primary Hadith Authorities: Sahih al-Bukhari (11/126) and Sahih Muslim (4/2084)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 103
+Primary Hadith Authorities: Sahih Muslim (4/2083) and Musnad Ahmad (2/79)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>When the Prophet (ﷺ) wanted to lie down to sleep, he used to place his right hand under his cheek and say
+Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 104
+Primary Hadith Authorities: Sunan Abu Dawud (4/311) and Jami' at-Tirmidhi
+Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/143)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here, dying and living are metaphors for sleep and wakefulness This explains why the normal order of these words has been reversed in this Hadith In other contexts the living is mentioned before dying 
+Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 105
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/113) and Sahih Muslim (4/2083)
+Quranic Foundations: Cross-referenced with foundational verses of divine life and ownership, including Surah Al-Baqarah </t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 107
+Primary Hadith Authorities: Sahih Muslim (4/2084)
+Quranic Foundations &amp; Notes: References the Gospel (Injil) revealed to 'Isa (Jesus), cross-referenced textually with Surah Al-'Alaq (96:15) regarding the textual concept of seizure by the forelock preceding being cast into Hell
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 107
+Primary Hadith Authorities: Sahih Muslim (4/2084)
+Quranic Foundations &amp; Notes: References the Gospel (Injil) revealed to 'Isa (Jesus), cross-referenced textually with Surah Al-'Alaq (96:15) regarding the concept of seizure by the forelock preceding being cast into Hell
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 108
+Primary Hadith Authorities: Sahih Muslim (4/2085)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Before you go to bed perform ablutions as you would for prayer, then lie down on your right side and say   The Prophet (ﷺ) said: Whoever says this and dies in his sleep, has died in a state of the natural monotheism (Fitrah)
+Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 111
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/113) and Sahih Muslim (4/2081)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28 (Before Sleeping), Supplication No 101
+Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 5361, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 9/506) and Sahih Muslim (Hadith No 2727)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>عن علي رضي الله عنه أن فاطمة رضي الله عنها شكت ما تلقى في يدها من الرحى وأتت النبي ﷺ تسأله خادماً، فلم تجده، فذكرت ذلك لعائشة، فلما جاء النبي ﷺ أخبرته، فجاءنا وقد أخذنا مضاجعنا، فذهبتُ قمْتُ، فقال: «مَكانَكما» فجلس بيننا حتى وجدتُ برَدَ قدميه على صدري، فقال: «ألا أدلُّكما على خيرٍ مما سألتُما؟ إذا أويتما إلى فراشكما -أو أخذتما مضاجعكما- فكبرا أربعاً وثلاثين، وسبحا ثلاثاً وثلاثين، واحْمدا ثلاثاً وثلاثين، فهو خير لكما من خادم» (رواه البخاري ومسلم)
+🤲 فضل الذكر
+ خيرٌ من خادم والتمكين بالقوة: يمنح الذاكرَ قوة بدنية ونشاطاً عظيماً يُغنيه عن الاستعانة بخادم، ويعينه على تحمل مشاق الأعمال اليومية وإنجازها دون تعب
+ إعانة النفس وطرد التعب: سبب في تيسير الأمور وتفريج الكربات البدنية والنفسية، حيث وجّه النبي ﷺ ابنتَه فاطمة وعلياً رضي الله عنهما إليه عند شكوى التعب
+📚 التوثيق المعتمد
+ المصدر: أخرجه البخاري في صحيحه، ومسلم في صحيحه، من حديث علي بن أبي طالب رضي الله عنه
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28 (Before Sleeping), Supplication No 102
+Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 5361, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 9/506) and Sahih Muslim (Hadith No 2727)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28 (Before Sleeping), Supplication No 104
+Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 5361, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 9/506) and Sahih Muslim (Hadith No 2727)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Reference: Allah will write ten Hasanaat (rewards) for whoever recites this ten times in the morning, and forgive him ten misdeeds and give him the reward of freeing ten slaves and protect him from Satan Whoever recites this ten times in the evening will get this same reward
+Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 92
+Primary Hadith Authorities: An-Nasa'i ('Amalul-Yawm wal-Laylah, No 24)
+Authentication: Chain of transmission graded Sahih (Sound) by Sheikh Al-Albani (Sahih al-Jami', 1/272)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الأجور الأربعة العظيمة: كَتَبَ الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
+ الحفظ من الشيطان: حماية تامّة للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
+📚 التوثيق المعتمد
+ المصدر: أخرجه النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 66
+Primary Hadith Authorities: Sahih Muslim (1/414)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 67
+Primary Hadith Authorities: Sahih al-Bukhari (1/255) and Sahih Muslim (1/414)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 68
+Primary Hadith Authorities: Sahih Muslim (1/415)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 69
+Primary Hadith Authorities: Sahih Muslim (1/418)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Allah will write ten Hasanaat (rewards) for whoever recites this ten times in the morning, and forgive him ten misdeeds and give him the reward of freeing ten slaves and protect him from Satan Whoever recites this ten times in the evening will get this same reward An-Nasa'i, 'Amalul-Yawm wal-Laylah (no 24) 
+Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 92
+Primary Hadith Authorities: An-Nasa'i ('Amalul-Yawm wal-Laylah, No 24)
+Authentication: Chain of transmission graded Sahih (Sound) by Sheikh Al-Albani (Sahih al-Jami', 1/272)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening), Supplication No 72
+Primary Hadith Authorities: Sahih Muslim (4/2090)
+Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 75 (Cross-referenced under Chapter 25: After Salam in certain thematic indexes)
+Primary Hadith Authorities: Al-Hakim (1/562), An-Nasa'i, and At-Tabarani
+Authentication: Authenticated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273), noting that At-Tabarani's chain of transmission is Jayyid (Reliable/Good)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (Words of Remembrance After Prayer), Supplication No 29 (Note: Depending on the edition's layout, it may correspond to sub-numbering within Chapter 25 or sequential text positioning)
+Primary Hadith Authorities: Sahih Muslim (1/414) / Sahih al-Bukhari
+Authentication: Structurally authenticated and universally accepted across the core canonical traditions</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الأجور الأربعة العظيمة: كَتَبَ الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
+ الحفظ من الشيطان: حماية تامّة للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
+📚 التوثيق المعتمد
+ المصدر: أخرجه الإمام النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الأجور الأربعة العظيمة: كتب الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
+ الحفظ من الشيطان: حماية تامّة للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
+📚 التوثيق المعتمد
+ المصدر: أخرجه النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ سؤال مقاصد الحياة الصالحة: يجمع العبد في بداية يومه سؤال ثلاثة أمور هي قوام السعادة والنجاح: العلم الذي ينفع صاحبه والأمة، والرزق الحلال المبارك فيه، والعمل الصالح المكتوب له القبول عند الله
+📚 التوثيق المعتمد
+ المصدر: خرّجه الإمام ابن ماجه في سننه (حديث رقم 925)، والإمام أحمد في المسند (6/294)، وصححه الإمام الألباني في صحيح ابن ماجه (1/152)
+ الكتاب المتداول: حصن المسلم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Hadith is authentic (Sahih) It was narrated by Imam Muslim in his Sahih on the authority of Abdullah bin Abbas (may Allah be pleased with them both), in the story of his staying overnight at the house of his maternal aunt, Maymunah, the wife of the Prophet ﷺ, and his description of the Prophet’s ﷺ prayer at night and his departure </t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 20 (Thematic entry: Supplication for entering the mosque)
+Primary Hadith Authorities: Sunan Abi Dawud (Hadith No 466), Sahih Muslim (Hadith No 713), and Sunan Ibn Majah (Hadith No 771)
+Authentication &amp; Textual Origin: Compiled as a unified text from multiple intersecting transmission strands and explicitly authenticated by Sheikh Al-Albani</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 21 (Thematic entry: Supplication for exiting the mosque)
+Primary Hadith Authorities: Sahih Muslim (Hadith No 713) and Sunan Ibn Majah (Hadith No 773 for the explicit protection clause)
+Authentication: Authenticated as Sahih (Authentic) by Sheikh Al-Albani</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 82 (Cross-referenced under Chapter 27: Morning and Evening Remembrance, and highly utilized across thematic text sections for Ruqyah)
+Primary Hadith Authorities: Sunan Abu Dawud (4/324), Musnad Ahmad (5/42), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 22), Ibn As-Sunni (No 69), and Al-Bukhari (Al-Adab al-Mufrad)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 26)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 122 (Thematic entry: Supplication for times of distress)
+Primary Hadith Authorities: Sahih al-Bukhari (7/154) and Sahih Muslim (4/2092)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 123 (Thematic entry: Supplication for times of distress)
+Primary Hadith Authorities: Jami' at-Tirmidhi (5/521)
+Authentication: Authenticated as Sahih (Authentic) by Sheikh Al-Albani in Sahih Jami' at-Tirmidhi (3/168)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 132 (Thematic entry: Supplication when facing an enemy or a person of authority)
+Primary Hadith Authorities: Sunan Abi Dawud (2/89) and Al-Hakim (2/142)
+Authentication: Authenticated as Sahih (Authentic) by Al-Hakim, as corroborated and agreed upon by Ad-Dhahabi</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 124 (Thematic entry: Supplication for times of distress and seeking assistance)
+Primary Hadith Authorities: Sunan Abi Dawud (4/324) and Jami' at-Tirmidhi (5/521)
+Authentication: Authenticated as Sahih (Authentic) by Sheikh Al-Albani</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 241 (Thematic entry: Chapter 123 - Seeking forgiveness and repentance)
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Fath al-Bari, 11/101) and Sahih Muslim (4/2075)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 120 (Thematic entry: Chapter 35 - Supplication for times of distress)
+Primary Hadith Authorities: Sunan Abi Dawud (4/324) and Musnad Ahmad (5/42)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz, as corroborated by Sheikh Al-Albani in Sahih Sunan Abi Dawud (3/932)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 121 (Thematic entry: Supplication for times of distress)
+Primary Hadith Authorities: Sunan Abu Dawud (4/324) and Musnad Ahmad (5/42)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 38) and authenticated by Sheikh Al-Albani in Sahih Sunan Abi Dawud</t>
+  </si>
+  <si>
+    <t>Reference: The Prophet (ﷺ) said: "Who recites blessings upon me ten times in the morning and ten times in the evening will obtain my intercession on the Day of Resurrection" At-Tabarani reported this Hadith together with two chains of transmission One of them is reliable (Jayyid) See Haythami's Majma'uz-Zawa'id 10/120, and Al-Albani's Sahihut-Targhib wat-Tarhib 1/273 
+Hisn al-Muslim 98
+Chapter 27: In the morning and evening, Book: Fortress of the Muslim (Hisn al-Muslim)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 87 (Cross-referenced under Chapter 27: Morning and Evening Remembrance, and highly utilized across thematic sections for distress, anxiety, and ultimate relief)
+Primary Hadith Authorities: Musnad Ahmad (4/337), An-Nasa'i ('Amalul-Yawm wal-Laylah, p 4), Ibn As-Sunni (No 68), and Jami' at-Tirmidhi (5/465)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 39)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 81
+Primary Hadith Authorities: Abu Dawud (4/318), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 7), Ibn As-Sunni (No 41), and Ibn Hibban (No 2361)
+Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 24)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 130, Supplication No 255 (Cross-referenced with No 93)
+Primary Hadith Authorities: Sahih al-Bukhari (7/67) and Sahih Muslim (4/2071)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t>فضل الذكر
+أجر عتق الرقاب: نيل ثواب عظيم يُعادل عتق أربعة أنفس حرّة من ذرية النبي إسماعيل عليه السلام
+تحقيق التوحيد الخالص: تجديد العهد مع الله بإثبات الألوهية، والملك، والحمد، والقدرة المطلقة له وحده لا شريك له
+📚 التوثيق المعتمد
+المصدر: صحيح البخاري (حديث رقم 6404) وصحيح مسلم (حديث رقم 2693)
+الكتاب المتداول: حصن المسلم، الباب 130 (باب فضل التسبيح والتحميد، والتهليل، والتكبير)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 1, Supplication No 3
+Primary Hadith Authorities: Jami' at-Tirmidhi (5/473)
+Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/144)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 1, Supplication No 4
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/113) and Sahih Muslim (4/2083)
+Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> فضل الذكر
+تجديد التوحيد والشكر: حمد الله على بعث البدن وردّ الروح بعد النوم (الموت الأصغر)
+التذكير بالآخرة: الاستعداد للبعث والنشور الحقيقي بالعمل الصالح منذ أول دقيقة في اليوم
+📚 التوثيق المعتمد
+المصدر: صحيح البخاري، كتاب الدعوات (انظر فتح الباري لابن حجر، مجلد 11، ص 113)
+الكتاب المتداول: حصن المسلم، الباب الأول (أذكار الاستيقاظ من النوم، الحديث الأول)</t>
+  </si>
+  <si>
+    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 1, Supplication No 5
+Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 3/39) and Sunan Ibn Majah (2/335)
+Authentication: The primary virtue is authenticated in Sahih al-Bukhari, with the specific textual wording utilized coming from Sunan Ibn Majah</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> فضل الذكر
+مغفرة الذنوب: تنقية العبد من الخطايا فور استيقاظه من النوم وتعاره بالليل
+إجابة الدعاء: فرصة عظيمة لاستجابة أي دعاء يدعو به العبد في تلك اللحظة
+قبول الصلاة: تضمن قبول صلاته إذا توضأ وصلى بعد قراءة هذا الذكر
+📚 التوثيق المعتمد
+المصدر: صحيح البخاري، كتاب التهجد، مع لفظ ابن ماجه في سننه (انظر فتح الباري لابن حجر، مجلد 3، ص 39)
+الكتاب المتداول: حصن المسلم، الباب الأول (أذكار الاستيقاظ من النوم، الحديث الثاني)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🤲 فضل الذكر
+ تفويض الملك والحمد لله: إعلان التوحيد الخالص والاستسلام لله في بداية اليوم ونهايته
+ طلب الخير الشامل والوقاية: الاستعانة بالله لنيل خير اليوم والمستقبل، والتحصن من الكسل، وسوء الكبر، وعذاب القبر والنار
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم (4/2088)، وأخرجه الترمذي (رقم 3390)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء) </t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+التوكل والالتجاء التام: إقرار العبد بأن كل حركاته وسكناته، وحياته وموته، وتقلبه في الصباح والمساء لا تكون إلا بالله وبتدبيره
+استحضار المآل والآخرة: تذكير النفس بمرجعها إلى الله وحده بالبعث والنشور صباحاً، والمصير والرجوع إليه مساءً
+📚 التوثيق المعتمد
+المصدر: أخرجه الترمذي في سننه (المجلد 3، صفحة 142، رقم 3391)، وصححه في صحيح الترمذي
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+موجب لدخول الجنة: مَن قاله موقناً بقلبه بصدق ما فيه حين يمسي ومات من ليلته دخل الجنة، ومَن قاله موقناً به حين يصبح ومات من يومه دخل الجنة
+أعلى صيغ الاستغفار: يتضمن التذلل والخضوع والاعتراف بنعم الله وتقصير العبد في حقه
+📚 التوثيق المعتمد
+المصدر: رواه البخاري (7/150، رقم 6306)، ورواه غيره في النسائي والترمذي
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+العتق من النار: مَن قرأ هذا الذكر أربع مرات في الصباح أو في المساء، كتب الله له النجاة والخلاص من عذاب النار في ذلك اليوم أو تلك الليلة
+📚 التوثيق المعتمد
+المصدر: رواه أبو داود (4/317)، وأخرجه البخاري في الأدب المفرد، والنسائي في عمل اليوم والليلة، وابن السني وإسناد النسائي وأبي داود حسن (تحسين الشيخ ابن باز)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+أداء شكر اليوم والليلة: مَن قرأه في الصباح فقد أدّى شكر يومه كاملًا، ومَن قرأه في المساء فقد أدّى شكر ليلته تجاه نعم الله
+الاعتراف بالمنعم: إقرار العبد بأن كل النعم الظاهرة والباطنة التي يتقلب فيها أو في غيره من الخلائق هي من فضل الله وحده
+📚 التوثيق المعتمد
+المصدر: رواه أبو داود (4/318)، والنسائي في عمل اليوم والليلة (رقم 7)، وابن السني (رقم 41)، وابن حبان (رقم 2361) وإسناده حسن (تحسين الشيخ ابن باز)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+سؤال العافية الشاملة: طلب سلامة البدن وحفظ الحواس (السمع والبصر) من الأمراض والفتن ليستعملها العبد في طاعة الله
+الاستعاذة من المهلكات: التحصن بالله من الكفر المذهب للدين، والفقر المضر بالدنيا، ومن عذاب القبر في الآخرة
+📚 التوثيق المعتمد
+المصدر: رواه أبو داود (4/324)، والإمام أحمد (5/42)، والنسائي في عمل اليوم والليلة (رقم 22)، وابن السني (رقم 69)، والبخاري في الأدب المفرد وإسناده حسن (تحسين الشيخ ابن باز في تحفة الأخيار)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+كفاية الهموم: من قالها سبع مرات في الصباح أو في المساء كفاه الله عز وجل كل ما يشغل باله أو يُقلقه من أمور الدنيا والآخرة
+تحقيق التوكل: تفويض الأمر لله والاعتماد عليه وحده لجلب المصالح ودفع المضار
+📚 التوثيق المعتمد
+المصدر: رواه ابن السني في عمل اليوم والليلة (رقم 71)، وأخرجه أبو داود (4/321) وكلا الروايتين مرفوعتان مباشرة إلى النبي ﷺ، وإسناد ابن السني صحيح
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الحفظ الشامل والتحصين التام: طلب الوقاية والحفظ الإلهي من الأدواء والشرور والمصائب التي قد تصيب العبد من سائر الجهات الست
+سؤال صلاح الدين والدنيا: جمعُ كل خير يرجوه المسلم بسؤال العفو المغفرة للذنوب، والعافية والبركة في النفس، والأهل، والمال، والأمن من المخاوف
+📚 التوثيق المعتمد
+المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح ابن ماجه (2/332)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الاستعاذة من مصادر الشرور: تحصين كامل للعبد من شر نفسه الأمارة بالسوء، ومن وساوس الشيطان وحبائله وشِركه
+الوقاية من الأذى المتعدي: حماية المسلم من أن يرتكب ذنباً يضر به نفسه، أو يتسبب في إلحاق الضرر والأذى بغيره من المسلمين
+📚 التوثيق المعتمد
+المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح الترمذي (3/142)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الحماية من فجأة البلاء: مَن قالها ثلاث مرات حين يصبح لم تُصبه فجأة بلاء ومصيبة بغتة حتى يمسي، ومَن قالها ثلاث مرات حين يمسي حُفظ من فجأة البلاء حتى يصبح
+التحصين الشامل: الاستعانة والاعتصام باسم الله الذي لا يمكن لأي مخلوق أو داء أو شر في الأرض ولا في السماء أن يضر أحداً يتحصن به
+📚 التوثيق المعتمد
+المصدر: رواه أبو داود (4/323)، والترمذي (5/465)، وابن ماجه (2/332)، والإمام أحمد؛ وإسناد ابن ماجه حسن (بتحسين الشيخ ابن باز)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+نيل رضا الله عز وجل: من قالها ثلاث مرات حين يصبح وثلاث مرات حين يمسي، كان حقاً ووعداً على الله سبحانه وتعالى أن يرضيه يوم القيامة ويثيبه بالجنة
+تجديد الرضا واليقين: ترسيخ القناعة التامة والرضا القلبي بربوبية الله، وتشريع الإسلام، ويسر وسنة النبي محمد ﷺ
+📚 التوثيق المعتمد
+المصدر: رواه الإمام أحمد (4/337)، والنسائي في عمل اليوم والليلة (ص 4)، وابن السني (رقم 68)، والترمذي (5/465) وإسناده حسن (بتحسين الشيخ ابن باز)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+صلاح الأحوال التام: طلب الاستعانة برحمة الله التي وسعت كل شيء لإصلاح كافة شؤون العبد الدينية والدنيوية
+البراءة من الحول والقوة: إظهار الافتقار التام إلى الله، والتحصن به من الخذلان أو أن يكل الله العبد إلى تدبير نفسه الضعيفة ولو للحظة واحدة
+📚 التوثيق المعتمد
+المصدر: أخرجه الحاكم في المستدرك (1/545)، وصححه، ووافقه الذهبي، وصححه الألباني في صحيح الترغيب والترهيب (1/273)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+سؤال الخيرات الخمس: التماس البركة والتوفيق الكامل في اليوم بنيل الفتح (تيسير الرزق والعمل)، والنصر على الأعداء والشيطان، ونور العلم والإيمان، والبركة في الوقت، والهدى والثبات على الحق
+التحصن من الشرور: حماية العبد من الآفات والشرور والذنوب التي قد تقع في يومه أو في غده
+📚 التوثيق المعتمد
+المصدر: رواه أبو داود (4/322)، وإسناده حسن وانظر أيضاً: ابن القيم في زاد المعاد (2/273)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+تجديد ميثاق الإيمان: ثبات العبد على الفطرة السوية (الإسلام)، وكلمة التوحيد الخالص (لا إله إلا الله)، والاستمساك بسنة النبي ﷺ ونهج الأنبياء من أول النهار وآخره
+البراءة من الشرك: التبرؤ من سائر ملل الكفر والشرك، وإعلان الاستسلام والانقياد لله وحده حنيفاً مسلماً
+📚 التوثيق المعتمد
+المصدر: رواه الإمام أحمد (3/406-407، و5/123)، والنسائي في عمل اليوم والليلة (رقم 34)، والترمذي (4/209)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+نيل الصدارة يوم القيامة: لم يأتِ أحدٌ يوم القيامة بعملٍ أفضل وأعلى ثواباً ممّن قال هذا الذكر، إلا عبدٌ قال مثل قوله أو زاد عليه في العدد
+محو الخطايا والذنوب: ثوابه يغفر الكبائر والذنوب وإن كانت كثيرة ومثل زبد البحر (كما ورد في الروايات الأخرى للحديث)
+📚 التوثيق المعتمد
+المصدر: رواه البخاري (4/2071)، وكذلك رواه مسلم
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+مضاعفة الأجر والثواب: يعادل في ثوابه وأجره ساعات طويلة من الذكر والعبادة المستمرة، حيث يسبح العبد الله بأعظم الأعداد والصفات
+الثناء العظيم الشامل: تنزيه الله وحمده بعبارات تجمع سائر المخلوقات، وزنة العرش العظيم، ومداد الكلمات الإلهية التي لا تنفد
+📚 التوثيق المعتمد
+المصدر: رواه مسلم (4/2090)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+سؤال مقاصد الحياة الصالحة: يجمع العبد في بداية يومه سؤال ثلاثة أمور هي قوام السعادة والنجاح: العلم الذي ينفع صاحبه والأمة، والرزق الحلال المبارك فيه، والعمل الصالح المكتوب له القبول عند الله
+📚 التوثيق المعتمد
+المصدر: أخرجه ابن ماجه (رقم 925)، وابن السني في عمل اليوم والليلة (رقم 54) وإسناده حسن (بتحسين الإمام ابن القيم في زاد المعاد 2/375)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الاقتداء بالسنة النبوية: لزوم هدي النبي ﷺ وتطبيق سنته الفِعلية، حيث كان يستغفر الله ويتوب إليه مئة مرة في اليوم مع أنه قد غُفِر له ما تقدم من ذنبه وما تأخر
+تطهير القلب وتفريج الهموم: جلاء القلوب من الغفلة والذنوب، وجلب السكينة، وسعة الرزق، وتيسير الأمور المتعسرة للمسلم في يومه وليله
+📚 التوثيق المعتمد
+المصدر: رواه البخاري (انظر فتح الباري لابن حجر 11/101)، ورواه مسلم (4/2075)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🤲 فضل الذكر
+الوقاية من السموم واللدغات: مَن قالها ثلاث مرات حين يمسي لم تضره حَمَةٌ (لدغة عقرب أو حية أو حشرة سامة) في تلك الليلة
+التحصين من الشرور: الاستعاذة بكلمات الله الكاملة التي لا يدخلها نقص، للحماية من شرور الإنس، والجن، والسباع، وسائر الهوام والمخلوقات
+📚 التوثيق المعتمد
+المصدر: رواه الإمام أحمد (2/290)، والنسائي في عمل اليوم والليلة (رقم 590)، والترمذي (3/187)، وابن السني (رقم 68) وإسناد ابن ماجه (2/266) صحيح بحسب الألباني، وحسّن الشيخ ابن باز حديث الترمذي
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء) </t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+نيل الشفاعة النبوية: من حافظ على الصلاة على النبي ﷺ عشر مرات في الصباح وعشر مرات في المساء، نال وعداً صادقاً بأن تدركه شفاعة النبي ﷺ يوم القيامة
+كفاية الهم وغفران الذنب: امتثال أمر الله بالصلاة على رسوله، وهي سبب عظيم لتفريج الهموم والكروب، ونزول الرحمات والبركة على العبد في يومه وليلته
+📚 التوثيق المعتمد
+المصدر: رواه الطبراني بإسنادين أحدهما جيد، وانظر: مجمع الزوائد للهيثمي (10/120)، وحسنه الألباني في صحيح الترغيب والترهيب (1/273)
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ تفويض الملك والحمد لله: إعلان التوحيد الخالص والاستسلام لله في بداية اليوم ونهايته
+ طلب الخير الشامل والوقاية: الاستعانة بالله لنيل خير الليلة والمستقبل، والتحصن من الكسل، وسوء الكبر، وعذاب القبر والنار
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم (4/2088)، وأخرجه الترمذي (رقم 3390)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ التوكل والالتجاء التام: إقرار العبد بأن كل حركاته وسكناته، وحياته وموته، وتقلبه في الصباح والمساء لا تكون إلا بالله وبتدبيره
+ استحضار المآل والآخرة: تذكير النفس بمرجعها إلى الله وحده بالمصير والرجوع إليه مساءً، وبالبعث والنشور صباحاً
+📚 التوثيق المعتمد
+ المصدر: أخرجه الترمذي في سننه (المجلد 3، صفحة 142، رقم 3391)، وصححه في صحيح الترمذي
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ العتق من النار: مَن قرأ هذا الذكر أربع مرات في الصباح أو في المساء، كتب الله له النجاة والخلاص من عذاب النار في ذلك اليوم أو تلك الليلة
+📚 التوثيق المعتمد
+ المصدر: رواه أبو داود (4/317)، وأخرجه البخاري في الأدب المفرد، والنسائي في عمل اليوم والليلة، وابن السني وإسناد النسائي وأبي داود حسن (بتحسين الشيخ ابن باز)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ أداء شكر اليوم والليلة: مَن قرأه في الصباح فقد أدّى شكر يومه كاملًا، ومَن قرأه في المساء فقد أدّى شكر ليلته تجاه نعم الله
+ الاعتراف بالمنعم: إقرار العبد بأن كل النعم الظاهرة والباطنة التي يتقلب فيها أو في غيره من الخلائق هي من فضل الله وحده
+📚 التوثيق المعتمد
+ المصدر: رواه أبو داود (4/318)، والنسائي في عمل اليوم والليلة (رقم 7)، وابن السني (رقم 41)، وابن حبان (رقم 2361) وإسناده حسن (بتحسين الشيخ ابن باز)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ سؤال الخيرات الخمس: التماس البركة والتوفيق الكامل في الليلة أو اليوم بنيل الفتح (تيسير الرزق والعمل)، والنصر على الأعداء والشيطان، ونور العلم والإيمان، والبركة في الوقت، والهدى والثبات على الحق
+ التحصن من الشرور: حماية العبد من الآفات والشرور والذنوب التي قد تقع في ليلته (أو يومه) أو في غده
+📚 التوثيق المعتمد
+ المصدر: رواه أبو داود (4/322)، وإسناده حسن وانظر أيضاً: ابن القيم في زاد المعاد (2/273)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ تجديد ميثاق الإيمان: ثبات العبد على الفطرة السوية (الإسلام)، وكلمة التوحيد الخالص (لا إله إلا الله)، والاستمساك بسنة النبي ﷺ ونهج الأنبياء من أول النهار وآخره
+ البراءة من الشرك: التبرؤ من سائر ملل الكفر والشرك، وإعلان الاستسلام والانقياد لله وحده حنيفاً مسلماً
+📚 التوثيق المعتمد
+ المصدر: رواه الإمام أحمد (3/406-407، و5/123)، والنسائي في عمل اليوم والليلة (رقم 34)، والترمذي (4/209)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ سؤال مقاصد الحياة الصالحة: يجمع العبد في بداية يومه سؤال ثلاثة أمور هي قوام السعادة والنجاح: العلم الذي ينفع صاحبه والأمة، والرزق الحلال المبارك فيه، والعمل الصالح المكتوب له القبول عند الله
+📚 التوثيق المعتمد
+ المصدر: أخرجه ابن ماجه (رقم 925)، وابن السني في عمل اليوم والليلة (رقم 54) وإسناده حسن (بتحسين الإمام ابن القيم في زاد المعاد 2/375)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الكفاية التامة: من قرأ هاتين الآيتين في ليلته كفتاه من كل سوء ومكروه، وقيل كفتاه وأجزأتاه عن قيام تلك الليلة من العبادة والذكر
+ تثبيت أركان الإيمان: تذكير بأصول العقيدة والتوكل، وسؤال الله اللطف، والمغفرة، والنصر على الأعداء قبل النوم
+📚 التوثيق المعتمد
+ المصدر: سورة البقرة (الآيتان 285-286) رواه البخاري (انظر فتح الباري لابن حجر 9/94)، ورواه مسلم (1/554)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ طلب الرحمة والحفظ عند النوم: تفويض الأمر لله تعالى وتسليمه الروح حال النوم، وسؤاله الرحمة والمغفرة للنفس إن قُبضت وماتت، والحفظ والرعاية والوقاية من الشرور إن كُتبت لها الحياة وعادت للدنيا
+📚 التوثيق المعتمد
+ المصدر: رواه البخاري (11/126)، ورواه مسلم (4/2084)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ التسليم المطلق لله: إقرار العبد بأن المحيا والممات وتدبير الروح والنفس بيد الله وحده لا شريك له
+ سؤال العافية والمغفرة: جمعُ الاستعاذة والطلب لحفظ النفس وصيانتها في حياتها، وسؤال المغفرة والرحمة لها بعد مماتها، مع طلب العافية الشاملة في الدين والدنيا
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم (4/2083)، والإمام أحمد (2/79)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الوقاية من أهوال الآخرة: سؤال الله الحماية والسلامة من عذاب يوم القيامة (يوم البعث والنشور)
+ الاقتداء بالهدي النبوي: لزوم سُنّة النبي ﷺ في هيئة النوم بوضع اليد اليمنى تحت الخد واستحضار الآخرة قبل النوم
+📚 التوثيق المعتمد
+ المصدر: رواه أبو داود (4/311)، وانظر أيضاً: صحيح الترمذي للألباني (3/143)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الاستسلام والافتتاح باسم الله: إيداع العبد نفسه وروحه لله تعالى عند الموتة الصغرى (النوم)، وتفويض حياته وموته ويقظته لتدبيره سبحانه
+ الاقتداء بالهدى النبوي: لزوم سُنّة النبي ﷺ في جعل آخر كلامه قبل النوم ذكراً لله وثناءً عليه، ليكون يومه منتهياً على الطاعة والتوحيد
+📚 التوثيق المعتمد
+ المصدر: أصله في صحيح البخاري (انظر فتح الباري لابن حجر العسقلاني 11/113)، ورواه مسلم (4/2083)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ قضاء الديون وتفريج الأزمات المادية: الالتجاء إلى الله سبحانه بنية التخلص من ثقل الديون وضيق الفقر، وسؤاله السعة والغنى في المال والرزق
+ التحصن بأسماء الله الحسنى: تفويض الأمر لله المستحق للربوبية المطلقة والقدرة التامة على كل المخلوقات، والاستعاذة به من شرور كل الدواب والآفات في الدنيا والآخرة
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (4/2084، رقم 2713)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ قضاء الديون وتفريج الأزمات المادية: الالتجاء إلى الله سبحانه بنية التخلص من ثقل الديون وضيق الفقر، وسؤاله السعة والغنى في المال والرزق
+ التحصن بأسماء الله الحسنى: تفويض الأمر لله المستحق للربوبية المطلقة والقدرة التامة على كل المخلوقات، والاستعاذة به من شرور كل الدواب والآفات في الدنيا والآخرة
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (4/2084، رقم 2713)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ استشعار نعم الله الكبرى: تذكير النفس بأجلّ النعم الدنيوية (الطعام، والشراب، والكفاية، والسكن) قبل النوم، ومقارنة حال العبد بمن حُرموا من المأوى والأمان لزيادة شكر الله
+ تحقيق الرضا والطمأنينة: الاعتراف بكفاية الله ولطفه ورعايته للعبد، مما يورث راحة البال وانشراح الصدر وطرد المخاوف قبل النوم
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (4/2085)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الاستعاذة من مصادر الشرور: تحصين كامل للعبد من شر نفسه الأمارة بالسوء، ومن وساوس الشيطان وحبائله وشِركه
+ الوقاية من الأذى المتعدي: حماية المسلم من أن يرتكب ذنباً يضر به نفسه، أو يتسبب في إلحاق الضرر والأذى بغيره من المسلمين
+📚 التوثيق المعتمد
+ المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح الترمذي (3/142)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الموت على الفطرة والسنة: مَن قال هذا الذكر قبل نومه ثم مات في ليلته تلك، مات على الفطرة السوية (دين الإسلام) وكان ممّن خُتم لهم بخير
+ كمال التفويض والتوكل: تفويض العبد سائر شؤونه وحياته لله وحده، وإظهار الافتقار التام والالتجاء إليه رغبةً في ثوابه ورهبةً من عقابه
+📚 التوثيق المعتمد
+ المصدر: رواه البخاري (انظر فتح الباري لابن حجر العسقلاني 11/113)، ورواه مسلم (4/2081)
+ الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ تحقيق التوحيد وإخلاص الدين: إعلان البراءة من الشرك، والاعتراف بأن النعمة والفضل والثناء كله لله وحده، مما يرسخ صدق العبودية والتوكل في قلب العبد بعد الفراغ من الصلاة
+ الاستعانة بالله والاعتراف بعجزه: التبرؤ من الحول والقوة الشخصية بالالتجاء إلى قوة الله (الحوقلة) لتيسير سائر الأعمال والطاعات
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (1/414)
+ الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ موجب لدخول الجنة: مَن حافظ على قراءتها فور الفراغ من الصلاة المكتوبة، لم يمنعه من دخول الجنة إلا أن يموت (بناءً على الأحاديث المفسرة للفضل في هذا الباب)
+ التحصين الشامل: حماية العبد وحفظه في ذمة الله ورعايته من الصلاة إلى الصلاة الأخرى
+📚 التوثيق المعتمد
+ المصدر: رواه البخاري (1/255)، ورواه مسلم (1/414)
+ الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ مغفرة الذنوب الشاملة: غفران خطايا العبد وذنوبه وإن كانت كثيرة مثل زبد البحر
+ تحقيق الأجور العظيمة بعد الصلاة: الاستمساك بالباقيات الصالحات التي تثقل الموازين وتجلب معية الله للعبد عقب الفراغ من الفريضة
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (1/415)
+ الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ مغفرة الذنوب الشاملة: غفران خطايا العبد وذنوبه وإن كانت كثيرة مثل زبد البحر عند المحافظة عليها خلف كل صلاة
+ التحصين والوقاية دبر الصلاة: حماية المسلم وكفايته من سائر الشرور والآفات والشرك بوساطة الاستعاذة بأعظم السور والتعوذ بها
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (1/418)
+ الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الحماية والإجارة من الجن والشياطين: مَن قرأها حين يصبح كان في حفظ الله وأمانه من أذى الشياطين حتى يمسي، ومَن قرأها حين يمسي أُجير وحُفظ منهم حتى يصبح
+ أعظم آية في كتاب الله: تشتمل على أصول التوحيد والأسماء والصفات العليا لله تعالى، وقراءتها تورث الطمأنينة والأمان التام للعبد
+📚 التوثيق المعتمد
+ المصدر: أخرجه الحاكم في المستدرك (1/562)، وصححه الألباني في صحيح الترغيب والترهيب (رقم 662 / 1/273)، وعزاه إلى النسائي والطبراني بإسناد جيد
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ كفاية الهموم وضيق الصدر: من قالها سبع مرات في الصباح أو في المساء كفاه الله عز وجل كل ما يشغل باله أو يُقلقه من أمور الدنيا والآخرة، وهي ركيزة أساسية في أدعية كشف الكرب والفرج
+ تحقيق التوكل التام: تفويض الأمر لله والاعتمد عليه وحده لجلب المصالح ودفع المضار، مما يورث النفس طمأنينة وسكينة
+📚 التوثيق المعتمد
+ المصدر: رواه ابن السني في عمل اليوم والليلة (رقم 71)، وأخرجه أبو داود (4/321) وكلا الروايتين مرفوعتان مباشرة إلى النبي ﷺ، وإسناد ابن السني صحيح
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ نيل الشفاعة النبوية: من حافظ على الصلاة على النبي ﷺ عشر مرات في الصباح وعشر مرات في المساء، نال وعداً صادقاً بأن تدركه شفاعة النبي ﷺ يوم القيامة
+ كفاية الهم وغفران الذنب: امتثال أمر الله بالصلاة على رسوله، وهي ركيزة أساسية في أدعية مفاتيح الفرج، وسبب عظيم لتفريج الهموم والكروب، ونزول الرحمات والبركة على العبد في يومه وليلته
+📚 التوثيق المعتمد
+ المصدر: رواه الطبراني بإسنادين أحدهما جيد، وانظر: مجمع الزوائد للهيثمي (10/120)، وحسنه الألباني في صحيح الترغيب والترهيب (1/273)
+ الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ طلب الرزق والخير البري: سؤال الله سبحانه وتعالى أن يفتح للعبد أبواب فضله الواسع، تيمناً بخروجه من المسجد والسعي في طلب الرزق والمعاش الحلال في الدنيا
+ العصمة والتحصين من الشيطان: نيل الوقاية والحفظ الإلهي من وساوس الشيطان ومكايده طوال فترة بقاء العبد خارج المسجد بعد انصرافه من العبادة
+📚 التوثيق المعتمد
+ المصدر: خرّجه الإمام مسلم في صحيحه (حديث رقم 713 للفقرة الأولى)، والإمام ابن ماجه في سننه (حديث رقم 773 لزيادة العصمة من الشيطان)، وصححه الإمام الألباني في (صحيح سنن ابن ماجه 1/129) وصحيح الجامع (رقم 515)
+ الكتاب المتداول: حصن المسلم، باب: دعاء الخروج من المسجد</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الحفظ من الشيطان طوال اليوم: الاستعاذة بالله العظيم وبأوصافه الجليلة عند دخول المسجد سبب في أن يقول الشيطان: "حُفِظَ مِنِّي سَائِرَ الْيَوْمِ"
+ التعرض للرحمات الإلهية: سؤال الله سبحانه وتعالى أن يفتح للعبد أبواب رحمته الواسعة، تيمناً بدخول بيت من بيوته ومظانّ نزول رحماته ورضوانه
+📚 التوثيق المعتمد
+ المصدر: خرّجه الإمام أبو داود في سننه (حديث رقم 466 للفقرة الأولى)، والإمام مسلم في صحيحه (حديث رقم 713 للفقرة الأخيرة)، والإمام ابن ماجه في سننه (حديث رقم 771 للبشير والصلاة) وصحح الإمام الألباني الأجزاء المجتمعة في (صحيح أبي داود 1/93) وصحيح الجامع
+ الكتاب المتداول: حصن المسلم، باب: دعاء دخول المسجد</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ سؤال الهداية الشاملة: طلب إحاطة النور الإلهي بالعبد من سائر جهاته الست، وفي حواسه الظاهرة والباطنة ليعصمه الله من الغواية
+ الاستضاءة يوم القيامة: التماس النور الحقيقي والهدى في الدنيا ليكون للمسلم نوراً عظيماً يستضيء به يوم القيامة في أهوال الظلم
+📚 التوثيق المعتمد
+ المصدر: رواه الإمام مسلم في صحيحه (رقم 763) عن عبد الله بن عباس رضي الله عنهما، في قصة مبيته عند خالته ميمونة زوج النبي ﷺ، ووصفه لصلاة النبي ﷺ بالليل وخروجه للفجر
+ الكتاب المتداول: حصن المسلم، باب: الدعاء للذهاب إلى المسجد</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الحماية والوقاية الدائمة: تحصين شامل للعبد وكفاية له من كل شر وسوء، وعصمة من الآفات بوساطة التعوذ بأعظم سور الحفظ دبر كل فريضة
+ مغفرة الذنوب: التزام التعقيب بالقرآن والذكر خلف الصلوات المكتوبة يعد من أسباب نيل مغفرة الله ومحو الخطايا
+📚 التوثيق المعتمد
+ المصدر: رواه مسلم في صحيحه (1/418) [رقم 523] من حديث عقبة بن عامر رضي الله عنه قال: "أمرني رسول الله ﷺ أن أقرأ بالمعوذات دبر كل صلاة"
+ الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+الوقاية من السموم واللدغات: مَن قالها ثلاث مرات حين يمسي لم تضره حَمَةٌ (لدغة عقرب أو حية أو حشرة سامة) في تلك الليلة
+التحصين من الشرور: الاستعاذة بكلمات الله الكاملة التي لا يدخلها نقص، للحماية من شرور الإنس، والجن، والسباع، وسائر الهوام والمخلوقات
+📚 التوثيق المعتمد
+المصدر: رواه الإمام أحمد (2/290)، والنسائي في عمل اليوم والليلة (رقم 590)، والترمذي (3/187)، وابن السني (رقم 68) وإسناد ابن ماجه (2/266) صحيح بحسب الألباني، وحسّن الشيخ ابن باز حديث الترمذي
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ شكر نعمة العافية والبعث: اعتراف بفضل الله المتمثل في سلامة البدن بعد النوم، وحمده على ردّ الروح التي هي في حكم المتوفاة عند النوم لتستأنف طاعته
+ التوفيق لملازمة الذكر: الثناء على الله الذي تفضل بفتح باب مناجاته والإذن للعبد بذكره وحمده فور استيقاظه، وجعل بداية اليوم منفتحة على العبودية
+📚 التوثيق المعتمد
+ المصدر: أخرجه الإمام الترمذي في سننه (المجلد 5، صفحة 473، رقم 3401)، وحسنه الإمام الألباني في صحيح سنن الترمذي (3/144)
+ الكتاب المتداول: حصن المسلم، الباب الأول (أذكار الاستيقاظ من النوم)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> فضل الذكر
+أداء شكر اليوم والليلة: مَن قاله في الصباح فقد أدّى شكر يومه كاملًا، ومَن قاله في المساء فقد أدّى شكر ليلته
+الاعتراف بالمنعم: إقرار العبد بأن كل النعم التي يتقلب فيها هو أو سائر الخلائق هي محض فضل وكرم من الله وحده
+📚 التوثيق المعتمد
+المصدر: أخرجه أبو داود (رقم 5073)، والنسائي في السنن الكبرى (رقم 9835/9832)، وابن حبان (رقم 861)، عن عبد الله بن غنام البياضي رضي الله عنه
+الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ الاستعانة بالله لمدّ العبد بالقوة والتوفيق للثبات على ذكره الدائم، وشكره على نعمه الظاهرة والباطنة، والإتيان بالعبادات على الوجه الأكمل والأحسن الذي يرضيه
+ وصية نبوية غالية: تذكير بمكانة هذا الدعاء العظيم
+يَا مُعَاذُ، وَاللَّهِ إِنِّي لَأُحِبُّكَ، وَاللَّهِ إِنِّي لَأُحِبُّكَ، فَقَالَ : أُوصِيكَ يَا مُعَاذُ لَا تَدَعَنَّ فِي دُبُرِ كُلِّ صَلَاةٍ تَقُولُ اللَّهُمَّ أَعِنِّي عَلَى ذِكْرِكَ، وَشُكْرِكَ، وَحُسْنِ عِبَادَتِكَ
+📚 التوثيق المعتمد
+ المصدر: خرّجه الإمام أبو داود في سننه (حديث رقم 1522)، والإمام النسائي في السنن (الكبرى والصغرى، حديث رقم 1303)، وصححه الإمام الألباني في صحيح أبي داود (1/284)، وفي صحيح الجامع (رقم 7969)
+ الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">🕋  </t>
     </r>
     <r>
@@ -849,7 +2220,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: الاغتسال، والتنظيف، وارتداء ملابس الإحرام، ثم عقد النية بالقلب
-« </t>
+</t>
     </r>
     <r>
       <rPr>
@@ -870,7 +2241,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : تقول , « لَبَّيْكَ اللَّهُمَّ عُمْرَةً
+      <t xml:space="preserve"> : تقول , لَبَّيْكَ اللَّهُمَّ عُمْرَةً
  الاشتراط عند الخوف من عائق: اللَّهُمَّ مَحِلِّي حَيْثُ حَبَسْتَنِي
  </t>
     </r>
@@ -906,7 +2277,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Step 2</t>
+      <t xml:space="preserve"> الخطوة الثانية</t>
     </r>
     <r>
       <rPr>
@@ -916,1428 +2287,256 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Entering Al-Masjid Al-Haram
-🔹 What to Do? (Action Steps):
-• Enter the mosque stepping with your right foot first.
-🕋  Supplication (Dua) for Entering the Mosque:
-«بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ»
-"Bismillah, was-salatu was-salamu 'ala Rasulillah. Allahumma-ftah li abwaba rahmatik."
-(In the name of Allah, and peace and blessings be upon the Messenger of Allah. O Allah, open the gates of Your mercy for me)
-👁️ Upon Seeing the Kaaba for the First Time:
-«اللَّهُمَّ زِدْ هَٰذَا الْبَيْتَ تَشْرِيفًا وَتَعْظِيمًا وَتَكْرِيمًا وَمَهَابَةً»
-"Allahumma zid hadhal-bayta tashrifan wa ta'dhiman wa takriman wa mahabah."
-(O Allah, increase this House in honor, greatness, respect, and awe)</t>
+      <t xml:space="preserve">: دخول المسجد الحرام
+</t>
     </r>
-  </si>
-  <si>
-    <t>يَبْدَأُ بِرِجْلِهِ الْيُسْرَى، وَيَقُولُ: بِسْمِ اللَّهِ وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ مِنْ فَضْلِكَ، اللَّهُمَّ اعْصِمْنِي مِنَ الشَّيْطَانِ الرَّجِيمِ</t>
-  </si>
-  <si>
-    <t>اللّهُـمَّ ما أَصْبَـَحَ بي مِـنْ نِعْـمَةٍ أَوْ بِأَحَـدٍ مِـنْ خَلْـقِك، فَمِـنْكَ وَحْـدَكَ لا شَرِيكَ لَـك، فَلَـكَ الْحَمْـدُ وَلَـكَ الشُّكْـر</t>
-  </si>
-  <si>
-    <t>لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ</t>
-  </si>
-  <si>
-    <t>الحَمْدُ للهِ الَّذِي عَافَانِي فِي جَسَدِي، وَرَدَّ عَلَيَّ رُوحِي، وَأَذِنَ لِي بِذِكْرِهِ</t>
-  </si>
-  <si>
-    <t>الحَمْدُ للهِ الَّذِي أَحْيَانَا بَعْدَ مَا أَمَاتَنَا وَإِلَيْهِ النُّشُورُ</t>
-  </si>
-  <si>
-    <t>لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، سُبْحَانَ اللهِ، وَالحَمْدُ للهِ، وَلا إِلهَ إِلاَّ اللهُ وَاللهُ أَكْبَرُ، وَلا حَوْلَ وَلا قُوَّةَ إِلاَّ بِاللهِ العَلِيِّ العَظِيمِ رَبِّ اغْفِرْ لِي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اللّهُـمَّ ما أَصْبَـَحَ بي مِـنْ نِعْـمَةٍ أَوْ بِأَحَـدٍ مِـنْ خَلْـقِك، فَمِـنْكَ وَحْـدَكَ لا شَرِيكَ لَـك، فَلَـكَ الْحَمْـدُ وَلَـكَ الشُّكْـر  
-Allāhumma mā aṣbaha bī min ni`matin aw bi aḥadin min khalqik, fa minka waḥdaka lā sharīka lak, falaka ‘l-ḥamdu wa lakash-shukr  
-O Allah, whatever blessing has been received by me or anyone of Your creation is from You alone, You have no partner All praise is for you and thanks is to You   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ 
- Lā 'ilāha 'illallāhu waḥdahu la sharīka lahu lahul-mulku wa lahul-ḥamdu, wa huwa 'alā kulli shay'in qadīr  
-There is none worthy of worship but Allah alone, Who has no partner His is the dominion and to Him belongs all praise and He is able to do all things</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحَمْدُ للهِ الَّذِي عَافَانِي فِي جَسَدِي، وَرَدَّ عَلَيَّ رُوحِي، وَأَذِنَ لِي بِذِكْرِهِ
-  Al-ḥamdu lillāhil-ladhī `āfānī fī jasadī, wa radda `alayya rūḥī, wa 'adhina lī bidhikrihi  
-Praise is to Allah Who gave strength to my body and returned my soul to me and permitted me to remember Him  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحَمْدُ للهِ الَّذِي أَحْيَانَا بَعْدَ مَا أَمَاتَنَا وَإِلَيْهِ النُّشُورُ
-  Alḥamdu lillāhil-ladhī 'aḥyānā ba`da mā 'amātanā wa 'ilayhin-nushūr  
-Praise is to Allah Who gives us life after He has caused us to die and to Him is the return  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا إِلهَ إِلاَّ اللهُ وَحْدَهُ لا شَرِيكَ لَهُ، لَهُ المُلْكُ وَلَهُ الحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، سُبْحَانَ اللهِ، وَالحَمْدُ للهِ، وَلا إِلهَ إِلاَّ اللهُ وَاللهُ أَكْبَرُ، وَلا حَوْلَ وَلا قُوَّةَ إِلاَّ بِاللهِ العَلِيِّ العَظِيمِ رَبِّ اغْفِرْ لِي
-    Lā 'ilāha 'illallāhu waḥdahu la sharīka lahu, lahul-mulku wa lahul-ḥamdu, wa huwa 'alā kulli shay'in qadīr Subḥānallāhi, walḥamdu lillāhi, wa lā 'ilāha 'illallāhu, wallāhu 'akbar, wa lā ḥaula wa lā quwwata 'illā billāhil-`aliyyil-`aẓīm, rabbighfir lī    
-There is none worthy of worship but Allah alone, Who has no partner, His is the dominion and to Him belongs all praise, and He is able to do all things Glory is to Allah Praise is to Allah There is none worthy of worship but Allah Allah is the Most Great There is no might and no power except by Allah's leave the Exalted, the Mighty My Lord forgive me  </t>
-  </si>
-  <si>
-    <t>أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذَا الْيَوْمِ وَخَيْرَ مَا بَعْدَهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذَا الْيَوْمِ وَشَرِّ مَا بَعْدَهُ، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ بِكَ أَصْبَحْنَا، وَبِكَ أَمْسَيْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَنْتَ رَبِّي لَا إِلَٰهَ إِلَّا أَنْتَ، خَلَقْتَنِي وَأَنَا عَبْدُكَ، وَأَنَا عَلَى عَهْدِكَ وَوَعْدِكَ مَا اسْتَطَعْتُ، أَعُوذُ بِكَ مِنْ شَرِّ مَا صَنَعْتُ، أَبُوءُ لَكَ بِنِعْمَتِكَ عَلَيَّ وَأَبُوءُ بِذَنْبِي، فَاغْفِرْ لِي فَإِنَّهُ لَا يَغْفِرُ الذُّنُوبَ إِلَّا أَنْتَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَصْبَحْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ مَا أَصْبَحَ بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ</t>
-  </si>
-  <si>
-    <t>حَسْبِيَ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ عَلَيْهِ تَوَكَّلْتُ وَهُوَ رَبُّ الْعَرْشِ الْعَظِيمِ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ عَالِمَ الْغَيْبِ وَالشَّهَادَةِ فَاطِرَ السَّمَاوَاتِ وَالْأَرْضِ رَبَّ كُلِّ شَيْءٍ وَمَلِيكَهُ، أَشْهَدُ أَنْ لَا إِلَٰهَ إِلَّا أَنْتَ، أَعُوذُ بِكَ مِنْ شَرِّ نَفْسِي وَمِنْ شَرِّ الشَّيْطَانِ وَشِرْكِهِ، وَأَنْ أَقْتَرِفَ عَلَى نَفْسِي سُوءًا أَوْ أَجُرَّهُ إِلَى مُسْلِمٍ</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الَّذِي لَا يَضُرُّ مَعَ اسْمِهِ شَيْءٌ فِي الْأَرْضِ وَلَا فِي السَّمَاءِ وَهُوَ السَّمِيعُ الْعَلِيمُ</t>
-  </si>
-  <si>
-    <t>رَضِيتُ بِاللَّهِ رَبًّا، وَبِالْإِسْلَامِ دِينًا، وَبِمُحَمَّدٍ ﷺ نَبِيًّا</t>
-  </si>
-  <si>
-    <t>أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذَا الْيَوْمِ فَتْحَهُ، وَنَصْرَهُ، وَنُورَهُ، وَبَرَكَتَهُ، وَهُدَاهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهِ وَشَرِّ مَا بَعْدَهُ</t>
-  </si>
-  <si>
-    <t>أَصْبَحْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ</t>
-  </si>
-  <si>
-    <t>سُبْحـانَ اللهِ وَبِحَمْـدِهِ</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ</t>
-  </si>
-  <si>
-    <t>سُبْحَانَ اللَّهِ وَبِحَمْدِهِ عَدَدَ خَلْقِهِ، وَرِضَا نَفْسِهِ، وَزِنَةَ عَرْشِهِ، وَمِدَادَ كَلِمَاتِهِ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ عِلْمًا نَافِعًا، وَرِزْقًا طَيِّبًا، وَعَمَلًا مُتَقَبَّلًا</t>
-  </si>
-  <si>
-    <t>أَعُوذُ بِكَلِمَاتِ اللَّهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ صَلِّ وَسَلِّمْ وَبَارِكْ عَلَى نَبِيِّنَا مُحَمَّدٍ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنَّا نَعُوذُ بِكَ مِنْ أَنْ نُشْرِكَ بِكَ شَيْئًا نَعْلَمُهُ، وَنَسْتَغْفِرُكَ لِمَا لَا نَعْلَمُهُ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْهَمِّ وَالْحَزَنِ، وَأَعُوذُ بِكَ مِنَ الْعَجْزِ وَالْكَسَلِ، وَأَعُوذُ بِكَ مِنَ الْجُبْنِ وَالْبُخْلِ، وَأَعُوذُ بِكَ مِنْ غَلَبَةِ الدَّيْنِ وَقَهْرِ الرِّجَالِ</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ هُوَ اللَّهُ أَحَدٌ ﴿١﴾ اللَّهُ الصَّمَدُ ﴿٢﴾ لَمْ يَلِدْ وَلَمْ يُولَدْ ﴿٣﴾ وَلَمْ يَكُن لَّهُ كُفُوًا أَحَدٌ ﴿٤﴾</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ أَعُوذُ بِرَبِّ الْفَلَقِ ﴿١﴾ مِن شَرِّ مَا خَلَقَ ﴿٢﴾ وَمِن شَرِّ غَاسِقٍ إِذَا وَقَبَ ﴿٣﴾ وَمِن شَرِّ النَّفَّاثَاتِ فِي الْعُقَدِ ﴿٤﴾ وَمِن شَرِّ حَاسِدٍ إِذَا حَسَدَ ﴿٥﴾</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ أَعُوذُ بِرَبِّ النَّاسِ ﴿١﴾ مَلِكِ النَّاسِ ﴿٢﴾ إِلَٰهِ النَّاسِ ﴿٣﴾ مِن شَرِّ الْوَسْوَاسِ الْخَنَّاسِ ﴿٤﴾ الَّذِي يُوَسْوِسُ فِي صُدُورِ النَّاسِ ﴿٥﴾ مِنَ الْجِنَّةِ وَالنَّاسِ ﴿٦﴾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
- اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ.
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>الخطوات العملية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: تقديم الرجل اليمنى عند الدخول
 </t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي، اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي، وأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَ مِنْ تَحْتِي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
-اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ </t>
-  </si>
-  <si>
-    <t>أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذِهِ اللَّيْلَةِ وَخَيْرَ مَا بَعْدَهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذِهِ اللَّيْلَةِ وَشَرِّ مَا بَعْدَهَا، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ بِكَ أَمْسَيْنَا، وَبِكَ أَصْبَحْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَمْسَيْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ مَا أَمْسَى بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ عَافِنِي فِي بَدَنِي، اللَّهُمَّ عَافِنِي فِي سَمْعِي، اللَّهُمَّ عَافِنِي فِي بَصَرِي، لَا إِلَٰهَ إِلَّا أَنْتَ اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْكُفْرِ وَالْفَقْرِ، وَأَعُوذُ بِكَ مِنْ عَذَابِ الْقَبْرِ، لَا إِلَٰهَ إِلَّا أَنْتَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي ووأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَمِنْ تَحْتِي</t>
-  </si>
-  <si>
-    <t>بِسـمِ اللهِ الذي لا يَضُـرُّ مَعَ اسمِـهِ شَيءٌ في الأرْضِ وَلا في السّمـاءِ وَهـوَ السّمـيعُ العَلـيم</t>
-  </si>
-  <si>
-    <t>أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذِهِ اللَّيْلَةِ فَتْحَهَا، وَنَصْرَهَا، وَنُورَهَا، وَبَرَكَتَهَا، وَهُدَاهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهَا وَشَرِّ مَا بَعْدَهَا</t>
-  </si>
-  <si>
-    <t>أَمْسَيْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ</t>
-  </si>
-  <si>
-    <t>أَسْتَغْفِرُ اللَّهَ وَأَتُوبُ إِلَيْهِ</t>
-  </si>
-  <si>
-    <t>سُبْحـانَ اللهِ وَبِحَمْـدِهِ
-Subḥānal-lāhi wa-bi-ḥamdih
-Glory is to Allah and praise is to Him</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ
-Lā ilāha illallāhu waḥdahu lā sharīka lah, lahul-mulku wa-lahul-ḥamd, wa-huwa ‘alā kulli shay’in qadīr
-None has the right to be worshipped except Allah, alone, without partner, to Him belongs all sovereignty and praise, and He is over all things Omnipotent</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ عِلْمًا نَافِعًا، وَرِزْقًا طَيِّبًا، وَعَمَلًا مُتَقَبَّلًا
-Allāhumma innī as'aluka ‘ilman nāfi‘ā, wa-rizqan ṭayyibā, wa-‘amalan mutaqabbalā
-O Allah, I ask You for knowledge that is of benefit, a good provision, and a deed that will be accepted</t>
-  </si>
-  <si>
-    <t>أَسْتَغْفِرُ اللَّهَ وَأَتُوبُ إِلَيْهِ
-Astaghfiru-Llāha wa-atūbu ilayh
-I seek Allah's forgiveness and I turn in repentance to Him</t>
-  </si>
-  <si>
-    <t>أَعُوذُ بِكَلِمَاتِ اللَّهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ
-A‘ūdhu bi-kalimātil-lāhit-tāmmāti min sharri mā khalaq
-I seek refuge in the Perfect Words of Allah from the evil of what He has created</t>
-  </si>
-  <si>
-    <t>أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
-اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ 
-A‘ūdhu billāhi minash-shayṭānir-rajīm
-Allāhu lā ilāha illā huwal-ḥayyul-qayyūm lā ta'khudhuhu sinatun wa lā nawm lahu mā fis-samāwāti wa mā fil-arḍ man dhal-ladhī yashfa‘u ‘indahu illā bi-idhnihi ya‘lamu mā bayna aydīhim wa mā khalfahum wa lā yuḥīṭūna bi-shay'im-min ‘ilmihi illā bimā shā' wasi‘a kursiyyuhus-samāwāti wal-arḍ wa lā ya'ūduhu ḥifẓuhumā wa huwal-‘aliyyul-‘aẓīm
-I seek refuge in Allah from Satan the outcast
-Allah! There is no deity except Him the Ever-Living the Sustainer of all existence Neither drowsiness overtakes Him nor sleep To Him belongs whatever is in the heavens and whatever is on the earth Who is it that can intercede with Him except by His permission? He knows what is before them and what will be after them and they encompass not a thing of His knowledge except for what He wills His Kursi extends over the heavens and the earth and their preservation tires Him not And He is the Most High the Most Great</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ هُوَ اللَّهُ أَحَدٌ ﴿١﴾ اللَّهُ الصَّمَدُ ﴿٢﴾ لَمْ يَلِدْ وَلَمْ يُولَدْ ﴿٣﴾ وَلَمْ يَكُن لَّهُ كُفُوًا أَحَدٌ ﴿٤﴾
-Bismillāhir-raḥmānir-raḥīm
-Qul huwal-Lāhu aḥad Allāhuṣ-ṣamad Lam yalid wa lam yūlad Wa lam yakul-lahu kufuwan aḥad
-In the name of Allah the Beneficent the Merciful
-Say "He is Allah [who is] One Allah the Eternal Refuge He neither begets nor is born Nor is there to Him any equivalent"</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ أَعُوذُ بِرَبِّ الْفَلَقِ ﴿١﴾ مِن شَرِّ مَا خَلَقَ ﴿٢﴾ وَمِن شَرِّ غَاسِقٍ إِذَا وَقَبَ ﴿٣﴾ وَمِن شَرِّ النَّفَّاثَاتِ فِي الْعُقَدِ ﴿٤﴾ وَمِن شَرِّ حَاسِدٍ إِذَا حَسَدَ ﴿٥﴾
-Bismillāhir-raḥmānir-raḥīm
-Qul a‘ūdhu bi-rabbil-falaq Min sharri mā khalaq Wa min sharri ghāsiqin idhā waqab Wa min sharrin-naffāthāti fil-‘uqad Wa min sharri ḥāsidin idhā ḥasad
-In the name of Allah the Beneficent the Merciful
-Say "I seek refuge in the Lord of daybreak From the evil of that which He created And from the evil of darkness when it settles And from the evil of the blowers in knots And from the evil of an envier when he envies"</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ أَعُوذُ بِرَبِّ النَّاسِ ﴿١﴾ مَلِكِ النَّاسِ ﴿٢﴾ إِلَٰهِ النَّاسِ ﴿٣﴾ مِن شَرِّ الْوَسْوَاسِ الْخَنَّاسِ ﴿٤﴾ الَّذِي يُوَسْوِسُ فِي صُدُورِ النَّاسِ ﴿٥﴾ مِنَ الْجِنَّةِ وَالنَّاسِ ﴿٦﴾
-Bismillāhir-raḥmānir-raḥīm
-Qul a‘ūdhu bi-rabbin-nās Malikin-nās Ilāhin-nās Min sharril-waswāsil-khannās Alladhī yuwaswisu fī ṣudūrin-nās Minal-jinnati wan-nās
-In the name of Allah the Beneficent the Merciful
-Say "I seek refuge in the Lord of mankind The Sovereign of mankind The God of mankind From the evil of the retreating whisperer - Who whispers [evil] into the breasts of mankind - From among the jinn and mankind"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذِهِ اللَّيْلَةِ وَخَيْرَ مَا بَعْدَهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذِهِ اللَّيْلَةِ وَشَرِّ مَا بَعْدَهَا، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ
-Amsaynā wa-amsal-mulku lillāhi wal-ḥamdu lillāh lā ilāha illallāhu waḥdahu lā sharīka lah lahul-mulku wa-lahul-ḥamd wa-huwa ‘alā kulli shay’in qadīr Rabbi as’aluka khayra mā fī hādhihil-laylati wa-khayra mā ba‘dahā wa-a‘ūdhu bika min sharri mā fī hādhihil-laylati wa-sharri mā ba‘dahā Rabbi a‘ūdhu bika minal-kasali wa-sū’il-kibar Rabbi a‘ūdhu bika min ‘adhābin fin-nāri wa-‘adhābin fil-qabr
-We have reached the evening and at this very time unto Allah belongs all sovereignty and all praise is for Allah None has the right to be worshipped except Allah alone without partner to Him belongs all sovereignty and praise and He is over all things Omnipotent My Lord I ask You for the good of this night and the good of what follows it and I take refuge in You from the evil of this night and the evil of what follows it My Lord I take refuge in You from laziness and senility My Lord I take refuge in You from torment in the Fire and punishment in the grave
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>دعاء دخول المسجد</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: «بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ»
 </t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ بِكَ أَمْسَيْنَا، وَبِكَ أَصْبَحْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ
-Allāhumma bika amsaynā wa-bika aṣbaḥnā wa-bika naḥyā wa-bika namūtu wa-ilaykal-maṣīr
-O Allah by Your leave we have reached the evening and by Your leave we have reached the morning by Your leave we live and by Your leave we die and unto You is our return</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَنْتَ رَبِّي لَا إِلَٰهَ إِلَّا أَنْتَ، خَلَقْتَنِي وَأَنَا عَبْدُكَ، وَأَنَا عَلَى عَهْدِكَ وَوَعْدِكَ مَا اسْتَطَعْتُ، أَعُوذُ بِكَ مِنْ شَرِّ مَا صَنَعْتُ، أَبُوءُ لَكَ بِنِعْمَتِكَ عَلَيَّ وَأَبُوءُ بِذَنْبِي، فَاغْفِرْ لِي فَإِنَّهُ لَا يَغْفِرُ الذُّنُوبَ إِلَّا أَنْتَ
-Allāhumma anta rabbī lā ilāha illā ant khalaqtanī wa-anā ‘abduk wa-anā ‘alā ‘ahdika wa-wa‘dika mas-taṭa‘t a‘ūdhu bika min sharri mā ṣana‘t abū’u laka bi-ni‘matika ‘alayya wa-abū’u bi-dhanbī fagh-fir lī fa-innahu lā yaghfirudh-dhunūba illā ant
-O Allah You are my Lord there is no deity except You You created me and I am Your servant and I am faithful to my covenant and my promise to You as much as I am able I seek refuge in You from the evil of what I have done I acknowledge before You Your favor upon me and I acknowledge my sin so forgive me for indeed no one forgets/forgives sins except You</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَمْسَيْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ
-Allāhumma innī amsaytu ush-hiduka wa-ush-hidu ḥamalata ‘arshika wa-malā'ikataka wa-jamī‘a khalqika annaka anta-Llāhu lā ilāha illā anta waḥdaka lā sharīka laka wa-anna Muḥhammadan ‘abduka wa-rasūluk
-O Allah I have entered the evening and I call upon You the bearers of Your Throne Your angels and all of Your creation to witness that You are Allah there is no deity except You alone without partner and that Muhammad is Your servant and Your Messenger</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ مَا أَمْسَى بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ
-Allāhumma mā amsā bī min ni‘matin aw bi-aḥadin min khalqika faminka waḥdaka lā sharīka laka falakal-ḥamdu wa-lakash-shukr
-O Allah whatever blessing has befallen me or any of Your creation this evening is from You alone without partner so for You is all praise and unto You is all thanks</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ عَافِنِي فِي بَدَنِي، اللَّهُمَّ عَافِنِي فِي سَمْعِي، اللَّهُمَّ عَافِنِي فِي بَصَرِي، لَا إِلَٰهَ إِلَّا أَنْتَ اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْكُفْرِ وَالْفَقْرِ، وَأَعُوذُ بِكَ مِنْ عَذَابِ الْقَبْرِ، لَا إِلَٰهَ إِلَّا أَنْتَ
-Allāhumma ‘āfinī fī badanī Allāhumma ‘āfinī fī sam‘ī Allāhumma ‘āfinī fī baṣarī lā ilāha illā ant Allāhumma innī a‘ūdhu bika minal-kufri wal-faqr wa-a‘ūdhu bika min ‘adhābil-qabr lā ilāha illā ant
-O Allah grant me health in my body O Allah grant me health in my hearing O Allah grant me health in my sight There is no deity except You O Allah I seek refuge in You from disbelief and poverty and I seek refuge in You from the punishment of the grave There is no deity except You</t>
-  </si>
-  <si>
-    <t>حَسْبِيَ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ عَلَيْهِ تَوَكَّلْتُ وَهُوَ رَبُّ الْعَرْشِ الْعَظِيمِ
-Ḥasbiyal-Lāhu lā ilāha illā huwa ‘alayhi tawakkaltu wa-huwa rabbul-‘arshil-‘aẓīm
-Allah is sufficient for me There is no deity except Him As for Him I have put my trust and He is the Lord of the Mighty Throne</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي ووأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَمِنْ تَحْتِي
-Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fi 'd-dunyā wa 'l-ākhirah Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fī dīnī wa dunyāya wa ahlī wa mālī Allāhumma-stur ‘awrātī wa āmin raw‘ātī Allāhumma-ḥfaẓnī min bayni yadayya wa min khalfī wa ‘an yamīnī wa ‘an shimālī wa min fawqī wa a‘ūdhu bi-‘aẓamatika an ughtāla min taḥtī
-O Allah I ask You for pardon and well-being in this world and the next O Allah I ask You for pardon and well-being in my religious and worldly affairs and in my family and my wealth O Allah conceal my faults and keep me safe from the things which I fear O Allah guard me from the front and from behind and from my right and from my left and from above me I seek refuge in Your greatness from being struck from beneath me</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ عَالِمَ الْغَيْبِ وَالشَّهَادَةِ فَاطِرَ السَّمَاوَاتِ وَالْأَرْضِ رَبَّ كُلِّ شَيْءٍ وَمَلِيكَهُ، أَشْهَدُ أَنْ لَا إِلَٰهَ إِلَّا أَنْتَ، أَعُوذُ بِكَ مِنْ شَرِّ نَفْسِي وَمِنْ شَرِّ الشَّيْطَانِ وَشِرْكِهِ، وَأَنْ أَقْتَرِفَ عَلَى نَفْسِي سُوءًا أَوْ أَجُرَّهُ إِلَى مُسْلِمٍ
-Allāhumma ‘ālimal-ghaybi wash-shahādah fāṭiras-samāwāti wal-arḍ rabba kulli shay’in wa-malīkah ash-hadu an lā ilāha illā ant a‘ūdhu bika min sharri nafsī wa-min sharrish-shayṭāni wa-shirkih wa-an aqtarifa ‘alā nafsī sū’an aw ajurrahu ilā muslim
-O Allah Knower of the unseen and the evident Creator of the heavens and the earth Lord of everything and its Possessor I bear witness that there is no deity except You I seek refuge in You from the evil of my soul and from the evil of Satan and his helper/ascribing partners to Allah and from committing any evil against myself or dragging it upon another Muslim</t>
-  </si>
-  <si>
-    <t>بِسـمِ اللهِ الذي لا يَضُـرُّ مَعَ اسمِـهِ شَيءٌ في الأرْضِ وَلا في السّمـاءِ وَهـوَ السّمـيعُ العَلـيم
-Bismillāhil-ladhī lā yaḍurru ma‘as-mihi shay’un fil-arḍi wa-lā fis-samā’i wa-huwas-samī‘ul-‘alīm
-In the name of Allah with Whose name nothing can cause harm on earth or in the heaven and He is the All-Hearing the All-Knowing</t>
-  </si>
-  <si>
-    <t>رَضِيتُ بِاللَّهِ رَبًّا، وَبِالْإِسْلَامِ دِينًا، وَبِمُحَمَّدٍ ﷺ نَبِيًّا
-Raḍītu billāhi rabban wa-bil-islāmi dīnan wa-bi-Muḥammadin ṣallallāhu ‘alayhi wa-sallama nabiyyā
-I am pleased with Allah as my Lord with Islam as my religion and with Muhammad (peace and blessings of Allah be upon him) as my Prophet</t>
-  </si>
-  <si>
-    <t>يَا حَيُّ يَا قَيُّومُ بِرَحْمَتِكَ أَسْتَغِيثُ، أَصْلِحْ لِي شَأْنِي كُلَّهُ، وَلَا تَكِلْنِي إِلَى نَفْسِي طَرْفَةَ عَيْنٍ
-Yā ḥayyu yā qayyūmu bi-raḥmatika astaghīth aṣliḥ lī sha’nī kullahu wa-lā takilnī ilā nafsī ṭarfata ‘ayn
-O Ever Living One O Sustainer of all by Your mercy I seek assistance rectify for me all of my affairs and do not leave me to myself even for the blink of an eye</t>
-  </si>
-  <si>
-    <t>أَمْسَيْنَا وَأَمْسَى الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذِهِ اللَّيْلَةِ فَتْحَهَا، وَنَصْرَهَا، وَنُورَهَا، وَبَرَكَتَهَا، وَهُدَاهَا، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهَا وَشَرِّ مَا بَعْدَهَا
-Amsaynā wa-amsal-mulku lillāhi rabbil-‘ālamīn Allāhumma innī as’aluka khayra hādhihil-laylah: fatḥahā wa-naṣrahā wa-nūrahā wa-barakatahā wa-hudāhā wa-a‘ūdhu bika min sharri mā fīhā wa-sharri mā ba‘dahā
-We have reached the evening and at this very time all sovereignty belongs to Allah Lord of the worlds O Allah I ask You for the good of this night its triumphs its victories its light its blessings and its guidance and I take refuge in You from the evil of this night and the evil that follows it</t>
-  </si>
-  <si>
-    <t>أَمْسَيْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ
-Amsaynā ‘alā fiṭratil-islām wa-‘alā kalimatil-ikhlāṣ wa-‘alā dīni nabiyyinā Muḥammadin ṣallallāhu ‘alayhi wa-sallam wa-‘alā millati abīnā Ibrāhīma ḥanīfan musliman wa-mā kāna minal-mushrikīn
-We have reached the evening upon the natural religion of Islam and the word of sincere devotion and the religion of our Prophet Muhammad (peace and blessings of Allah be upon him) and the creed of our father Ibrahim a man of pure faith and a Muslim and he was not of those who associate partners with Allah</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ
-Lā ilāha illallāhu waḥdahu lā sharīka lah lahul-mulku wa-lahul-ḥamd wa-huwa ‘alā kulli shay’in qadīr
-None has the right to be worshipped except Allah alone without partner to Him belongs all sovereignty and praise and He is over all things Omnipotent</t>
-  </si>
-  <si>
-    <t>سُبْحَانَ اللَّهِ وَبِحَمْدِهِ عَدَدَ خَلْقِهِ، وَرِضَا نَفْسِهِ، وَزِنَةَ عَرْشِهِ، وَمِدَادَ كَلِمَاتِهِ
-Subḥānal-lāhi wa-bi-ḥamdih ‘adada khalqih wa-riḍā nafsih wa-zinata ‘arshih wa-midāda kalimātih
-Glory is to Allah and praise is to Him by the number of His creation and His pleasure and by the weight of His Throne and the ink of His words</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَسْأَلُكَ عِلْمًا نَافِعًا، وَرِزْقًا طَيِّبًا، وَعَمَلًا مُتَقَبَّلًا
-Allāhumma innī as'aluka ‘ilman nāfi‘ā wa-rizqan ṭayyibā wa-‘amalan mutaqabbalā
-O Allah I ask You for knowledge that is of benefit a good provision and a deed that will be accepted</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ صَلِّ وَسَلِّمْ وَبَارِكْ عَلَى نَبِيِّنَا مُحَمَّدٍ
-Allāhumma ṣalli wa-sallim wa-bārik ‘alā nabiyyinā Muḥammad
-O Allah send Your praise peace and blessings upon our Prophet Muhammad</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنَّا نَعُوذُ بِكَ مِنْ أَنْ نُشْرِكَ بِكَ شَيْئًا نَعْلَمُهُ، وَنَسْتَغْفِرُكَ لِمَا لَا نَعْلَمُهُ
-Allāhumma innā na‘ūdhu bika min an nushrika bika shay’an na‘lamuh wa-nastaghfiruka limā lā na‘lamuh
-O Allah we seek refuge in You from ascribing anything to You knowingly and we seek Your forgiveness for that which we do not know</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْهَمِّ وَالْحَزَنِ، وَأَعُوذُ بِكَ مِنَ الْعَجْزِ وَالْكَسَلِ، وَأَعُوذُ بِكَ مِنَ الْجُبْنِ وَالْبُخْلِ، وَأَعُوذُ بِكَ مِنْ غَلَبَةِ الدَّيْنِ وَقَهْرِ الرِّجَالِ
-Allāhumma innī a‘ūdhu bika minal-hammi wal-ḥazan wa-a‘ūdhu bika minal-‘ajzi wal-kasal wa-a‘ūdhu bika minal-jubni wal-bukhl wa-a‘ūdhu bika min ghalabatid-dayni wa-qahrir-rijāl
-O Allah I seek refuge in You from anxiety and sorrow and I seek refuge in You from inability and laziness and I seek refuge in You from cowardice and miserliness and I seek refuge in You from the burden of debt and from being overpowered by men</t>
-  </si>
-  <si>
-    <t>أَسْتَغْفِرُ اللَّهَ الْعَظِيمَ الَّذِي لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ وَأَتُوبُ إِلَيْهِ
-Astaghfiru-Llāhal-‘aẓīmal-ladhī lā ilāha illā huwal-ḥayyul-qayyūmu wa-atūbu ilayh
-I seek the forgiveness of Allah the Mighty Whom there is no deity except Him the Ever-Living the Sustainer of all existence and I turn to Him in repentance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أَعُوذُ بِاللَّهِ مِنَ الشَّيْطَانِ الرَّجِيمِ
-اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ الْحَيُّ الْقَيُّومُ ۚ لَا تَأْخُذُهُ سِنَةٌ وَلَا نَوْمٌ ۚ لَّهُ مَا فِي السَّمَاوَاتِ وَمَا فِي الْأَرْضِ ۗ مَن ذَا الَّذِي يَشْفَعُ عِندَهُ إِلَّا بِإِذْنِهِ ۚ يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ ۖ وَلَا يُحِيطُونَ بِشَيْءٍ مِّنْ عِلْمِهِ إِلَّا بِمَا شَاءَ ۚ وَسِعَ كُرْسِيُّهُ السَّمَاوَاتِ وَالْأَرْضَ ۖ وَلَا يَئُودُهُ حِفْظُهُمَا ۚ وَهُوَ الْعَلِيُّ الْعَظِيمُ
-A`ūdhu billāhi min ash-shaytāni 'r-rajīm
- Allāhu lā ilāha illā huwal-ḥayyul-qayyūm lā ta'khudhuhu sinatun wa lā nawm lahu mā fis-samāwāti wa mā fil-arḍ man dhal-ladhī yashfa‘u ‘indahu illā bi-idhnihi ya‘lamu mā bayna aydīhim wa mā khalfahum wa lā yuḥīṭūna bi-shay'im-min ‘ilmihi illā bimā shā' wasi‘a kursiyyuhus-samāwāti wal-arḍ wa lā ya'ūduhu ḥifẓuhumā wa huwal-‘aliyyul-‘aẓīm
-O Allah! There is no deity except Him the Ever-Living the Sustainer of all existence Neither drowsiness overtakes Him nor sleep To Him belongs whatever is in the heavens and whatever is on the earth Who is it that can intercede with Him except by His permission? He knows what is before them and what will be after them and they encompass not a thing of His knowledge except for what He wills His Kursi extends over the heavens and the earth and their preservation tires Him not And He is the Most High the Most Great </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ هُوَ اللَّهُ أَحَدٌ ﴿١﴾ اللَّهُ الصَّمَدُ ﴿٢﴾ لَمْ يَلِدْ وَلَمْ يُولَدْ ﴿٣﴾ وَلَمْ يَكُن لَّهُ كُفُوًا أَحَدٌ ﴿٤﴾
-Bismillāhir-raḥmānir-raḥīm
-Qul huwal-Lāhu aḥad Allāhuṣ-ṣamad Lam yalid wa lam yūlad Wa lam yakul-lahu kufuwan aḥad 
-In the name of Allah the Beneficent the Merciful
-Say "He is Allah [who is] One Allah the Eternal Refuge He neither begets nor is born Nor is there to Him any equivalent
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>عند رؤية الكعبة لأول مرة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: «اللَّهُمَّ زِدْ هَٰذَا الْبَيْتَ تَشْرِيفًا وَتَعْظِيمًا وَتَكْرِيمًا وَمَهَابَةً»</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> الخطوة الثالثة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: الطواف حول الكعبة (7 أشواط)
 </t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ
-قُلْ أَعُوذُ بِرَبِّ الْفَلَقِ ﴿١﴾ مِن شَرِّ مَا خَلَقَ ﴿٢﴾ وَمِن شَرِّ غَاسِقٍ إِذَا وَقَبَ ﴿٣﴾ وَمِن شَرِّ النَّفَّاثَاتِ فِي الْعُقَدِ ﴿٤﴾ وَمِن شَرِّ حَاسِدٍ إِذَا حَسَدَ ﴿٥﴾
-Bismillāhir-raḥmānir-raḥīm
-Qul a‘ūdhu bi-rabbil-falaq Min sharri mā khalaq Wa min sharri ghāsiqin idhā waqab Wa min sharrin-naffāthāti fil-‘uqad Wa min sharri ḥāsidin idhā ḥasad
-In the name of Allah the Beneficent the Merciful
-Say I seek refuge in the Lord of daybreak From the evil of that which He created And from the evil of darkness when it settles And from the evil of the blowers in knots And from the evil of an envier when he envies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ وَالْحَمْدُ لِلَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، رَبِّ أَسْأَلُكَ خَيْرَ مَا فِي هَٰذَا الْيَوْمِ وَخَيْرَ مَا بَعْدَهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِي هَٰذَا الْيَوْمِ وَشَرِّ مَا بَعْدَهُ، رَبِّ أَعُوذُ بِكَ مِنَ الْكَسَلِ وَسُوءِ الْكِبَرِ، رَبِّ أَعُوذُ بِكَ مِنْ عَذَابٍ فِي النَّارِ وَعَذَابٍ فِي الْقَبْرِ
-Aṣbaḥnā wa-aṣbaḥal-mulku lillāhi wal-ḥamdu lillāh lā ilāha illallāhu waḥdahu lā sharīka lah lahul-mulku wa-lahul-ḥamd wa-huwa ‘alā kulli shay’in qadīr Rabbi as’aluka khayra mā fī hādhal-yawmi wa-khayra mā ba‘dah wa-a‘ūdhu bika min sharri mā fī hādhal-yawmi wa-sharri mā ba‘dah Rabbi a‘ūdhu bika minal-kasali wa-sū’il-kibar Rabbi a‘ūdhu bika min ‘adhābin fin-nāri wa-‘adhābin fil-qabr
-We have reached the morning and at this very time unto Allah belongs all sovereignty and all praise is for Allah None has the right to be worshipped except Allah alone without partner to Him belongs all sovereignty and praise and He is over all things Omnipotent My Lord I ask You for the good of this day and the good of what follows it and I take refuge in You from the evil of this day and the evil of what follows it My Lord I take refuge in You from laziness and senility My Lord I take refuge in You from torment in the Fire and punishment in the grave </t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ بِكَ أَصْبَحْنَا، وَبِكَ أَمْسَيْنَا، وَبِكَ نَحْيَا وَبِكَ نَمُوتُ، وَإِلَيْكَ النُّشُورُ
-Allāhumma bika aṣbaḥnā wa-bika amsaynā wa-bika naḥyā wa-bika namūtu wa-ilaykan-nushūr
-O Allah by Your leave we have reached the morning and by Your leave we have reached the evening by Your leave we live and by Your leave we die and unto You is our resurrection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اللَّهُمَّ أَنْتَ رَبِّي لَا إِلَٰهَ إِلَّا أَنْتَ، خَلَقْتَنِي وَأَنَا عَبْدُكَ، وَأَنَا عَلَى عَهْدِكَ وَوَعْدِكَ مَا اسْتَطَعْتُ، أَعُوذُ بِكَ مِنْ شَرِّ مَا صَنَعْتُ، أَبُوءُ لَكَ بِنِعْمَتِكَ عَلَيَّ وَأَبُوءُ بِذَنْبِي، فَاغْفِرْ لِي فَإِنَّهُ لَا يَغْفِرُ الذُّنُوبَ إِلَّا أَنْتَ
-Allāhumma anta rabbī lā ilāha illā ant khalaqtanī wa-anā ‘abduk wa-anā ‘alā ‘ahdika wa-wa‘dika mas-taṭa‘t a‘ūdhu bika min sharri mā ṣana‘t abū’u laka bi-ni‘matika ‘alayya wa-abū’u bi-dhanbī fagh-fir lī fa-innahu lā yaghfirudh-dhunūba illā ant 
-O Allah You are my Lord there is no deity except You You created me and I am Your servant and I am faithful to my covenant and my promise to You as much as I am able I seek refuge in You from the evil of what I have done I acknowledge before You Your favor upon me and I acknowledge my sin so forgive me for indeed no one forgives sins except You
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>الخطوات العملية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 
+🕋 جعل الكعبة عن يسارك.
+🕋 استقبال الحجر الأسود لبدء الشوط
+🕋 عند محاذاة الحجر الأسود (بداية كل شوط): تُشير بيدك قائلاً: «بِسْمِ اللَّهِ وَاللَّهُ أَكْبَرُ»
+🕋 بين الركن اليماني والحجر الأسود (في كل شوط): «رَبَّنَا آتِنَا فِي الدُّنْيَا حَسَنَةً وَفِي الْآخِرَةِ حَسَنَةً وَقِنَا عَذَابَ النَّارِ»
+🕋 أثناء بقية الطواف:
+• ليس هناك دعاء محدد لكل شوط
+• ادعُ بما تشاء من الاستغفار، والذكر، وقراءة القرآن</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> الخطوة الخامسة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: السعي بين الصفا والمروة (7 أشواط)
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">اللَّهُمَّ إِنِّي أَصْبَحْتُ أُشْهِدُكَ، وَأُشْهِدُ حَمَلَةَ عَرْشِكَ، وَمَلَائِكَتَكَ وَجَمِيعَ خَلْقِكَ، أَنَّكَ أَنْتَ اللَّهُ لَا إِلَٰهَ إِلَّا أَنْتَ وَحْدَهُ لَا شَرِيكَ لَهُ، وَأَنَّ مُحَمَّدًا عَبْدُكَ وَرَسُولُكَ
-Allāhumma innī aṣbaḥtu ush-hiduka wa-ush-hidu ḥamalata ‘arshika wa-malā'ikataka wa-jamī‘a khalqika annaka anta-Llāhu lā ilāha illā anta waḥdaka lā sharīka laka wa-anna Muḥhammadan ‘abduka wa-rasūluk 
-O Allah I have entered a new morning and I call upon You the bearers of Your Throne Your angels and all of Your creation to witness that You are Allah there is no deity except You alone without partner and that Muhammad is Your servant and Your Messenger  </t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ مَا أَصْبَحَ بِي مِنْ نِعْمَةٍ أَوْ بِأَحَدٍ مِنْ خَلْقِكَ، فَمِنْكَ وَحْدَكَ لَا شَرِيكَ لَكَ، فَلَكَ الْحَمْدُ وَلَكَ الشُّكْرُ
- Allāhumma mā aṣbaḥa bī min ni‘matin aw bi-aḥadin min khalqika faminka waḥdaka lā sharīka laka falakal-ḥamdu wa-lakash-shukr 
-O Allah whatever blessing has befallen me or any of Your creation this morning is from You alone without partner so for You is all praise and unto You is all thanks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اللَّهُمَّ عَافِنِي فِي بَدَنِي، اللَّهُمَّ عَافِنِي فِي سَمْعِي، اللَّهُمَّ عَافِنِي فِي بَصَرِي، لَا إِلَٰهَ إِلَّا أَنْتَ
-اللَّهُمَّ إِنِّي أَعُوذُ بِكَ مِنَ الْكُفْرِ وَالْفَقْرِ، وَأَعُوذُ بِكَ مِنْ عَذَابِ الْقَبْرِ، لَا إِلَٰهَ إِلَّا أَنْتَ
-Allāhumma ‘āfinī fī badanī Allāhumma ‘āfinī fī sam‘ī Allāhumma ‘āfinī fī baṣarī lā ilāha illā ant Allāhumma innī a‘ūdhu bika minal-kufri wal-faqr wa-a‘ūdhu bika min ‘adhābil-qabr lā ilāha illā ant 
-O Allah grant me health in my body O Allah grant me health in my hearing O Allah grant me health in my sight There is no deity except You O Allah I seek refuge in You from disbelief and poverty and I seek refuge in You from the punishment of the grave There is no deity except You  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">حَسْبِيَ اللَّهُ لَا إِلَٰهَ إِلَّا هُوَ عَلَيْهِ تَوَكَّلْتُ وَهُوَ رَبُّ الْعَرْشِ الْعَظِيمِ
-Ḥasbiyal-Lāhu lā ilāha illā huwa ‘alayhi tawakkaltu wa-huwa rabbul-‘arshil-‘aẓīm 
-Allah is sufficient for me There is no deity except Him As for Him I have put my trust and He is the Lord of the Mighty Throne </t>
-  </si>
-  <si>
-    <t xml:space="preserve">اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي الدُّنْيَا وَالْآخِرَةِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَفْوَ وَالْعَافِيَةَ فِي دِينِي وَدُنْيَايَ وَأَهْلِي وَمَالِي، اللَّهُمَّ اسْتُرْ عَوْرَاتِي وَآمِنْ رَوْعَاتِي، اللَّهُمَّ احْفَظْنِي مِنْ بَيْنِ يَدَيَّ وَمِنْ خَلْفِي وَعَنْ يَمِينِي وَعَنْ شِمَالِي وَمِنْ فَوْقِي، وأَعُوذُ بِعَظَمَتِكَ أَنْ أُغْتَالَ مِنْ تَحْتِي
- Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fi 'd-dunyā wa 'l-ākhirah Allāhumma innī as'aluka 'l-afwa wa 'l-āfiyah fī dīnī wa dunyāya wa ahlī wa mālī Allāhumma-stur ‘awrātī wa āmin raw‘ātī Allāhumma-ḥfaẓnī min bayni yadayya wa min khalfī wa ‘an yamīnī wa ‘an shimālī wa min fawqī wa a‘ūdhu bi-‘aẓamatika an ughtāla min taḥtī
-O Allah I ask You for pardon and well-being in this world and the next O Allah I ask You for pardon and well-being in my religious and worldly affairs and in my family and my wealth O Allah conceal my faults and keep me safe from the things which I fear O Allah guard me from the front and from behind and from my right and from my left and from above me I seek refuge in Your greatness from being struck from beneath me </t>
-  </si>
-  <si>
-    <t xml:space="preserve">اللَّهُمَّ عَالِمَ الْغَيْبِ وَالشَّهَادَةِ فَاطِرَ السَّمَاوَاتِ وَالْأَرْضِ رَبَّ كُلِّ شَيْءٍ وَمَلِيكَهُ، أَشْهَدُ أَنْ لَا إِلَٰهَ إِلَّا أَنْتَ، أَعُوذُ بِكَ مِنْ شَرِّ نَفْسِي وَمِنْ شَرِّ الشَّيْطَانِ وَشِرْكِهِ، وَأَنْ أَقْتَرِفَ عَلَى نَفْسِي سُوءًا أَوْ أَجُرَّهُ إِلَى مُسْلِمٍ
-Allāhumma ‘ālimal-ghaybi wash-shahādah fāṭiras-samāwāti wal-arḍ rabba kulli shay’in wa-malīkah ash-hadu an lā ilāha illā ant a‘ūdhu bika min sharri nafsī wa-min sharrish-shayṭāni wa-shirkih wa-an aqtarifa ‘alā nafsī sū’an aw ajurrahu ilā muslim
-O Allah Knower of the unseen and the evident Creator of the heavens and the earth Lord of everything and its Possessor I bear witness that there is no deity except You I seek refuge in You from the evil of my soul and from the evil of Satan and his helper/ascribing partners to Allah and from committing any evil against myself or dragging it upon another Muslim
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>الخطوات العملية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+• التوجه إلى جبل الصفا لبدء السعي نزولاً إلى المروة
+• ملحوظة للمعتمر: الذهاب شوط، والإياب شوط آخر
+⛰️ الدعاء عند الوقوف على الصفا وعلى المروة (بداية الأشواط):
+• تستقبل القبلة وتقول:
+       - اللَّهُ أَكْبَرُ، اللَّهُ أَكْبَرُ، اللَّهُ أَكْبَرُ
+       - لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ
+       - لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ، أَنْجَزَ وَعْدَهُ، وَنَصَرَ عَبْدَهُ، وَهَزَمَ الْأَحْزَابَ وَحْدَهُ
 </t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الَّذِي لَا يَضُرُّ مَعَ اسْمِهِ شَيْءٌ فِي الْأَرْضِ وَلَا فِي السَّمَاءِ وَهُوَ السَّمِيعُ الْعَلِيمُ
-Bismillāhil-ladhī lā yaḍurru ma‘as-mihi shay’un fil-arḍi wa-lā fis-samā’i wa-huwas-samī‘ul-‘alīm
-In the name of Allah with Whose name nothing can cause harm on earth or in the heaven and He is the All-Hearing the All-Knowing</t>
-  </si>
-  <si>
-    <t>أَصْبَحْنَا وَأَصْبَحَ الْمُلْكُ لِلَّهِ رَبِّ الْعَالَمِينَ، اللَّهُمَّ إِنِّي أَسْأَلُكَ خَيْرَ هَٰذَا الْيَوْمِ فَتْحَهُ، وَنَصْرَهُ، وَنُورَهُ، وَبَرَكَتَهُ، وَهُدَاهُ، وَأَعُوذُ بِكَ مِنْ شَرِّ مَا فِيهِ وَشَرِّ مَا بَعْدَهُ
-Aṣbaḥnā wa-aṣbaḥal-mulku lillāhi rabbil-‘ālamīn Allāhumma innī as’aluka khayra hādhal-yawm: fatḥahu wa-naṣrahu wa-nūrahu wa-barakatahu wa-hudāh wa-a‘ūdhu bika min sharri mā fīhi wa-sharri mā ba‘dah
-We have reached the morning and at this very time all sovereignty belongs to Allah Lord of the worlds O Allah I ask You for the good of this day its triumphs its victories its light its blessings and its guidance and I take refuge in You from the evil of this day and the evil that follows it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أَصْبَحْنَا عَلَى فِطْرَةِ الْإِسْلَامِ، وَعَلَى كَلِمَةِ الْإِخْلَاصِ، وَعَلَى دِينِ نَبِيِّنَا مُحَمَّدٍ ﷺ، وَعَلَى مِلَّةِ أَبِينَا إِبْرَاهِيمَ حَنِيفًا مُسْلِمًا، وَمَا كَانَ مِنَ الْمُشْرِكِينَ Aṣbahnā `alā fiṭrati ‘l-Islām wa `alā kalimati ‘l-ikhlās wa `alā dīni nabiyyinā Muḥammadin (ṣallallāhu `alayhi wa sallam) wa `alā millati abīnā Ibrāhīm ḥanīfan Musliman wa mā kāna mina ‘l-mushrikīn We have entered a new day upon the natural religion of Islam the word of sincere devotion the religion of our Prophet Muhammad (peace and blessings of Allah be upon him) and the faith of our father Ibrahim He was upright (in worshipping Allah) and a Muslim He was not of those who worship others besides Allah
-</t>
-  </si>
-  <si>
-    <t>أسْتَغْفِرُ اللهَ وَأتُوبُ إلَيْهِ
-Astaghfiru-Llāha wa-atūbu ilayh
-I seek Allah's forgiveness and I turn in repentance to Him</t>
-  </si>
-  <si>
-    <t>بِاسْمِكَ رَبِّي وَضَعْتُ جَنْبِي وَبِكَ أَرْفَعُهُ، فَإِنْ أَمْسَكْتَ نَفْسِي فَارْحَمْهَا، وَإِنْ أَرْسَلْتَهَا فَاحْفَظْهَا بِمَا تَحْفَظُ بِهِ عِبَادَكَ الصَّالِحِينَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنَّكَ خَلَقْتَ نَفْسِي وَأَنْتَ تَوَفَّاهَا، لَكَ مَمَاتُهَا وَمَحْيَاهَا، إِنْ أَحْيَيْتَهَا فَاحْفَظْهَا، وَإِنْ أَمَتَّهَا فَاغْفِرْ لَهَا اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَافِيَةَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ قِنِي عَذَابَكَ يَوْمَ تَبْعَثُ عِبَادَكَ</t>
-  </si>
-  <si>
-    <t>بِاسْمِكَ اللَّهُمَّ أَمُوتُ وَأَحْيَا</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ رَبَّ السَّمَاوَاتِ السَّبْعِ وَرَبَّ الْعَرْشِ الْعَظِيمِ، رَبَّنَا وَرَبَّ كُلِّ شَيْءٍ، فَالِقَ الْحَبِّ وَالنَّوَى، وَمُنْزِلَ التَّوْرَاةِ وَالْإِنجِيلِ وَالْفُرْقَانِ، أَعُوذُ بِكَ مِنْ شَرِّ كُلِّ شَيْءٍ أَنْتَ آخِذٌ بِنَاصِيَتِهِ</t>
-  </si>
-  <si>
-    <t>للَّهُمَّ أَنْتَ الْأَوَّلُ فَلَيْسَ قَبْلَكَ شَيْءٌ، وَأَنْتَ الْآخِرُ فَلَيْسَ بَعْدَكَ شَيْءٌ، وَأَنْتَ الظَّاهِرُ فَلَيْسَ فَوْقَكَ شَيْءٌ، وَأَنْتَ الْبَاطِنُ فَلَيْسَ دُونَكَ شَيْءٌ، اقْضِ عَنَّا الدَّيْنِ وَأَغْنِنَا مِنَ الْفَقْرِ</t>
-  </si>
-  <si>
-    <t>الْحَمْدُ لِلَّهِ الَّذِي أَطْعَمَنَا وَسَقَانَا، وَكَفَانَا وَآوَانَا، فَكَمْ مِمَّنْ لَا كَافِيَ لَهُ وَلَا مُؤْوِيَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَسْلَمْتُ نَفْسِي إِلَيْكَ، وَفَوَّضْتُ أَمْرِي إِلَيْكَ، وَوَجَّهْتُ وَجْهِي إِلَيْكَ، وَأَلْجَأْتُ ظَهْرِي إِلَيْكَ، رَغْبَةً وَرَهْبَةً إِلَيْكَ، لَا مَلْجَأَ وَلَا مَنْجَى مِنْكَ إِلَّا إِلَيْكَ، آمَنْتُ بِكِتَابِكَ الَّذِي أَنْزَلْتَ، وَبِنَبِيِّكَ الَّذِي أَرْسَلْتَ</t>
-  </si>
-  <si>
-    <t>سُبْحَانَ اللَّهِ</t>
-  </si>
-  <si>
-    <t>الْحَمْدُ لِلَّهِ</t>
-  </si>
-  <si>
-    <t>اللَّهُ أَكْبَرُ</t>
-  </si>
-  <si>
-    <t>سُبْحَانَ اللَّهِ
-Subḥānal-lāh
-Glory is to Allah</t>
-  </si>
-  <si>
-    <t>الْحَمْدُ لِلَّهِ
-Al-ḥamdu lillāh
-All praise is to Allah</t>
-  </si>
-  <si>
-    <t>اللَّهُ أَكْبَرُ
-Allāhu Akbar
-Allah is the Most Great</t>
-  </si>
-  <si>
-    <t>آمَنَ الرَّسُولُ بِمَا أُنزِلَ إِلَيْهِ مِن رَّبِّهِ وَالْمُؤْمِنُونَ ۚ كُلٌّ آمَنَ بِاللَّهِ وَمَلَائِكَتِهِ وَكُتُبِهِ وَرُسُلِهِ لَا نُفَرِّقُ بَيْنَ أَحَدٍ مِّن رُّسُلِهِ ۚ وَقَالُوا سَمِعْنَا وَأَطَعْنَا ۖ غُفْرَانَكَ رَبَّنَا وَإِلَيْكَ الْمَصِيرُ ﴿٢٨٥﴾ لَا يُكَلِّفُ اللَّهُ نَفْسًا إِلَّا وُسْعَهَا ۚ لَهَا مَا كَسَبَتْ وَعَلَيْهَا مَا اكْتَسَبَتْ ۗ رَبَّنَا لَا تُؤَاخِذْنَا إِن نَّسِينَا أَوْ أَخْطَأْنَا ۚ رَبَّنَا وَلَا تَحْمِلْ عَلَيْنَا إِصْرًا كَمَا حَمَلْتَهُ عَلَى الَّذِينَ مِن قَبْلِنَا ۚ رَبَّنَا وَلَا تُحَمِّلْنَا مَا لَا طَاقَةَ لَنَا بِهِ ۖ وَاعْفُ عَنَّا وَاغْفِرْ لَنَا وَارْحَمْنَا ۚ أَنتَ مَوْلَانَا فَانصُرْنَا عَلَى الْقَوْمِ الْكَافِرِينَ ﴿٢٨٦﴾
-Āmanar-rasūlu bimā unzila ilayhi mir-rabbihi wal-mu'minūn kullun āmana billāhi wa-malā'ikatihi wa-kutubihi wa-rusulih lā nufarriqu bayna aḥadim-mir-rusulih wa-qālū sami‘nā wa-aṭa‘nā ghufrānaka rabbanā wa-ilaykal-maṣīr Lā yukalliful-lāhu nafsan illā wus‘ahā lahā mā kasabat wa-‘alayhā maktasabat rabbanā lā tu'ākhidhnā in-nasīnā aw akhṭa'nā rabbanā walā taḥmil ‘alaynā iṣran kamā ḥamaltahu ‘alalladhīna min qablinā rabbanā walā tuḥammilnā mā lā ṭāqata lanā bih wa‘fu ‘annā waghfir lanā warḥamnā anta mawlānā fanṣurnā ‘alal-qawmil-kāfirīn
-The Messenger has believed in what was revealed to him from his Lord and [so have] the believers All of them have believed in Allah and His angels and His books and His messengers [saying] "We make no distinction between any of His messengers" And they say "We hear and we obey [We seek] Your forgiveness our Lord and to You is the [final] destination" Allah does not charge a soul except [with that within] its capacity It will have [the consequence of] what [good] it has gained and it will bear [the consequence of] what [evil] it has earned "Our Lord do not impose blame upon us if we have forgotten or erred Our Lord and lay not upon us a burden like that which You laid upon those before us Our Lord and burden us not with that which we have no ability to bear And pardon us; and forgive us; and have mercy upon us You are our protector so give us victory over the disbelieving people"</t>
-  </si>
-  <si>
-    <t>بِاسْمِكَ رَبِّي وَضَعْتُ جَنْبِي وَبِكَ أَرْفَعُهُ، فَإِنْ أَمْسَكْتَ نَفْسِي فَارْحَمْهَا، وَإِنْ أَرْسَلْتَهَا فَاحْفَظْهَا بِمَا تَحْفَظُ بِهِ عِبَادَكَ الصَّالِحِينَ
-Bismika Rabbī waḍa‘tu janbī wa-bika arfa‘uh fa-in amsakta nafsī farḥamhā wa-in arsaltahā faḥfaẓhā bimā taḥfaẓu bihi ‘ibādakas-ṣāliḥīn
-In Your name my Lord I lie down and in Your name I rise If You should take my soul then have mercy upon it and if You should return it then protect it as You protect Your righteous servants</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ إِنَّكَ خَلَقْتَ نَفْسِي وَأَنْتَ تَوَفَّاهَا، لَكَ مَمَاتُهَا وَمَحْيَاهَا، إِنْ أَحْيَيْتَهَا فَاحْفَظْهَا، وَإِنْ أَمَتَّهَا فَاغْفِرْ لَهَا اللَّهُمَّ إِنِّي أَسْأَلُكَ الْعَافِيَةَ
-Allāhumma innaka khalaqta nafsī wa-anta tawaffāhā laka mamātuhā wa-maḥyāhā in aḥyaytahā faḥfaẓhā wa-in amattahā faghfir lahā Allāhumma innī as'aluka 'l-āfiyah
-O Allah You have created my soul and You take its life Unto You belongs its death and its life If You should keep it alive then protect it and if You should take its life then forgive it O Allah I ask You for well-being</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ قِنِي عَذَابَكَ يَوْمَ تَبْعَثُ عِبَادَكَ
-Allāhumma qinī ‘adhābaka yawma tab‘athu ‘ibādak
-O Allah save me from Your punishment on the Day that You resurrect Your servants</t>
-  </si>
-  <si>
-    <t>بِاسْمِكَ اللَّهُمَّ أَمُوتُ وَأَحْيَا
-Bismika-Llāhumma amūtu wa-aḥyā
-In Your name O Allah I die and I live</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ رَبَّ السَّمَاوَاتِ السَّبْعِ وَرَبَّ الْعَرْشِ الْعَظِيمِ، رَبَّنَا وَرَبَّ كُلِّ شَيْءٍ، فَالِقَ الْحَبِّ وَالنَّوَى، وَمُنْزِلَ التَّوْرَاةِ وَالْإِنجِيلِ وَالْفُرْقَانِ، أَعُوذُ بِكَ مِنْ شَرِّ كُلِّ شَيْءٍ أَنْتَ آخِذٌ بِنَاصِيَتِهِ
-Allāhumma rabbas-samāwātis-sab‘i wa-rabbal-arshil-aẓīm rabbanā wa-rabba kulli shay’ fāliqal-ḥabbi wan-nawā wa-munzilat-tawrāti wal-injīli wal-furqān a‘ūdhu bika min sharri kulli shay’in anta ākhidhun bi-nāṣiyatih
-O Allah Lord of the seven heavens and Lord of the Magnificent Throne our Lord and Lord of everything Splitter of the grain and the date-stone Revealer of the Torah the Gospel and the Criterion (the Quran) I seek refuge in You from the evil of everything whose forehead You hold</t>
-  </si>
-  <si>
-    <t>للَّهُمَّ أَنْتَ الْأَوَّلُ فَلَيْسَ قَبْلَكَ شَيْءٌ، وَأَنْتَ الْآخِرُ فَلَيْسَ بَعْدَكَ شَيْءٌ، وَأَنْتَ الظَّاهِرُ فَلَيْسَ فَوْقَكَ شَيْءٌ، وَأَنْتَ الْبَاطِنُ فَلَيْسَ دُونَكَ شَيْءٌ، اقْضِ عَنَّا الدَّيْنِ وَأَغْنِنَا مِنَ الْفَقْرِ
-Allāhumma antal-awwalu falaysa qablaka shay' wa-antal-ākhiru falaysa ba‘daka shay' wa-antaz-ẓāhiru falaysa fawqaka shay' wa-antal-bāṭinu falaysa dūnaka shay' iqḍi ‘annad-dayna wa-aghninā minal-faqr
-O Allah You are the First and there is nothing before You and You are the Last and there is nothing after You You are the Manifest and there is nothing above You and You are the Hidden and there is nothing beyond You Decide our debt for us and remove our poverty</t>
-  </si>
-  <si>
-    <t>الْحَمْدُ لِلَّهِ الَّذِي أَطْعَمَنَا وَسَقَانَا، وَكَفَانَا وَآوَانَا، فَكَمْ مِمَّنْ لَا كَافِيَ لَهُ وَلَا مُؤْوِيَ
-Al-ḥamdu lillāhil-ladhī aṭ‘amanā wa-saqānā wa-kafānā wa-āwānā fakam mimman lā kāfiya lahu wa-lā mu'wī
-Praise is to Allah Who has fed us and given us drink and Who has sufficed us and given us shelter for how many are there who have no one to suffice them and no one to give them shelter</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَسْلَمْتُ نَفْسِي إِلَيْكَ، وَفَوَّضْتُ أَمْرِي إِلَيْكَ، وَوَجَّهْتُ وَجْهِي إِلَيْكَ، وَأَلْجَأْتُ ظَهْرِي إِلَيْكَ، رَغْبَةً وَرَهْبَةً إِلَيْكَ، لَا مَلْجَأَ وَلَا مَنْجَى مِنْكَ إِلَّا إِلَيْكَ، آمَنْتُ بِكِتَابِكَ الَّذِي أَنْزَلْتَ، وَبِنَبِيِّكَ الَّذِي أَرْسَلْتَ
-Allāhumma aslamtu nafsī ilayk wa-fawwaḍtu amrī ilayk wa-wajjahtu wajhī ilayk wa-alja'tu ẓahrī ilayk raghbatan wa-rahbatan ilayk lā malja'a wa-lā manjan minka illā ilayk āmantu bi-kitābikal-ladhī anzalt wa-bi-nabiyyikal-ladhī arsalt
-O Allah I submit myself to You entrust my affairs to You turn my face to You and lay myself down depending upon You out of hope and fear of You There is no refuge and no escape from You except to You I believe in Your Book which You have revealed and in Your Prophet whom You have sent</t>
-  </si>
-  <si>
-    <t>أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ اللَّهُمَّ أَنْتَ السَّلَامُ وَمِنْكَ السَّلَامُ، تَبَارَكْتَ يَا ذَا الْجَلَالِ وَالْإِكْرَامِ</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، اللَّهُمَّ لَا مَانِعَ لِمَا أَعْطَيْتَ، وَلَا مُعْطِيَ لِمَا مَنَعْتَ، وَلَا يَنْفَعُ ذَا الْجَدِّ مِنْكَ الْجَدُّ</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، لَا حَوْلَ وَلَا قُوَّةَ إِلَّا بِاللَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَلَا نَعْبُدُ إِلَّا إِيَّاهُ، لَهُ النِّعْمَةُ وَلَهُ الْفَضْلُ وَلَهُ الثَّنَاءُ الْحَسَنُ، لَا إِلَٰهَ إِلَّا اللَّهُ مُخْلِصِينَ لَهُ الدِّينَ وَلَوْ كَرِهَ الْكَافِرُونَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَجِرْنِي مِنْ النَّار</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَعِنِّي عَلَى ذِكْرِكَ وَشُكْرِكَ وَحُسْنِ عِبَادَتِكَ</t>
-  </si>
-  <si>
-    <t>أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ، أَسْتَغْفِرُ اللَّهَ اللَّهُمَّ أَنْتَ السَّلَامُ وَمِنْكَ السَّلَامُ، تَبَارَكْتَ يَا ذَا الْجَلَالِ وَالْإِكْرَامِ
-Astaghfiru-Llāh, Astaghfiru-Llāh, Astaghfiru-Llāh Allāhumma antas-salāmu wa-minkas-salām, tabārakta yā dhal-jalāli wal-ikrām
-I seek Allah's forgiveness (three times) O Allah, You are Peace and from You comes peace Blessed are You, O Owner of majesty and honor</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، اللَّهُمَّ لَا مَانِعَ لِمَا أَعْطَيْتَ، وَلَا مُعْطِيَ لِمَا مَنَعْتَ، وَلَا يَنْفَعُ ذَا الْجَدِّ مِنْكَ الْجَدُّ
-Lā ilāha illallāhu waḥdahu lā sharīka lah, lahul-mulku wa-lahul-ḥamd, wa-huwa ‘alā kulli shay’in qadīr Allāhumma lā māni‘a limā aṭayt, wa-lā mu‘ṭiya limā mana‘t, wa-lā yanfa‘u dhal-jaddi minkal-jadd
-None has the right to be worshipped except Allah, alone, without partner, to Him belongs all sovereignty and praise, and He is over all things Omnipotent O Allah, none can prevent what You lead to give, and none can give what You prevent, and no wealth or majesty can benefit anyone against Your will</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ، وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ، لَا حَوْلَ وَلَا قُوَّةَ إِلَّا بِاللَّهِ، لَا إِلَٰهَ إِلَّا اللَّهُ وَلَا نَعْبُدُ إِلَّا إِيَّاهُ، لَهُ النِّعْمَةُ وَلَهُ الْفَضْلُ وَلَهُ الثَّنَاءُ الْحَسَنُ، لَا إِلَٰهَ إِلَّا اللَّهُ مُخْلِصِينَ لَهُ الدِّينَ وَلَوْ كَرِهَ الْكَافِرُونَ
-Lā ilāha illallāhu waḥdahu lā sharīka lah, lahul-mulku wa-lahul-ḥamd, wa-huwa ‘alā kulli shay’in qadīr Lā ḥawla wa-lā quwwata illā billāh Lā ilāha illallāhu wa-lā na‘budu illā iyyāh, lahun-ni‘matu wa-lahul-faḍlu wa-lahuth-thanā’ul-ḥasan Lā ilāha illallāhu mukhliṣīna lahud-dīna wa-law karihal-kāfirūn
-None has the right to be worshipped except Allah, alone, without partner, to Him belongs all sovereignty and praise and He is over all things Omnipotent There is no might nor power except with Allah None has the right to be worshipped except Allah and we worship none other than Him From Him comes all favor and to Him belongs all grace and to Him belongs all good praise None has the right to be worshipped except Allah, we are sincere in our devotion to Him even though the disbelievers may detest it</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَجِرْنِي مِنْ النَّار
-Allāhumma ajirnī minan-nār
-O Allah, protect me from the Fire</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ أَعِنِّي عَلَى ذِكْرِكَ وَشُكْرِكَ وَحُسْنِ عِبَادَتِكَ
-Allāhumma a‘innī ‘alā dhikrika, wa-shukrika, wa-ḥusni ‘ibādatik
-O Allah, help me to remember You, to give You thanks, and to worship You in the best of manners</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ اجْعَلْ فِي قَلْبِي نُوراً، وَفِي لِسَانِي نُوراً، وَاجْعَلْ فِي سَمْعِي نُوراً، وَاجْعَلْ فِي بَصَرِي نُوراً، وَاجْعَلْ مِنْ خَلْفِي نُوراً، وَمِنْ أَمَامِي نُوراً، وَاجْعَلْ مِنْ فَوْقِي نُوراً، وَمِنْ تَحْتِي نُوراً، اللَّهُمَّ أَعْطِنِي نُوراً</t>
-  </si>
-  <si>
-    <t>يَبْدَأُ بِرِجْلِهِ اليُمْنَى، وَيَقُولُ: أَعُوذُ بِاللَّهِ الْعَظِيمِ، وَبِوَجْهِهِ الْكَرِيمِ، وَسُلْطَانِهِ الْقَدِيمِ، مِنَ الشَّيْطَانِ الرَّجِيمِ [بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ]، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ اجْعَلْ فِي قَلْبِي نُوراً، وَفِي لِسَانِي نُوراً، وَاجْعَلْ فِي سَمْعِي نُوراً، وَاجْعَلْ فِي بَصَرِي نُوراً، وَاجْعَلْ مِنْ خَلْفِي نُوراً، وَمِنْ أَمَامِي نُوراً، وَاجْعَلْ مِنْ فَوْقِي نُوراً، وَمِنْ تَحْتِي نُوراً، اللَّهُمَّ أَعْطِنِي نُوراً
-Allāhumma-j‘al fī qalbī nūrā wa-fī lisānī nūrā wa-j‘al fī sam‘ī nūrā wa-j‘al fī baṣarī nūrā wa-j‘al min khalfī nūrā wa-min amāmī nūrā wa-j‘al min fawqī nūrā wa-min taḥtī nūrā Allāhumma a‘ṭinī nūrā
-O Allah place light in my heart and on my tongue light and place light in my hearing and place light in my seeing and place light behind me and light before me and place light above me and light beneath me O Allah grant me light</t>
-  </si>
-  <si>
-    <t>يَبْدَأُ بِرِجْلِهِ اليُمْنَى، وَيَقُولُ: أَعُوذُ بِاللَّهِ الْعَظِيمِ، وَبِوَجْهِهِ الْكَرِيمِ، وَسُلْطَانِهِ الْقَدِيمِ، مِنَ الشَّيْطَانِ الرَّجِيمِ [بِسْمِ اللَّهِ، وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ]، اللَّهُمَّ افْتَحْ لِي أَبْوَابَ رَحْمَتِكَ
-A‘ūdhu billāhil-‘aẓīm wa-bi-wajhihil-karīm wa-sulṭānihil-qadīm minash-shayṭānir-rajīm Bismillāhi waṣ-ṣalātu was-salāmu ‘alā rasūlillāh Allāhummaf-taḥ lī abwāba raḥmatik
-I seek refuge in Allah the Almighty in His Noble Face and in His Eternal Dominion from Satan the outcast In the name of Allah and blessings and peace be upon the Messenger of Allah O Allah open for me the gates of Your mercy</t>
-  </si>
-  <si>
-    <t>يَبْدَأُ بِرِجْلِهِ الْيُسْرَى، وَيَقُولُ: بِسْمِ اللَّهِ وَالصَّلَاةُ وَالسَّلَامُ عَلَى رَسُولِ اللَّهِ، اللَّهُمَّ إِنِّي أَسْأَلُكَ مِنْ فَضْلِكَ، اللَّهُمَّ اعْصِمْنِي مِنَ الشَّيْطَانِ الرَّجِيمِ
-Bismillāhi waṣ-ṣalātu was-salāmu ‘alā rasūlillāh Allāhumma innī as’aluka min faḍlik Allāhumma‘-ṣimnī minash-shayṭānir-rajīm
-In the name of Allah and peace and blessings be upon the Messenger of Allah O Allah I ask You from Your favor O Allah guard me from Satan the outcast</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ ﴿١﴾
-الْحَمْدُ لِلَّهِ رَبِّ الْعَالَمِينَ ﴿٢﴾ الرَّحْمَٰنِ الرَّحِيمِ ﴿٣﴾ مَالِكِ يَوْمِ الدِّينِ ﴿٤﴾ إِيَّاكَ نَعْبُدُ وَإِيَّاكَ نَسْتَعِينُ ﴿٥﴾ اهْدِنَا الصِّرَاطَ الْمُسْتَقِيمَ ﴿٦﴾ صِرَاطَ الَّذِينَ أَنْعَمْتَ عَلَيْهِمْ غَيْرِ الْمَغْضُوبِ عَلَيْهِمْ وَلَا الضَّالِّينَ ﴿٧﴾</t>
-  </si>
-  <si>
-    <t>بِسْمِ اللَّهِ الرَّحْمَٰنِ الرَّحِيمِ ﴿١﴾ 
-الْحَمْدُ لِلَّهِ رَبِّ الْعَالَمِينَ ﴿٢﴾ الرَّحْمَٰنِ الرَّحِيمِ ﴿٣﴾ مَالِكِ يَوْمِ الدِّينِ ﴿٤﴾ إِيَّاكَ نَعْبُدُ وَإِيَّاكَ نَسْتَعِينُ ﴿٥﴾ اهْدِنَا الصِّرَاطَ الْمُسْتَقِيمَ ﴿٦﴾ صِرَاطَ الَّذِينَ أَنْعَمْتَ عَلَيْهِمْ غَيْرِ الْمَغْضُوبِ عَلَيْهِمْ وَلَا الضَّالِّينَ ﴿٧﴾
-Bismillāhir-raḥmānir-raḥīm 
-Al-ḥamdu lillāhi rabbil-‘ālamīn Ar-raḥmānir-raḥīm Mālikiyawmid-dīn Iyyāka na‘budu wa-iyyāka nasta‘īn Ihdinaṣ-ṣirāṭal-mustaqīm Ṣirāṭal-ladhīna an‘amta ‘alayhim ghayril-maghḍūbi ‘alayhim walad-ḍāllīn
-In the name of Allah the Beneficent the Merciful 
-Praise is to Allah Lord of the worlds The Beneficent the Merciful Owner of the Day of Judgment You alone we worship and You alone we ask for help Guide us to the straight path The path of those upon whom You have bestowed favor not of those who have evoked [Your] anger or of those who are astray</t>
-  </si>
-  <si>
-    <t>اللهُ اللهُ رَبِّي لَا أُشْرِكُ بِهِ شَيْئًا
-Allāhu Allāhu rabbī lā ushriku bihi shay'ā
-Allah Allah is my Lord I do not associate anything with Him</t>
-  </si>
-  <si>
-    <t>لَّا إِلَٰهَ إِلَّا أَنتَ سُبْحَانَكَ إِنِّي كُنتُ مِنَ الظَّالِمِينَ
-Lā ilāha illā anta subḥānaka innī kuntu minaz-ẓālimīn
-There is no deity except You; exalted are You Indeed I have been of the wrongdoers</t>
-  </si>
-  <si>
-    <t>حَسْبُنَا اللَّهُ وَنِعْمَ الْوَكِيلُ
-Ḥasbunāl-Lāhu wa-ni‘mal-wakīl
-Allah is sufficient for us and He is the best Disposer of affairs</t>
-  </si>
-  <si>
-    <t>لَا حَوْلَ وَلَا قُوَّةَ إِلَّا بِاللَّهِ الْعَلِيِّ الْعَظِيمِ
-Lā ḥawla wa-lā quwwata illā billāhil-‘aliyyil-‘aẓīm
-There is no might nor power except with Allah the Most High the Most Great</t>
-  </si>
-  <si>
-    <t>لَا إِلَٰهَ إِلَّا اللَّهُ الْعَظِيمُ الْحَلِيمُ، لَا إِلَٰهَ إِلَّا اللَّهُ رَبُّ الْعَرْشِ الْعَظِيمِ، لَا إِلَٰهَ إِلَّا اللَّهُ رَبُّ السَّمَاوَاتِ وَرَبُّ الْأَرْضِ وَرَبُّ الْعَرْشِ الْكَرِيمِ
-Lā ilāha illallāhul-‘Aẓīmul-Ḥalīm lā ilāha illallāhu Rabbul-‘Arshil-‘aẓīm lā ilāha illallāhu Rabbus-samāwāti wa-Rabbul-arḍi wa-Rabbul-‘Arshil-karīm
-There is no deity except Allah the Magnificent the Forbearing There is no deity except Allah Lord of the Magnificent Throne There is no deity except Allah Lord of the heavens and Lord of the earth and Lord of the Noble Throne</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ رَحْمَتَكَ أَرْجُو فَلَا تَكِلْنِي إِلَى نَفْسِي طَرْفَةَ عَيْنٍ، وَأَصْلِحْ لِي شَأْنِي كُلَّهُ، لَا إِلَٰهَ إِلَّا أَنْتَ
-Allāhumma raḥmataka arjū falā takilnī ilā nafsī ṭarfata ‘ayn wa-aṣliḥ lī sha’nī kullahu lā ilāha illā ant
-O Allah it is Your mercy that I hope for so do not leave me to myself even for the blink of an eye and rectify for me all of my affairs There is no deity except You</t>
-  </si>
-  <si>
-    <t>اللَّهُمَّ صَلِّ وَسَلِّيمْ عَلَى نَبِيِّنَا مُحَمَّدٍ
-Allāhumma ṣalli wa-sallim ‘alā nabiyyinā Muḥammad
-O Allah send Your praise and peace upon our Prophet Muhammad</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 75
-Primary Hadith Authorities: Al-Hakim (1/562), An-Nasa'i, and At-Tabarani
-Authentication: Authenticated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273), noting that At-Tabarani's chain of transmission is Jayyid (Reliable/Good)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الحماية والإجارة من الجن: من قرأها حين يصبح كان في حفظ الله وأمانه من أذى الشياطين والجن حتى يمسي، ومن قرأها حين يمسي كان محمياً منهم حتى يصبح
-📚 التوثيق المعتمد
-المصدر: أخرجه الحاكم (1/ 562)، وصححه الألباني في صحيح الترغيب والترهيب برقم (1/ 273)، وعزاه إلى النسائي والطبراني
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 76
-Primary Hadith Authorities: Jami' at-Tirmidhi (5/567) and Sunan Abu Dawud (4/322)
-Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/182)
-Whoever recites these three times in the morning and in the evening, they will suffice him (as a protection) against everything</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الكفاية التامة: تكفي العبد من كل شر، وضُر، وسوء، وتغنيه عن أي حماية أو رقية أخرى في يومه وليلته
-📚 التوثيق المعتمد
-المصدر: رواه الترمذي، وأبو داود، والنسائي
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 78 / 79
-Primary Hadith Authorities: Sahih Muslim (4/2088)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 78
-Primary Hadith Authorities: Jami' at-Tirmidhi
-Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/142)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 79 (Sayyid al-Istighfar)
-Primary Hadith Authorities: Sahih al-Bukhari (7/150), Sunan an-Nasa'i, and Jami' at-Tirmidhi
-Authentication: Structurally authenticated and universally accepted within Sahih al-Bukhari</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 80
-Primary Hadith Authorities: Sunan Abu Dawud (4/317), Al-Bukhari (Al-Adab al-Mufrad), An-Nasa'i ('Amalul-Yawm wal-Laylah), and Ibn As-Sunni
-Authentication: Chains of transmission from An-Nasa'i and Abu Dawud graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 23)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 81
-Primary Hadith Authorities: Sunan Abu Dawud (4/318), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 7), Ibn As-Sunni (No 41), and Sahih Ibn Hibban (No 2361)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 24)
-Please paste the next citatio</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 82
-Primary Hadith Authorities: Sunan Abu Dawud (4/324), Musnad Ahmad (5/42), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 22), Ibn As-Sunni (No 69), and Al-Bukhari (Al-Adab al-Mufrad)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 26)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 83
-Primary Hadith Authorities: Ibn As-Sunni (No 71) and Sunan Abu Dawud (4/321)
-Authentication: Both reports are traced directly back to the Prophet ﷺ (Marfu'), with the chain of transmission from Ibn As-Sunni graded Sahih (Sound)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 84
-Primary Hadith Authorities: Sunan Abu Dawud and Sunan Ibn Majah
-Authentication: Authenticated in Sheikh Al-Albani's Sahih Sunan Ibn Majah (2/332)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 85
-Primary Hadith Authorities: Jami' at-Tirmidhi and Sunan Abu Dawud
-Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/142)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الاستعاذة من مصادر الشرور: تحصين كامل للعبد من شر نفسه الأمارة بالسوء، ومن وساوس الشيطان وحبائله وشِركه
-الوقاية من الأذى المتعدي: حماية المسلم من أن يرتكب ذنباً يضر به نفسه، أو يتسبب في إلحاق الضرر والأذى بغيره من المسلمين
-📚 التوثيق المعتمد
-المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح الترمذي (3/142)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)، الذِّكْر رقم (85)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 86
-Primary Hadith Authorities: Sunan Abu Dawud (4/323), Jami' at-Tirmidhi (5/465), Sunan Ibn Majah (2/332), and Musnad Ahmad
-Authentication: Ibn Majah's chain of transmission is graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 39)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 87
-Primary Hadith Authorities: Musnad Ahmad (4/337), An-Nasa'i ('Amalul-Yawm wal-Laylah, p 4), Ibn As-Sunni (No 68), and Jami' at-Tirmidhi (5/465)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 39)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 88
-Primary Hadith Authorities: Mustadrak Al-Hakim (1/545)
-Authentication: Chain of transmission graded Sahih (Sound) by Al-Hakim, as corroborated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 89
-Primary Hadith Authorities: Sunan Abu Dawud (4/322) and Ibn al-Qayyim (Zad al-Ma'ad, 2/273)
-Authentication: Chain of transmission graded Hasan (Good)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 90
-Primary Hadith Authorities: Musnad Ahmad (3/406-407, 5/123), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 34), and Jami' at-Tirmidhi (4/209)
-Authentication: Traced through early authoritative prophetic traditions and traditionally preserved across key Sunan and Musnad compilations</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 91
-Primary Hadith Authorities: Sahih al-Bukhari (4/2071)
-Authentication: Structurally authenticated and universally accepted within Sahih al-Bukhari</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 92
-Primary Hadith Authorities: An-Nasa'i ('Amalul-Yawm wal-Laylah, No 24)
-Authentication: Chain of transmission graded Sahih (Sound) by Sheikh Al-Albani (Sahih al-Jami', 1/272)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الأجور الأربعة العظيمة: كتب الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
-الحفظ من الشيطان: حماية للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
-📚 التوثيق المعتمد
-المصدر: أخرجه النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 94
-Primary Hadith Authorities: Sahih Muslim (4/2090)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 95
-Primary Hadith Authorities: Sunan Ibn Majah (No 925) and Ibn As-Sunni (No 54)
-Authentication: Chain of transmission graded Hasan (Good) by Ibn al-Qayyim (Zad al-Ma'ad, 2/375)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 96
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/101) and Sahih Muslim (4/2075)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 97
-Primary Hadith Authorities: Musnad Ahmad (2/290), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 590), Jami' at-Tirmidhi (3/187), Ibn As-Sunni (No 68), and Sunan Ibn Majah (2/266)
-Authentication: Sunan Ibn Majah's chain is graded Sahih (Sound) by Sheikh Al-Albani, and Jami' at-Tirmidhi's report is graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 45)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 98
-Primary Hadith Authorities: Al-Mu'jam al-Kabir by At-Tabarani
-Authentication: Reported via two transmission chains, with one graded Jayyid (Reliable/Good) Verified by Al-Haythami in Majma' uz-Zawa'id (10/120) and authenticated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening)
-Primary Hadith Authorities: Musnad Ahmad (Hadith No 19606) and Al-Bukhari (Al-Adab al-Mufrad, Hadith No 716)
-Authentication: Graded Sahih (Authentic) by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (Hadith No 36)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-السلامة من الشرك: وقاية العبد وحمايته من الوقوع في الشرك الأكبر والأصغر (كالرياء وخفاء المقاصد)
-تطهير السريرة: إظهار العجز والافتقار إلى الله بطلب المغفرة عن الذنوب والخطايا غير المتعمدة التي لا يعلمها الإنسان
-📚 التوثيق المعتمد
-المصدر: خرّجه الإمام أحمد في المسند (حديث رقم 19606)، وخرّجه الإمام البخاري في الأدب المفرد (حديث رقم 716)، وصححه الإمام الألباني في صحيح الترغيب والترهيب (حديث رقم 36)
-الكتاب المتداول: حصن المسلم، باب: ما يقول من خاف الشرك</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening)
-Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 2893, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 11/173) and Sunan Abi Dawud (Hadith No 1555)
-Authentication &amp; Textual Origin: The foundational narration originates in Sahih al-Bukhari via Anas bin Malik (ra) with highly similar wording The explicit, famous wording preserved in this specific text is recorded by Sunan Abi Dawud within the narrative of Abu Umamah (ra)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-تفريج الهموم والكروب: التماس النجاة والوقاية من أمهات الآفات النفسية والبدنية والمالية والاجتماعية التي تُقعد العبد عن دينه ودنياه
-التحصن من قهر الدَّيْن: حماية للمسلم من ضيق المداين وغلبة الرجال وتسلّط الأعداء، وبث الطمأنينة والانشراح في الصدر والقلب
-📚 التوثيق المعتمد
-المصدر: أصله في صحيح البخاري (حديث رقم 2893، وانظر فتح الباري 11/173) من حديث أنس بن مالك رضي الله عنه بلفظ متقارب واللفظ المشهور المذكور أعلاه رواه أبو داود في سننه (رقم 1555) في قصة أبي أمامة رضي الله عنه
-الكتاب المتداول: حصن المسلم، باب: أذكار الصباح والمساء / الكرب ودفع الهم</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening)
-Primary Hadith Authorities: Sunan Abi Dawud (Hadith No 1517) and Jami' at-Tirmidhi (Hadith No 3577)
-Authentication: Graded Sahih (Authentic) by Sheikh Al-Albani in Sahih Jami' at-Tirmidhi (3/182) and in Mishkat al-Masabih (No 2353)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-مغفرة الكبائر والذنوب العظام: نيل مغفرة الله الشاملة للذنوب، حتى وإن ارتكب العبد ذنباً عظيماً كالفرار من الزحف (الهروب من معركة القتال)
-التوسل بالاسم الأعظم: يجمع الاستغفار بين إعلان التوبة الصادقة والاعتراف بربوبية الله المتضمنة لصفات الحياة والقيومية
-📚 التوثيق المعتمد
-المصدر: خرّجه الإمام أبو داود في سننه (حديث رقم 1517)، وخرّجه الإمام الترمذي في سننه (حديث رقم 3577)، وصححه الإمام الألباني في صحيح الترمذي (3/182)، وفي مشكاة المصابيح (رقم 2353)
-الكتاب المتداول: حصن المسلم، باب: أذكار الاستغفار والتوبة</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 81
-Primary Hadith Authorities: Sunan Abu Dawud (4/318), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 7), Ibn As-Sunni (No 41), and Sahih Ibn Hibban (No 2361)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 24)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 101
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 9/94) and Sahih Muslim (1/554)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>"If any of you rises from his bed and later returns to it, let him dust off his bed with his waist garment three times and mention the Name of Allah, for he does not know what may have entered the bed after him, and when he lies down he should say   " 
-Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 102
-Primary Hadith Authorities: Sahih al-Bukhari (11/126) and Sahih Muslim (4/2084)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 103
-Primary Hadith Authorities: Sahih Muslim (4/2083) and Musnad Ahmad (2/79)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>When the Prophet (ﷺ) wanted to lie down to sleep, he used to place his right hand under his cheek and say
-Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 104
-Primary Hadith Authorities: Sunan Abu Dawud (4/311) and Jami' at-Tirmidhi
-Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/143)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Here, dying and living are metaphors for sleep and wakefulness This explains why the normal order of these words has been reversed in this Hadith In other contexts the living is mentioned before dying 
-Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 105
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/113) and Sahih Muslim (4/2083)
-Quranic Foundations: Cross-referenced with foundational verses of divine life and ownership, including Surah Al-Baqarah </t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 107
-Primary Hadith Authorities: Sahih Muslim (4/2084)
-Quranic Foundations &amp; Notes: References the Gospel (Injil) revealed to 'Isa (Jesus), cross-referenced textually with Surah Al-'Alaq (96:15) regarding the textual concept of seizure by the forelock preceding being cast into Hell
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 107
-Primary Hadith Authorities: Sahih Muslim (4/2084)
-Quranic Foundations &amp; Notes: References the Gospel (Injil) revealed to 'Isa (Jesus), cross-referenced textually with Surah Al-'Alaq (96:15) regarding the concept of seizure by the forelock preceding being cast into Hell
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 108
-Primary Hadith Authorities: Sahih Muslim (4/2085)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Before you go to bed perform ablutions as you would for prayer, then lie down on your right side and say   The Prophet (ﷺ) said: Whoever says this and dies in his sleep, has died in a state of the natural monotheism (Fitrah)
-Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28, Supplication No 111
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/113) and Sahih Muslim (4/2081)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28 (Before Sleeping), Supplication No 101
-Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 5361, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 9/506) and Sahih Muslim (Hadith No 2727)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>عن علي رضي الله عنه أن فاطمة رضي الله عنها شكت ما تلقى في يدها من الرحى وأتت النبي ﷺ تسأله خادماً، فلم تجده، فذكرت ذلك لعائشة، فلما جاء النبي ﷺ أخبرته، فجاءنا وقد أخذنا مضاجعنا، فذهبتُ قمْتُ، فقال: «مَكانَكما» فجلس بيننا حتى وجدتُ برَدَ قدميه على صدري، فقال: «ألا أدلُّكما على خيرٍ مما سألتُما؟ إذا أويتما إلى فراشكما -أو أخذتما مضاجعكما- فكبرا أربعاً وثلاثين، وسبحا ثلاثاً وثلاثين، واحْمدا ثلاثاً وثلاثين، فهو خير لكما من خادم» (رواه البخاري ومسلم)
-🤲 فضل الذكر
- خيرٌ من خادم والتمكين بالقوة: يمنح الذاكرَ قوة بدنية ونشاطاً عظيماً يُغنيه عن الاستعانة بخادم، ويعينه على تحمل مشاق الأعمال اليومية وإنجازها دون تعب
- إعانة النفس وطرد التعب: سبب في تيسير الأمور وتفريج الكربات البدنية والنفسية، حيث وجّه النبي ﷺ ابنتَه فاطمة وعلياً رضي الله عنهما إليه عند شكوى التعب
-📚 التوثيق المعتمد
- المصدر: أخرجه البخاري في صحيحه، ومسلم في صحيحه، من حديث علي بن أبي طالب رضي الله عنه
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28 (Before Sleeping), Supplication No 102
-Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 5361, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 9/506) and Sahih Muslim (Hadith No 2727)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 28 (Before Sleeping), Supplication No 104
-Primary Hadith Authorities: Sahih al-Bukhari (Hadith No 5361, referenced with Ibn Hajar Al-Asqalani's commentary, Fath al-Bari, 9/506) and Sahih Muslim (Hadith No 2727)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Reference: Allah will write ten Hasanaat (rewards) for whoever recites this ten times in the morning, and forgive him ten misdeeds and give him the reward of freeing ten slaves and protect him from Satan Whoever recites this ten times in the evening will get this same reward
-Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 92
-Primary Hadith Authorities: An-Nasa'i ('Amalul-Yawm wal-Laylah, No 24)
-Authentication: Chain of transmission graded Sahih (Sound) by Sheikh Al-Albani (Sahih al-Jami', 1/272)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الأجور الأربعة العظيمة: كَتَبَ الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
- الحفظ من الشيطان: حماية تامّة للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
-📚 التوثيق المعتمد
- المصدر: أخرجه النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 66
-Primary Hadith Authorities: Sahih Muslim (1/414)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 67
-Primary Hadith Authorities: Sahih al-Bukhari (1/255) and Sahih Muslim (1/414)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 68
-Primary Hadith Authorities: Sahih Muslim (1/415)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (After Salam), Supplication No 69
-Primary Hadith Authorities: Sahih Muslim (1/418)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Allah will write ten Hasanaat (rewards) for whoever recites this ten times in the morning, and forgive him ten misdeeds and give him the reward of freeing ten slaves and protect him from Satan Whoever recites this ten times in the evening will get this same reward An-Nasa'i, 'Amalul-Yawm wal-Laylah (no 24) 
-Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 92
-Primary Hadith Authorities: An-Nasa'i ('Amalul-Yawm wal-Laylah, No 24)
-Authentication: Chain of transmission graded Sahih (Sound) by Sheikh Al-Albani (Sahih al-Jami', 1/272)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27 (In the Morning and Evening), Supplication No 72
-Primary Hadith Authorities: Sahih Muslim (4/2090)
-Authentication: Structurally authenticated and universally accepted within Sahih Muslim</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 75 (Cross-referenced under Chapter 25: After Salam in certain thematic indexes)
-Primary Hadith Authorities: Al-Hakim (1/562), An-Nasa'i, and At-Tabarani
-Authentication: Authenticated by Sheikh Al-Albani in Sahih at-Targhib wat-Tarhib (1/273), noting that At-Tabarani's chain of transmission is Jayyid (Reliable/Good)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 25 (Words of Remembrance After Prayer), Supplication No 29 (Note: Depending on the edition's layout, it may correspond to sub-numbering within Chapter 25 or sequential text positioning)
-Primary Hadith Authorities: Sahih Muslim (1/414) / Sahih al-Bukhari
-Authentication: Structurally authenticated and universally accepted across the core canonical traditions</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الأجور الأربعة العظيمة: كَتَبَ الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
- الحفظ من الشيطان: حماية تامّة للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
-📚 التوثيق المعتمد
- المصدر: أخرجه الإمام النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الأجور الأربعة العظيمة: كتب الله للعبد بها عشر حسنات، ومحا عنه عشر سيئات، ونال ثواباً يعادل عتق عشر رقاب في سبيل الله
- الحفظ من الشيطان: حماية تامّة للعبد من مكائد الشيطان ووساوسه طوال يومه إذا قالها صباحاً، وطوال ليلته إذا قالها مساءً
-📚 التوثيق المعتمد
- المصدر: أخرجه النسائي في عمل اليوم والليلة (رقم 24)، وإسناده صحيح (تصحيح الشيخ الألباني في صحيح الترغيب والترهيب 1/272)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- سؤال مقاصد الحياة الصالحة: يجمع العبد في بداية يومه سؤال ثلاثة أمور هي قوام السعادة والنجاح: العلم الذي ينفع صاحبه والأمة، والرزق الحلال المبارك فيه، والعمل الصالح المكتوب له القبول عند الله
-📚 التوثيق المعتمد
- المصدر: خرّجه الإمام ابن ماجه في سننه (حديث رقم 925)، والإمام أحمد في المسند (6/294)، وصححه الإمام الألباني في صحيح ابن ماجه (1/152)
- الكتاب المتداول: حصن المسلم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This Hadith is authentic (Sahih) It was narrated by Imam Muslim in his Sahih on the authority of Abdullah bin Abbas (may Allah be pleased with them both), in the story of his staying overnight at the house of his maternal aunt, Maymunah, the wife of the Prophet ﷺ, and his description of the Prophet’s ﷺ prayer at night and his departure </t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 20 (Thematic entry: Supplication for entering the mosque)
-Primary Hadith Authorities: Sunan Abi Dawud (Hadith No 466), Sahih Muslim (Hadith No 713), and Sunan Ibn Majah (Hadith No 771)
-Authentication &amp; Textual Origin: Compiled as a unified text from multiple intersecting transmission strands and explicitly authenticated by Sheikh Al-Albani</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 21 (Thematic entry: Supplication for exiting the mosque)
-Primary Hadith Authorities: Sahih Muslim (Hadith No 713) and Sunan Ibn Majah (Hadith No 773 for the explicit protection clause)
-Authentication: Authenticated as Sahih (Authentic) by Sheikh Al-Albani</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 82 (Cross-referenced under Chapter 27: Morning and Evening Remembrance, and highly utilized across thematic text sections for Ruqyah)
-Primary Hadith Authorities: Sunan Abu Dawud (4/324), Musnad Ahmad (5/42), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 22), Ibn As-Sunni (No 69), and Al-Bukhari (Al-Adab al-Mufrad)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 26)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 122 (Thematic entry: Supplication for times of distress)
-Primary Hadith Authorities: Sahih al-Bukhari (7/154) and Sahih Muslim (4/2092)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 123 (Thematic entry: Supplication for times of distress)
-Primary Hadith Authorities: Jami' at-Tirmidhi (5/521)
-Authentication: Authenticated as Sahih (Authentic) by Sheikh Al-Albani in Sahih Jami' at-Tirmidhi (3/168)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 132 (Thematic entry: Supplication when facing an enemy or a person of authority)
-Primary Hadith Authorities: Sunan Abi Dawud (2/89) and Al-Hakim (2/142)
-Authentication: Authenticated as Sahih (Authentic) by Al-Hakim, as corroborated and agreed upon by Ad-Dhahabi</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 124 (Thematic entry: Supplication for times of distress and seeking assistance)
-Primary Hadith Authorities: Sunan Abi Dawud (4/324) and Jami' at-Tirmidhi (5/521)
-Authentication: Authenticated as Sahih (Authentic) by Sheikh Al-Albani</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 241 (Thematic entry: Chapter 123 - Seeking forgiveness and repentance)
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Fath al-Bari, 11/101) and Sahih Muslim (4/2075)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 120 (Thematic entry: Chapter 35 - Supplication for times of distress)
-Primary Hadith Authorities: Sunan Abi Dawud (4/324) and Musnad Ahmad (5/42)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz, as corroborated by Sheikh Al-Albani in Sahih Sunan Abi Dawud (3/932)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 121 (Thematic entry: Supplication for times of distress)
-Primary Hadith Authorities: Sunan Abu Dawud (4/324) and Musnad Ahmad (5/42)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 38) and authenticated by Sheikh Al-Albani in Sahih Sunan Abi Dawud</t>
-  </si>
-  <si>
-    <t>Reference: The Prophet (ﷺ) said: "Who recites blessings upon me ten times in the morning and ten times in the evening will obtain my intercession on the Day of Resurrection" At-Tabarani reported this Hadith together with two chains of transmission One of them is reliable (Jayyid) See Haythami's Majma'uz-Zawa'id 10/120, and Al-Albani's Sahihut-Targhib wat-Tarhib 1/273 
-Hisn al-Muslim 98
-Chapter 27: In the morning and evening, Book: Fortress of the Muslim (Hisn al-Muslim)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Supplication No 87 (Cross-referenced under Chapter 27: Morning and Evening Remembrance, and highly utilized across thematic sections for distress, anxiety, and ultimate relief)
-Primary Hadith Authorities: Musnad Ahmad (4/337), An-Nasa'i ('Amalul-Yawm wal-Laylah, p 4), Ibn As-Sunni (No 68), and Jami' at-Tirmidhi (5/465)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 39)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 27, Supplication No 81
-Primary Hadith Authorities: Abu Dawud (4/318), An-Nasa'i ('Amalul-Yawm wal-Laylah, No 7), Ibn As-Sunni (No 41), and Ibn Hibban (No 2361)
-Authentication: Chain of transmission graded Hasan (Good) by Sheikh Ibn Baz (Tuhfat al-Akhyar, p 24)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 130, Supplication No 255 (Cross-referenced with No 93)
-Primary Hadith Authorities: Sahih al-Bukhari (7/67) and Sahih Muslim (4/2071)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t>فضل الذكر
-أجر عتق الرقاب: نيل ثواب عظيم يُعادل عتق أربعة أنفس حرّة من ذرية النبي إسماعيل عليه السلام
-تحقيق التوحيد الخالص: تجديد العهد مع الله بإثبات الألوهية، والملك، والحمد، والقدرة المطلقة له وحده لا شريك له
-📚 التوثيق المعتمد
-المصدر: صحيح البخاري (حديث رقم 6404) وصحيح مسلم (حديث رقم 2693)
-الكتاب المتداول: حصن المسلم، الباب 130 (باب فضل التسبيح والتحميد، والتهليل، والتكبير)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 1, Supplication No 3
-Primary Hadith Authorities: Jami' at-Tirmidhi (5/473)
-Authentication: Authenticated in Sheikh Al-Albani's Sahih Jami' at-Tirmidhi (3/144)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 1, Supplication No 4
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 11/113) and Sahih Muslim (4/2083)
-Authentication: Structurally authenticated and universally accepted across both Sahih al-Bukhari and Sahih Muslim (Muttafaqun Alayh / Agreed Upon)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فضل الذكر
-تجديد التوحيد والشكر: حمد الله على بعث البدن وردّ الروح بعد النوم (الموت الأصغر)
-التذكير بالآخرة: الاستعداد للبعث والنشور الحقيقي بالعمل الصالح منذ أول دقيقة في اليوم
-📚 التوثيق المعتمد
-المصدر: صحيح البخاري، كتاب الدعوات (انظر فتح الباري لابن حجر، مجلد 11، ص 113)
-الكتاب المتداول: حصن المسلم، الباب الأول (أذكار الاستيقاظ من النوم، الحديث الأول)</t>
-  </si>
-  <si>
-    <t>Source: Hisn al-Muslim (Fortress of the Muslim), Chapter 1, Supplication No 5
-Primary Hadith Authorities: Sahih al-Bukhari (referenced with Ibn Hajar Al-Asqalani's commentary, Fathul-Bari, 3/39) and Sunan Ibn Majah (2/335)
-Authentication: The primary virtue is authenticated in Sahih al-Bukhari, with the specific textual wording utilized coming from Sunan Ibn Majah</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فضل الذكر
-مغفرة الذنوب: تنقية العبد من الخطايا فور استيقاظه من النوم وتعاره بالليل
-إجابة الدعاء: فرصة عظيمة لاستجابة أي دعاء يدعو به العبد في تلك اللحظة
-قبول الصلاة: تضمن قبول صلاته إذا توضأ وصلى بعد قراءة هذا الذكر
-📚 التوثيق المعتمد
-المصدر: صحيح البخاري، كتاب التهجد، مع لفظ ابن ماجه في سننه (انظر فتح الباري لابن حجر، مجلد 3، ص 39)
-الكتاب المتداول: حصن المسلم، الباب الأول (أذكار الاستيقاظ من النوم، الحديث الثاني)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🤲 فضل الذكر
- تفويض الملك والحمد لله: إعلان التوحيد الخالص والاستسلام لله في بداية اليوم ونهايته
- طلب الخير الشامل والوقاية: الاستعانة بالله لنيل خير اليوم والمستقبل، والتحصن من الكسل، وسوء الكبر، وعذاب القبر والنار
-📚 التوثيق المعتمد
- المصدر: رواه مسلم (4/2088)، وأخرجه الترمذي (رقم 3390)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء) </t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-التوكل والالتجاء التام: إقرار العبد بأن كل حركاته وسكناته، وحياته وموته، وتقلبه في الصباح والمساء لا تكون إلا بالله وبتدبيره
-استحضار المآل والآخرة: تذكير النفس بمرجعها إلى الله وحده بالبعث والنشور صباحاً، والمصير والرجوع إليه مساءً
-📚 التوثيق المعتمد
-المصدر: أخرجه الترمذي في سننه (المجلد 3، صفحة 142، رقم 3391)، وصححه في صحيح الترمذي
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-موجب لدخول الجنة: مَن قاله موقناً بقلبه بصدق ما فيه حين يمسي ومات من ليلته دخل الجنة، ومَن قاله موقناً به حين يصبح ومات من يومه دخل الجنة
-أعلى صيغ الاستغفار: يتضمن التذلل والخضوع والاعتراف بنعم الله وتقصير العبد في حقه
-📚 التوثيق المعتمد
-المصدر: رواه البخاري (7/150، رقم 6306)، ورواه غيره في النسائي والترمذي
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-العتق من النار: مَن قرأ هذا الذكر أربع مرات في الصباح أو في المساء، كتب الله له النجاة والخلاص من عذاب النار في ذلك اليوم أو تلك الليلة
-📚 التوثيق المعتمد
-المصدر: رواه أبو داود (4/317)، وأخرجه البخاري في الأدب المفرد، والنسائي في عمل اليوم والليلة، وابن السني وإسناد النسائي وأبي داود حسن (تحسين الشيخ ابن باز)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-أداء شكر اليوم والليلة: مَن قرأه في الصباح فقد أدّى شكر يومه كاملًا، ومَن قرأه في المساء فقد أدّى شكر ليلته تجاه نعم الله
-الاعتراف بالمنعم: إقرار العبد بأن كل النعم الظاهرة والباطنة التي يتقلب فيها أو في غيره من الخلائق هي من فضل الله وحده
-📚 التوثيق المعتمد
-المصدر: رواه أبو داود (4/318)، والنسائي في عمل اليوم والليلة (رقم 7)، وابن السني (رقم 41)، وابن حبان (رقم 2361) وإسناده حسن (تحسين الشيخ ابن باز)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-سؤال العافية الشاملة: طلب سلامة البدن وحفظ الحواس (السمع والبصر) من الأمراض والفتن ليستعملها العبد في طاعة الله
-الاستعاذة من المهلكات: التحصن بالله من الكفر المذهب للدين، والفقر المضر بالدنيا، ومن عذاب القبر في الآخرة
-📚 التوثيق المعتمد
-المصدر: رواه أبو داود (4/324)، والإمام أحمد (5/42)، والنسائي في عمل اليوم والليلة (رقم 22)، وابن السني (رقم 69)، والبخاري في الأدب المفرد وإسناده حسن (تحسين الشيخ ابن باز في تحفة الأخيار)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-كفاية الهموم: من قالها سبع مرات في الصباح أو في المساء كفاه الله عز وجل كل ما يشغل باله أو يُقلقه من أمور الدنيا والآخرة
-تحقيق التوكل: تفويض الأمر لله والاعتماد عليه وحده لجلب المصالح ودفع المضار
-📚 التوثيق المعتمد
-المصدر: رواه ابن السني في عمل اليوم والليلة (رقم 71)، وأخرجه أبو داود (4/321) وكلا الروايتين مرفوعتان مباشرة إلى النبي ﷺ، وإسناد ابن السني صحيح
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الحفظ الشامل والتحصين التام: طلب الوقاية والحفظ الإلهي من الأدواء والشرور والمصائب التي قد تصيب العبد من سائر الجهات الست
-سؤال صلاح الدين والدنيا: جمعُ كل خير يرجوه المسلم بسؤال العفو المغفرة للذنوب، والعافية والبركة في النفس، والأهل، والمال، والأمن من المخاوف
-📚 التوثيق المعتمد
-المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح ابن ماجه (2/332)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الاستعاذة من مصادر الشرور: تحصين كامل للعبد من شر نفسه الأمارة بالسوء، ومن وساوس الشيطان وحبائله وشِركه
-الوقاية من الأذى المتعدي: حماية المسلم من أن يرتكب ذنباً يضر به نفسه، أو يتسبب في إلحاق الضرر والأذى بغيره من المسلمين
-📚 التوثيق المعتمد
-المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح الترمذي (3/142)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الحماية من فجأة البلاء: مَن قالها ثلاث مرات حين يصبح لم تُصبه فجأة بلاء ومصيبة بغتة حتى يمسي، ومَن قالها ثلاث مرات حين يمسي حُفظ من فجأة البلاء حتى يصبح
-التحصين الشامل: الاستعانة والاعتصام باسم الله الذي لا يمكن لأي مخلوق أو داء أو شر في الأرض ولا في السماء أن يضر أحداً يتحصن به
-📚 التوثيق المعتمد
-المصدر: رواه أبو داود (4/323)، والترمذي (5/465)، وابن ماجه (2/332)، والإمام أحمد؛ وإسناد ابن ماجه حسن (بتحسين الشيخ ابن باز)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-نيل رضا الله عز وجل: من قالها ثلاث مرات حين يصبح وثلاث مرات حين يمسي، كان حقاً ووعداً على الله سبحانه وتعالى أن يرضيه يوم القيامة ويثيبه بالجنة
-تجديد الرضا واليقين: ترسيخ القناعة التامة والرضا القلبي بربوبية الله، وتشريع الإسلام، ويسر وسنة النبي محمد ﷺ
-📚 التوثيق المعتمد
-المصدر: رواه الإمام أحمد (4/337)، والنسائي في عمل اليوم والليلة (ص 4)، وابن السني (رقم 68)، والترمذي (5/465) وإسناده حسن (بتحسين الشيخ ابن باز)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-صلاح الأحوال التام: طلب الاستعانة برحمة الله التي وسعت كل شيء لإصلاح كافة شؤون العبد الدينية والدنيوية
-البراءة من الحول والقوة: إظهار الافتقار التام إلى الله، والتحصن به من الخذلان أو أن يكل الله العبد إلى تدبير نفسه الضعيفة ولو للحظة واحدة
-📚 التوثيق المعتمد
-المصدر: أخرجه الحاكم في المستدرك (1/545)، وصححه، ووافقه الذهبي، وصححه الألباني في صحيح الترغيب والترهيب (1/273)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-سؤال الخيرات الخمس: التماس البركة والتوفيق الكامل في اليوم بنيل الفتح (تيسير الرزق والعمل)، والنصر على الأعداء والشيطان، ونور العلم والإيمان، والبركة في الوقت، والهدى والثبات على الحق
-التحصن من الشرور: حماية العبد من الآفات والشرور والذنوب التي قد تقع في يومه أو في غده
-📚 التوثيق المعتمد
-المصدر: رواه أبو داود (4/322)، وإسناده حسن وانظر أيضاً: ابن القيم في زاد المعاد (2/273)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-تجديد ميثاق الإيمان: ثبات العبد على الفطرة السوية (الإسلام)، وكلمة التوحيد الخالص (لا إله إلا الله)، والاستمساك بسنة النبي ﷺ ونهج الأنبياء من أول النهار وآخره
-البراءة من الشرك: التبرؤ من سائر ملل الكفر والشرك، وإعلان الاستسلام والانقياد لله وحده حنيفاً مسلماً
-📚 التوثيق المعتمد
-المصدر: رواه الإمام أحمد (3/406-407، و5/123)، والنسائي في عمل اليوم والليلة (رقم 34)، والترمذي (4/209)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-نيل الصدارة يوم القيامة: لم يأتِ أحدٌ يوم القيامة بعملٍ أفضل وأعلى ثواباً ممّن قال هذا الذكر، إلا عبدٌ قال مثل قوله أو زاد عليه في العدد
-محو الخطايا والذنوب: ثوابه يغفر الكبائر والذنوب وإن كانت كثيرة ومثل زبد البحر (كما ورد في الروايات الأخرى للحديث)
-📚 التوثيق المعتمد
-المصدر: رواه البخاري (4/2071)، وكذلك رواه مسلم
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-مضاعفة الأجر والثواب: يعادل في ثوابه وأجره ساعات طويلة من الذكر والعبادة المستمرة، حيث يسبح العبد الله بأعظم الأعداد والصفات
-الثناء العظيم الشامل: تنزيه الله وحمده بعبارات تجمع سائر المخلوقات، وزنة العرش العظيم، ومداد الكلمات الإلهية التي لا تنفد
-📚 التوثيق المعتمد
-المصدر: رواه مسلم (4/2090)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-سؤال مقاصد الحياة الصالحة: يجمع العبد في بداية يومه سؤال ثلاثة أمور هي قوام السعادة والنجاح: العلم الذي ينفع صاحبه والأمة، والرزق الحلال المبارك فيه، والعمل الصالح المكتوب له القبول عند الله
-📚 التوثيق المعتمد
-المصدر: أخرجه ابن ماجه (رقم 925)، وابن السني في عمل اليوم والليلة (رقم 54) وإسناده حسن (بتحسين الإمام ابن القيم في زاد المعاد 2/375)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الاقتداء بالسنة النبوية: لزوم هدي النبي ﷺ وتطبيق سنته الفِعلية، حيث كان يستغفر الله ويتوب إليه مئة مرة في اليوم مع أنه قد غُفِر له ما تقدم من ذنبه وما تأخر
-تطهير القلب وتفريج الهموم: جلاء القلوب من الغفلة والذنوب، وجلب السكينة، وسعة الرزق، وتيسير الأمور المتعسرة للمسلم في يومه وليله
-📚 التوثيق المعتمد
-المصدر: رواه البخاري (انظر فتح الباري لابن حجر 11/101)، ورواه مسلم (4/2075)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🤲 فضل الذكر
-الوقاية من السموم واللدغات: مَن قالها ثلاث مرات حين يمسي لم تضره حَمَةٌ (لدغة عقرب أو حية أو حشرة سامة) في تلك الليلة
-التحصين من الشرور: الاستعاذة بكلمات الله الكاملة التي لا يدخلها نقص، للحماية من شرور الإنس، والجن، والسباع، وسائر الهوام والمخلوقات
-📚 التوثيق المعتمد
-المصدر: رواه الإمام أحمد (2/290)، والنسائي في عمل اليوم والليلة (رقم 590)، والترمذي (3/187)، وابن السني (رقم 68) وإسناد ابن ماجه (2/266) صحيح بحسب الألباني، وحسّن الشيخ ابن باز حديث الترمذي
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء) </t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-نيل الشفاعة النبوية: من حافظ على الصلاة على النبي ﷺ عشر مرات في الصباح وعشر مرات في المساء، نال وعداً صادقاً بأن تدركه شفاعة النبي ﷺ يوم القيامة
-كفاية الهم وغفران الذنب: امتثال أمر الله بالصلاة على رسوله، وهي سبب عظيم لتفريج الهموم والكروب، ونزول الرحمات والبركة على العبد في يومه وليلته
-📚 التوثيق المعتمد
-المصدر: رواه الطبراني بإسنادين أحدهما جيد، وانظر: مجمع الزوائد للهيثمي (10/120)، وحسنه الألباني في صحيح الترغيب والترهيب (1/273)
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- تفويض الملك والحمد لله: إعلان التوحيد الخالص والاستسلام لله في بداية اليوم ونهايته
- طلب الخير الشامل والوقاية: الاستعانة بالله لنيل خير الليلة والمستقبل، والتحصن من الكسل، وسوء الكبر، وعذاب القبر والنار
-📚 التوثيق المعتمد
- المصدر: رواه مسلم (4/2088)، وأخرجه الترمذي (رقم 3390)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- التوكل والالتجاء التام: إقرار العبد بأن كل حركاته وسكناته، وحياته وموته، وتقلبه في الصباح والمساء لا تكون إلا بالله وبتدبيره
- استحضار المآل والآخرة: تذكير النفس بمرجعها إلى الله وحده بالمصير والرجوع إليه مساءً، وبالبعث والنشور صباحاً
-📚 التوثيق المعتمد
- المصدر: أخرجه الترمذي في سننه (المجلد 3، صفحة 142، رقم 3391)، وصححه في صحيح الترمذي
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- العتق من النار: مَن قرأ هذا الذكر أربع مرات في الصباح أو في المساء، كتب الله له النجاة والخلاص من عذاب النار في ذلك اليوم أو تلك الليلة
-📚 التوثيق المعتمد
- المصدر: رواه أبو داود (4/317)، وأخرجه البخاري في الأدب المفرد، والنسائي في عمل اليوم والليلة، وابن السني وإسناد النسائي وأبي داود حسن (بتحسين الشيخ ابن باز)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- أداء شكر اليوم والليلة: مَن قرأه في الصباح فقد أدّى شكر يومه كاملًا، ومَن قرأه في المساء فقد أدّى شكر ليلته تجاه نعم الله
- الاعتراف بالمنعم: إقرار العبد بأن كل النعم الظاهرة والباطنة التي يتقلب فيها أو في غيره من الخلائق هي من فضل الله وحده
-📚 التوثيق المعتمد
- المصدر: رواه أبو داود (4/318)، والنسائي في عمل اليوم والليلة (رقم 7)، وابن السني (رقم 41)، وابن حبان (رقم 2361) وإسناده حسن (بتحسين الشيخ ابن باز)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- سؤال الخيرات الخمس: التماس البركة والتوفيق الكامل في الليلة أو اليوم بنيل الفتح (تيسير الرزق والعمل)، والنصر على الأعداء والشيطان، ونور العلم والإيمان، والبركة في الوقت، والهدى والثبات على الحق
- التحصن من الشرور: حماية العبد من الآفات والشرور والذنوب التي قد تقع في ليلته (أو يومه) أو في غده
-📚 التوثيق المعتمد
- المصدر: رواه أبو داود (4/322)، وإسناده حسن وانظر أيضاً: ابن القيم في زاد المعاد (2/273)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- تجديد ميثاق الإيمان: ثبات العبد على الفطرة السوية (الإسلام)، وكلمة التوحيد الخالص (لا إله إلا الله)، والاستمساك بسنة النبي ﷺ ونهج الأنبياء من أول النهار وآخره
- البراءة من الشرك: التبرؤ من سائر ملل الكفر والشرك، وإعلان الاستسلام والانقياد لله وحده حنيفاً مسلماً
-📚 التوثيق المعتمد
- المصدر: رواه الإمام أحمد (3/406-407، و5/123)، والنسائي في عمل اليوم والليلة (رقم 34)، والترمذي (4/209)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- سؤال مقاصد الحياة الصالحة: يجمع العبد في بداية يومه سؤال ثلاثة أمور هي قوام السعادة والنجاح: العلم الذي ينفع صاحبه والأمة، والرزق الحلال المبارك فيه، والعمل الصالح المكتوب له القبول عند الله
-📚 التوثيق المعتمد
- المصدر: أخرجه ابن ماجه (رقم 925)، وابن السني في عمل اليوم والليلة (رقم 54) وإسناده حسن (بتحسين الإمام ابن القيم في زاد المعاد 2/375)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الكفاية التامة: من قرأ هاتين الآيتين في ليلته كفتاه من كل سوء ومكروه، وقيل كفتاه وأجزأتاه عن قيام تلك الليلة من العبادة والذكر
- تثبيت أركان الإيمان: تذكير بأصول العقيدة والتوكل، وسؤال الله اللطف، والمغفرة، والنصر على الأعداء قبل النوم
-📚 التوثيق المعتمد
- المصدر: سورة البقرة (الآيتان 285-286) رواه البخاري (انظر فتح الباري لابن حجر 9/94)، ورواه مسلم (1/554)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- طلب الرحمة والحفظ عند النوم: تفويض الأمر لله تعالى وتسليمه الروح حال النوم، وسؤاله الرحمة والمغفرة للنفس إن قُبضت وماتت، والحفظ والرعاية والوقاية من الشرور إن كُتبت لها الحياة وعادت للدنيا
-📚 التوثيق المعتمد
- المصدر: رواه البخاري (11/126)، ورواه مسلم (4/2084)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- التسليم المطلق لله: إقرار العبد بأن المحيا والممات وتدبير الروح والنفس بيد الله وحده لا شريك له
- سؤال العافية والمغفرة: جمعُ الاستعاذة والطلب لحفظ النفس وصيانتها في حياتها، وسؤال المغفرة والرحمة لها بعد مماتها، مع طلب العافية الشاملة في الدين والدنيا
-📚 التوثيق المعتمد
- المصدر: رواه مسلم (4/2083)، والإمام أحمد (2/79)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الوقاية من أهوال الآخرة: سؤال الله الحماية والسلامة من عذاب يوم القيامة (يوم البعث والنشور)
- الاقتداء بالهدي النبوي: لزوم سُنّة النبي ﷺ في هيئة النوم بوضع اليد اليمنى تحت الخد واستحضار الآخرة قبل النوم
-📚 التوثيق المعتمد
- المصدر: رواه أبو داود (4/311)، وانظر أيضاً: صحيح الترمذي للألباني (3/143)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الاستسلام والافتتاح باسم الله: إيداع العبد نفسه وروحه لله تعالى عند الموتة الصغرى (النوم)، وتفويض حياته وموته ويقظته لتدبيره سبحانه
- الاقتداء بالهدى النبوي: لزوم سُنّة النبي ﷺ في جعل آخر كلامه قبل النوم ذكراً لله وثناءً عليه، ليكون يومه منتهياً على الطاعة والتوحيد
-📚 التوثيق المعتمد
- المصدر: أصله في صحيح البخاري (انظر فتح الباري لابن حجر العسقلاني 11/113)، ورواه مسلم (4/2083)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- قضاء الديون وتفريج الأزمات المادية: الالتجاء إلى الله سبحانه بنية التخلص من ثقل الديون وضيق الفقر، وسؤاله السعة والغنى في المال والرزق
- التحصن بأسماء الله الحسنى: تفويض الأمر لله المستحق للربوبية المطلقة والقدرة التامة على كل المخلوقات، والاستعاذة به من شرور كل الدواب والآفات في الدنيا والآخرة
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (4/2084، رقم 2713)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- قضاء الديون وتفريج الأزمات المادية: الالتجاء إلى الله سبحانه بنية التخلص من ثقل الديون وضيق الفقر، وسؤاله السعة والغنى في المال والرزق
- التحصن بأسماء الله الحسنى: تفويض الأمر لله المستحق للربوبية المطلقة والقدرة التامة على كل المخلوقات، والاستعاذة به من شرور كل الدواب والآفات في الدنيا والآخرة
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (4/2084، رقم 2713)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- استشعار نعم الله الكبرى: تذكير النفس بأجلّ النعم الدنيوية (الطعام، والشراب، والكفاية، والسكن) قبل النوم، ومقارنة حال العبد بمن حُرموا من المأوى والأمان لزيادة شكر الله
- تحقيق الرضا والطمأنينة: الاعتراف بكفاية الله ولطفه ورعايته للعبد، مما يورث راحة البال وانشراح الصدر وطرد المخاوف قبل النوم
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (4/2085)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الاستعاذة من مصادر الشرور: تحصين كامل للعبد من شر نفسه الأمارة بالسوء، ومن وساوس الشيطان وحبائله وشِركه
- الوقاية من الأذى المتعدي: حماية المسلم من أن يرتكب ذنباً يضر به نفسه، أو يتسبب في إلحاق الضرر والأذى بغيره من المسلمين
-📚 التوثيق المعتمد
- المصدر: أخرجه أبو داود في سننه، وصححه الألباني في صحيح الترمذي (3/142)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الموت على الفطرة والسنة: مَن قال هذا الذكر قبل نومه ثم مات في ليلته تلك، مات على الفطرة السوية (دين الإسلام) وكان ممّن خُتم لهم بخير
- كمال التفويض والتوكل: تفويض العبد سائر شؤونه وحياته لله وحده، وإظهار الافتقار التام والالتجاء إليه رغبةً في ثوابه ورهبةً من عقابه
-📚 التوثيق المعتمد
- المصدر: رواه البخاري (انظر فتح الباري لابن حجر العسقلاني 11/113)، ورواه مسلم (4/2081)
- الكتاب المتداول: حصن المسلم، الباب 28 (أذكار النوم)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- تحقيق التوحيد وإخلاص الدين: إعلان البراءة من الشرك، والاعتراف بأن النعمة والفضل والثناء كله لله وحده، مما يرسخ صدق العبودية والتوكل في قلب العبد بعد الفراغ من الصلاة
- الاستعانة بالله والاعتراف بعجزه: التبرؤ من الحول والقوة الشخصية بالالتجاء إلى قوة الله (الحوقلة) لتيسير سائر الأعمال والطاعات
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (1/414)
- الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- موجب لدخول الجنة: مَن حافظ على قراءتها فور الفراغ من الصلاة المكتوبة، لم يمنعه من دخول الجنة إلا أن يموت (بناءً على الأحاديث المفسرة للفضل في هذا الباب)
- التحصين الشامل: حماية العبد وحفظه في ذمة الله ورعايته من الصلاة إلى الصلاة الأخرى
-📚 التوثيق المعتمد
- المصدر: رواه البخاري (1/255)، ورواه مسلم (1/414)
- الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- مغفرة الذنوب الشاملة: غفران خطايا العبد وذنوبه وإن كانت كثيرة مثل زبد البحر
- تحقيق الأجور العظيمة بعد الصلاة: الاستمساك بالباقيات الصالحات التي تثقل الموازين وتجلب معية الله للعبد عقب الفراغ من الفريضة
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (1/415)
- الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- مغفرة الذنوب الشاملة: غفران خطايا العبد وذنوبه وإن كانت كثيرة مثل زبد البحر عند المحافظة عليها خلف كل صلاة
- التحصين والوقاية دبر الصلاة: حماية المسلم وكفايته من سائر الشرور والآفات والشرك بوساطة الاستعاذة بأعظم السور والتعوذ بها
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (1/418)
- الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الحماية والإجارة من الجن والشياطين: مَن قرأها حين يصبح كان في حفظ الله وأمانه من أذى الشياطين حتى يمسي، ومَن قرأها حين يمسي أُجير وحُفظ منهم حتى يصبح
- أعظم آية في كتاب الله: تشتمل على أصول التوحيد والأسماء والصفات العليا لله تعالى، وقراءتها تورث الطمأنينة والأمان التام للعبد
-📚 التوثيق المعتمد
- المصدر: أخرجه الحاكم في المستدرك (1/562)، وصححه الألباني في صحيح الترغيب والترهيب (رقم 662 / 1/273)، وعزاه إلى النسائي والطبراني بإسناد جيد
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>اعتمَرَ النبي ﷺ في حياته أربع عُمرٍ كلها في شهر ذي القعدة إلا عمرته التي كانت مع حجته</t>
-  </si>
-  <si>
-    <t>فضل دخول المسجد الحرام ورؤية الكعبة مضاعفة الأجور: الصلاة في المسجد الحرام تعدل 100,000 صلاة فيما سواهاستجابة الدعاء: رؤية الكعبة لأول مرة وهيبتها من المواطن التي يُرجى فيها استجابة الدعاء، حيث تنزل الرحمات على هذا البيت المبارك كل يوم</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فضل السعي بين الصفا والمروةإحياء شعائر الله: السعي هو تخليد لذكرى توكل السيدة هاجر عليها السلام وبحثها عن الماء لوليدها إسماعيل، وهو من شعائر الله العظيمةثواب عظيم: السعي بين الصفا والمروة يعدل في الثواب عتق الرقاب، وهو ركن لا تصح العمرة إلا به</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فضل الحلق أو التقصير (التحلل) دعاء النبي بالرحمة والمغفرة: نال المحلقون النصيب الأكبر من دعاء النبي ﷺ بالرحمة ثلاث مرات، وللمقصرين مرة واحدة، حيث قال: «اللَّهُمَّ ارْحَمِ المُحَلِّقِينَ، قالوا: والمُقَصِّرِينَ يا رَسولَ اللَّهِ؟ قالَ: اللَّهُمَّ ارْحَمِ المُحَلِّقِينَ، قالوا: والمُقَصِّرِينَ يا رَسولَ اللَّهِ؟ قالَ: والمُقَصِّرِينَ»خروج من الذنوب: هو الإعلان الرسمي لتمام العبادة والخضوع الكامل لله بتسليم الرأس (وهي موضع العزة) لله سبحانه</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 💡إرشاد للمعتمر</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: تُكررها 3 مرات، وتدعو بينها بما تحب من الدعاء الحر
+الدعاء أثناء السعي (بين الجبلين):
+ يُستحب تكرار
+«رَبِّ اغْفِرْ وَارْحَمْ إِنَّكَ أَنْتَ الْأَعَزُّ الْأَكْرَمُ»</t>
+    </r>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+فضل الإحرام والتلبية تطهير من الذنوب: الطهارة والاغتسال عند الميقات يمثلان استعداداً ظاهرياً وباطنياً للوقوف بين يدي اللهتسبّح معه الكائنات: قال النبي ﷺ: ما مِن مُسلمٍ يُلبِّي إلَّا لبَّى مَن عن يمينِه أو عَن شمالِه مِن حجرٍ أو شجرٍ أو مَدرٍ، حتَّى تنقطعَ الأرضُ مِن ههُنا وَههُنا
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام الترمذي في سننه (رقم 828)، والإمام ابن ماجه (رقم 2921)، وصححه الإمام الألباني في صحيح الجامع، من حديث سهل بن سعد الساعدي رضي الله عنه
+ الكتاب المتداول: حصن المسلم، باب التلبية</t>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+فضل دخول المسجد الحرام ورؤية الكعبة مضاعفة الأجور: الصلاة في المسجد الحرام تعدل 100,000 صلاة فيما سواهاستجابة الدعاء: رؤية الكعبة لأول مرة وهيبتها من المواطن التي يُرجى فيها استجابة الدعاء، حيث تنزل الرحمات على هذا البيت المبارك كل يوم
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام أحمد في مسنده (رقم 14694)، والإمام ابن ماجه في سننه (رقم 1406)، وصححه الإمام الألباني في صحيح ابن ماجه، من حديث جابر بن عبد الله رضي الله عنهما ووردت أحاديث وآثار في فضل الدعاء عند رؤية الكعبة أخرجها الإمام البيهقي في السنن الكبرى
+ الكتاب المتداول: حصن المسلم، باب فضل الصلاة في مسجدي مكة والمدينة</t>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+ فضل الطواف حول الكعبة حطّ السيئات ورفع الدرجات: كل خطوة يخطوها المعتمر في الطواف لها أجر، قال ﷺ: مَنْ طَافَ بِهَذَا الْبَيْتِ أُسْبُوعاً (أي 7 أشواط) فَأَحْصَاهُ، كَانَ كَعِتْقِ رَقَبَةٍ، لا يَضَعُ قَدَماً وَلا يَرْفَعُ أُخْرَى إِلا حَطَّ اللَّهُ عَنْهُ بِهَا خَطِيئَةً، وَكَتَبَ لَهُ بِهَا حَسَنَةً
+مغفرة الذنوب: الطواف بالبيت يعود بالعبد كيوم ولدته أمه إذا تقبله الله
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام الترمذي في سننه (رقم 959) واللفظ له، والإمام أحمد في مسنده (رقم 4462)، وصححه الإمام الألباني في صحيح الجامع (رقم 6379)، من حديث عبد الله بن عمر رضي الله عنهما
+ الكتاب المتداول: حصن المسلم، باب الذكر عند استلام الحجر الأسود والدعاء في الطواف</t>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+ فضل السعي بين الصفا والمروة إحياء شعائر الله: السعي هو تخليد لذكرى توكل السيدة هاجر عليها السلام وبحثها عن الماء لوليدها إسماعيل، وهو من شعائر الله العظيمةثواب عظيم: السعي بين الصفا والمروة يعدل في الثواب عتق الرقاب، وهو ركن لا تصح العمرة إلا به
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام الطبراني في المعجم الكبير، والإمام البزار في مسنده، وصححه الإمام الألباني في صحيح الترغيب والترهيب (رقم 1118)، من حديث عبد الله بن عمر رضي الله عنهما عن النبي ﷺ وفيه: وأما طوافك بالصفا والمروة كعتق سبعين رقبة
+ الكتاب المتداول: حصن المسلم، باب ما يقول إذا وقف على الصفا والمروة</t>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+فضل ركعتي الطواف والشرب من زمزم
+مقام إبراهيم: الصلاة خلف المقام هي إحياء لسنة الخليل إبراهيم عليه السلام وامتثال لأمر الله: وَاتَّخِذُوا مِنْ مَقَامِ إِبْرَاهِيمَ مُصَلًّى
+الشرب من زمزم : طعام طُعم وشفاء سُقم: ماء زمزم مبارك، والدعاء عنده مستجاب، وهو نية لما شُرب له (شفاء، علم، رزق، أو مغفرة)
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام مسلم في صحيحه (رقم 1218) في حديث جابر الطويل في صفة حج النبي ﷺ وصلاته خلف المقام وأخرج قصة زمزم وفضلها الإمام البخاري في صحيحه (رقم 3364) من حديث ابن عباس رضي الله عنهما، وأخرج حديث "ماء زمزم لما شرب له" الإمام ابن ماجه (رقم 3062) وحسنه وصححه جمع من أهل العلم
+ الكتاب المتداول: حصن المسلم، باب الدعاء خلف مقام إبراهيم، وباب: الشرب من ماء زمزم</t>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+ فضل الحلق أو التقصير (التحلل) دعاء النبي بالرحمة والمغفرة: نال المحلقون النصيب الأكبر من دعاء النبي ﷺ بالرحمة ثلاث مرات، وللمقصرين مرة واحدة، حيث قال: «اللَّهُمَّ ارْحَمِ المُحَلِّقِينَ، قالوا: والمُقَصِّرِينَ يا رَسولَ اللَّهِ؟ قالَ: اللَّهُمَّ ارْحَمِ المُحَلِّقِينَ، قالوا: والمُقَصِّرِينَ يا رَسولَ اللَّهِ؟ قالَ: والمُقَصِّرِينَ»خروج من الذنوب: هو الإعلان الرسمي لتمام العبادة والخضوع 
+الكامل لله بتسليم الرأس (وهي موضع العزة) لله سبحانه
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام البخاري في صحيحه (رقم 1727)، والإمام مسلم في صحيحه (رقم 1301)، من حديث عبد الله بن عمر رضي الله عنهما أن رسول الله ﷺ قال: «اللَّهُمَّ ارْحَمِ المُحَلِّقِينَ، قالوا: والمُقَصِّرِينَ يا رَسولَ اللَّهِ؟ قالَ: اللَّهُمَّ ارْحَمِ المُحَلِّقِينَ، قالوا: والمُقَصِّرِينَ يا رَسولَ اللَّهِ؟ قالَ: والمُقَصِّرِينَ»
+ الكتاب المتداول: حصن المسلم، باب التحلل من الإحرام</t>
+  </si>
+  <si>
+    <t>🕋 فَضْلُ نُسُكِ العُمْرَةِ وَشَعَائِرُهَا
+اعتمَرَ النبي ﷺ في حياته أربع عُمرٍ كلها في شهر ذي القعدة إلا عمرته التي كانت مع حجته
+📜 الدَّلِيلُ المَرْجِعِيُّ
+ المصدر: أخرجه الإمام البخاري في صحيحه (3/3)، وأخرجه الإمام مسلم في صحيحه (2/916)، من حديث أنس بن مالك رضي الله عنه قال: «اعتمر رسول الله ﷺ أربع عمر، كلهن في ذي القعدة إلا التي مع حجته»
+ الكتاب المتداول: زاد المعاد في هدي خير العباد للإمام ابن القيم (فصل في عُمَرِهِ ﷺ) وصحيح البخاري كتاب العمرة في باب كم اعتمر النبي ﷺ</t>
   </si>
   <si>
     <r>
@@ -2383,10 +2582,10 @@
       </rPr>
       <t xml:space="preserve">:
 • صلاة ركعتين خلف مقام إبراهيم (أو في أي مكان متاح داخل الحرم).
-• التوجه للشرب من ماء زمزم.
-💧 عند الشرب من ماء زمزم:
-• ليس هناك نص دعاء إلزامي محدد.
-• ادعُ بما تشاء من خيري الدنيا والآخرة.
+• التوجه للشرب من ماء زمزم
+💧 عند الشرب من ماء زمزم
+• ليس هناك نص دعاء إلزامي محدد
+• ادعُ بما تشاء من خيري الدنيا والآخرة
 </t>
     </r>
     <r>
@@ -2408,85 +2607,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: «مَاءُ زَمْزَمَ لِمَا شُرِبَ لَهُ» (حديث شريف).</t>
+      <t>: «مَاءُ زَمْزَمَ لِمَا شُرِبَ لَهُ» (حديث شريف)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> الخطوة الخامسة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: السعي بين الصفا والمروة (7 أشواط)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>الخطوات العملية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-• التوجه إلى جبل الصفا لبدء السعي نزولاً إلى المروة.
-• ملحوظة للمعتمر: الذهاب شوط، والإياب شوط آخر.
-⛰️ الدعاء عند الوقوف على الصفا وعلى المروة (بداية الأشواط):
-• تستقبل القبلة وتقول:
-       - اللَّهُ أَكْبَرُ، اللَّهُ أَكْبَرُ، اللَّهُ أَكْبَرُ
-       - لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ لَا شَرِيكَ لَهُ، لَهُ الْمُلْكُ وَلَهُ الْحَمْدُ وَهُوَ عَلَى كُلِّ شَيْءٍ قَدِيرٌ
-       - لَا إِلَٰهَ إِلَّا اللَّهُ وَحْدَهُ، أَنْجَزَ وَعْدَهُ، وَنَصَرَ عَبْدَهُ، وَهَزَمَ الْأَحْزَابَ وَحْدَهُ
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 💡إرشاد للمعتمر</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: تُكررها 3 مرات، وتدعو بينها بما تحب من الدعاء الحر.
-الدعاء أثناء السعي (بين الجبلين):
- يُستحب تكرار:
-«رَبِّ اغْفِرْ وَارْحَمْ إِنَّكَ أَنْتَ الْأَعَزُّ الْأَكْرَمُ»</t>
-    </r>
+    <t>🤲 فضل الذكر
+ أعظم سورة في القرآن: هي أم الكتاب والسبع المثاني التي لا تصح الصلاة إلا بها، وتشتمل على مجامع التوحيد والثناء والطلب
+ رقية شرعية شافية: رقية مباركة تُقرأ بنية الشفاء من الأمراض البدنية، ولدغات الهوام، والهموم والكروب؛ لقول النبي ﷺ عنها: وما أدراك أنها رقية؟
+📚 التوثيق المعتمد
+ المصدر: رواه البخاري (حديث رقم 2276 / 5007) ومسلم (حديث رقم 2201)، من حديث أبي سعيد الخدري رضي الله عنه
+ الكتاب المتداول: حصن المسلم، باب الرقية الشرعية من أذكار الكتاب والسنة</t>
   </si>
   <si>
     <t>🤲 فضل الذكر
@@ -2494,7 +2624,7 @@
  تحقيق التوحيد المطلق: يرتكز فضلها على إعلان التوحيد الخالص لله والالتجاء التام إليه، والبراءة من الشرك كله، وهو سبب كشف الغموم
 📚 التوثيق المعتمد
  المصدر: أخرجه الإمام أبو داود في سننه، وصححه الإمام الألباني في صحيح ابن ماجه (2/335) وصحيح أبي داود، عن أسماء بنت عميس رضي الله عنها
- الكتاب المتداول: حصن المسلم، باب: دعاء الكرب</t>
+ الكتاب المتداول: حصن المسلم، باب دعاء الكرب</t>
   </si>
   <si>
     <t>🤲 فضل الذكر
@@ -2502,7 +2632,7 @@
  الجمع بين التوحيد والاعتراف بالذنب: يتضمن الذكر تنزيه الله عز وجل وإثبات الألوهية له وحده، مع إقرار العبد بتقصيره وظلمه لنفسه، وهو أقرب أبواب الإجابة والفرج
 📚 التوثيق المعتمد
  المصدر: أخرجه الإمام الترمذي في سننه (حديث رقم 3505)، والإمام أحمد في المسند (حديث رقم 1462)، وصححه الإمام الألباني في صحيح الترمذي، من حديث سعد بن أبي وقاص رضي الله عنه
- الكتاب المتداول: حصن المسلم، باب: دعاء الكرب</t>
+ الكتاب المتداول: حصن المسلم، باب دعاء الكرب</t>
   </si>
   <si>
     <t xml:space="preserve">🤲 فضل الذكر
@@ -2510,15 +2640,15 @@
  طرد الفزع وبث السكينة: يقين العبد بكفاية الله له يطرد الخوف والرعب من قلبه، ويورثه شجاعة وثباتاً وطمأنينة أمام المحن والتهديدات
 📚 التوثيق المعتمد
  المصدر: رواه الإمام مسلم في صحيحه (حديث رقم 3005)، في قصة الغلام وأصحاب الأخدود الشهيرة
- الكتاب المتداول: حصن المسلم، باب: ما يقول من خاف ظلماً أو عدواً (أو دعاء الفزع والكرب) </t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- كشف الغم وتفريج الكرب الشديد: دعوة عظيمة نادى بها نبي الله يونس عليه السلام في بطن الحوت، وهي ركيزة أساسية في تفريج الهموم وضيق الصدر، وما دعا بها مسلم في شيء قط إلا استجاب الله له
- الجمع بين التوحيد والاعتراف بالذنب: يتضمن الذكر تنزيه الله عز وجل وإثبات الألوهية له وحده، مع إقرار العبد بتقصيره وظلمه لنفسه، وهو من أقرب أبواب الإجابة وتفويض الأمر لله للفرج واليسر
-📚 التوثيق المعتمد
- المصدر: أخرجه الإمام الترمذي في سننه (5/529)، وأخرجه الحاكم في المستدرك وصححه ووافقه الذهبي (1/505)، وصححه الإمام الألباني في صحيح الترمذي (3/168)، من حديث سعد بن أبي وقاص رضي الله عنه
- الكتاب المتداول: حصن المسلم، باب: دعاء الكرب (باب الكرب والهم)</t>
+ الكتاب المتداول: حصن المسلم، باب ما يقول من خاف ظلماً أو عدواً (أو دعاء الفزع والكرب) </t>
+  </si>
+  <si>
+    <t>🤲 فضل الذكر
+ كنز من كنوز الجنة وباب من أبوابها: هي كلمة استسلام وتفويض لله عز وجل، وتعد من أعظم العطايا الذخيرة للمؤمن في الآخرة، ولها تأثير عجيب في تحمل الأثقال، ومكابدة المشاق، وتحسين الأحوال بفضل الله وتوفيقه
+ دفع الهموم وتفريج الكرب الشديد: ركيزة أساسية في الاستعانة بالله والتبتل إليه، وهي دواء نافع لتفريج ضيق الصدر والغم، لما فيها من إقرار كامل من العبد بالعجز والضعف، والالتجاء التام إلى حول الله وقوته وقدرته
+📚 التوثيق المعتمد
+ المصدر: أخرجه الإمام البخاري في صحيحه (9/95)، وأخرجه الإمام مسلم في صحيحه (4/2076)، من حديث أبي موسى الأشعري رضي الله عنه وجاءت زيادة "العلي العظيم" في روايات أخرى أخرجها الإمام أحمد في مسنده
+ الكتاب المتداول: حصن المسلم، باب الدعاء عند الكرب</t>
   </si>
   <si>
     <t>🤲 فضل الذكر
@@ -2526,7 +2656,7 @@
  النجاة والبركة وعموم الخيرات: جالب لمغفرة الذنوب، ونزول الغيث والبركات، والإمداد بالأموال والبنين، وإعطاء البدن القوة والراحة والسكينة
 📚 التوثيق المعتمد
  المصدر: أصله في القرآن الكريم (سورة نوح، الآيات 10-12) وفي صحيح البخاري (حديث رقم 6307)، وصحيح مسلم (حديث رقم 2702) في الحث على لزوم التوبة والاستغفار في اليوم مئة مرة
- الكتاب المتداول: حصن المسلم، باب: الاستغفار والتوبة</t>
+ الكتاب المتداول: حصن المسلم، باب الاستغفار والتوبة</t>
   </si>
   <si>
     <t>🤲 فضل الذكر
@@ -2534,7 +2664,7 @@
  إثبات عظمة الخالق وسعة حلمه: ترتكز حكمة الفرج فيه على تقديم الثناء المكرر بصفات العظمة والحلم والربوبية والملك المطلق لله، مما يورث القلب سكينة ويقينًا تامًا برحمة الله وفرجه القريب
 📚 التوثيق المعتمد
  المصدر: رواه البخاري (حديث رقم 6345)، ورواه مسلم في صحيحه (حديث رقم 2730)، من حديث عبد الله بن عباس رضي الله عنهما
- الكتاب المتداول: حصن المسلم، باب: دعاء الكرب</t>
+ الكتاب المتداول: حصن المسلم، باب دعاء الكرب</t>
   </si>
   <si>
     <t>🤲 فضل الذكر
@@ -2542,108 +2672,29 @@
  كمال الافتقار والتوكل: تفويض وتدبير سائر شؤون العبد (الدين والدنيا) لله وحده، والاستعاذة به من الخذلان أو أن يتركه الله لنفسه الضعيفة العاجزة ولو للحظة واحدة
 📚 التوثيق المعتمد
  المصدر: رواه الإمام أبو داود في سننه (4/324، برقم 5090)، والإمام أحمد في المسند (5/42)، وحسّنه الإمام الألباني في صحيح أبي داود
- الكتاب المتداول: حصن المسلم، باب: دعاء الكرب</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- كفاية الهموم وضيق الصدر: من قالها سبع مرات في الصباح أو في المساء كفاه الله عز وجل كل ما يشغل باله أو يُقلقه من أمور الدنيا والآخرة، وهي ركيزة أساسية في أدعية كشف الكرب والفرج
- تحقيق التوكل التام: تفويض الأمر لله والاعتمد عليه وحده لجلب المصالح ودفع المضار، مما يورث النفس طمأنينة وسكينة
-📚 التوثيق المعتمد
- المصدر: رواه ابن السني في عمل اليوم والليلة (رقم 71)، وأخرجه أبو داود (4/321) وكلا الروايتين مرفوعتان مباشرة إلى النبي ﷺ، وإسناد ابن السني صحيح
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- نيل الشفاعة النبوية: من حافظ على الصلاة على النبي ﷺ عشر مرات في الصباح وعشر مرات في المساء، نال وعداً صادقاً بأن تدركه شفاعة النبي ﷺ يوم القيامة
- كفاية الهم وغفران الذنب: امتثال أمر الله بالصلاة على رسوله، وهي ركيزة أساسية في أدعية مفاتيح الفرج، وسبب عظيم لتفريج الهموم والكروب، ونزول الرحمات والبركة على العبد في يومه وليلته
-📚 التوثيق المعتمد
- المصدر: رواه الطبراني بإسنادين أحدهما جيد، وانظر: مجمع الزوائد للهيثمي (10/120)، وحسنه الألباني في صحيح الترغيب والترهيب (1/273)
- الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- طلب الرزق والخير البري: سؤال الله سبحانه وتعالى أن يفتح للعبد أبواب فضله الواسع، تيمناً بخروجه من المسجد والسعي في طلب الرزق والمعاش الحلال في الدنيا
- العصمة والتحصين من الشيطان: نيل الوقاية والحفظ الإلهي من وساوس الشيطان ومكايده طوال فترة بقاء العبد خارج المسجد بعد انصرافه من العبادة
-📚 التوثيق المعتمد
- المصدر: خرّجه الإمام مسلم في صحيحه (حديث رقم 713 للفقرة الأولى)، والإمام ابن ماجه في سننه (حديث رقم 773 لزيادة العصمة من الشيطان)، وصححه الإمام الألباني في (صحيح سنن ابن ماجه 1/129) وصحيح الجامع (رقم 515)
- الكتاب المتداول: حصن المسلم، باب: دعاء الخروج من المسجد</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الحفظ من الشيطان طوال اليوم: الاستعاذة بالله العظيم وبأوصافه الجليلة عند دخول المسجد سبب في أن يقول الشيطان: "حُفِظَ مِنِّي سَائِرَ الْيَوْمِ"
- التعرض للرحمات الإلهية: سؤال الله سبحانه وتعالى أن يفتح للعبد أبواب رحمته الواسعة، تيمناً بدخول بيت من بيوته ومظانّ نزول رحماته ورضوانه
-📚 التوثيق المعتمد
- المصدر: خرّجه الإمام أبو داود في سننه (حديث رقم 466 للفقرة الأولى)، والإمام مسلم في صحيحه (حديث رقم 713 للفقرة الأخيرة)، والإمام ابن ماجه في سننه (حديث رقم 771 للبشير والصلاة) وصحح الإمام الألباني الأجزاء المجتمعة في (صحيح أبي داود 1/93) وصحيح الجامع
- الكتاب المتداول: حصن المسلم، باب: دعاء دخول المسجد</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- سؤال الهداية الشاملة: طلب إحاطة النور الإلهي بالعبد من سائر جهاته الست، وفي حواسه الظاهرة والباطنة ليعصمه الله من الغواية
- الاستضاءة يوم القيامة: التماس النور الحقيقي والهدى في الدنيا ليكون للمسلم نوراً عظيماً يستضيء به يوم القيامة في أهوال الظلم
-📚 التوثيق المعتمد
- المصدر: رواه الإمام مسلم في صحيحه (رقم 763) عن عبد الله بن عباس رضي الله عنهما، في قصة مبيته عند خالته ميمونة زوج النبي ﷺ، ووصفه لصلاة النبي ﷺ بالليل وخروجه للفجر
- الكتاب المتداول: حصن المسلم، باب: الدعاء للذهاب إلى المسجد</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الحماية والوقاية الدائمة: تحصين شامل للعبد وكفاية له من كل شر وسوء، وعصمة من الآفات بوساطة التعوذ بأعظم سور الحفظ دبر كل فريضة
- مغفرة الذنوب: التزام التعقيب بالقرآن والذكر خلف الصلوات المكتوبة يعد من أسباب نيل مغفرة الله ومحو الخطايا
-📚 التوثيق المعتمد
- المصدر: رواه مسلم في صحيحه (1/418) [رقم 523] من حديث عقبة بن عامر رضي الله عنه قال: "أمرني رسول الله ﷺ أن أقرأ بالمعوذات دبر كل صلاة"
- الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
-الوقاية من السموم واللدغات: مَن قالها ثلاث مرات حين يمسي لم تضره حَمَةٌ (لدغة عقرب أو حية أو حشرة سامة) في تلك الليلة
-التحصين من الشرور: الاستعاذة بكلمات الله الكاملة التي لا يدخلها نقص، للحماية من شرور الإنس، والجن، والسباع، وسائر الهوام والمخلوقات
-📚 التوثيق المعتمد
-المصدر: رواه الإمام أحمد (2/290)، والنسائي في عمل اليوم والليلة (رقم 590)، والترمذي (3/187)، وابن السني (رقم 68) وإسناد ابن ماجه (2/266) صحيح بحسب الألباني، وحسّن الشيخ ابن باز حديث الترمذي
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- شكر نعمة العافية والبعث: اعتراف بفضل الله المتمثل في سلامة البدن بعد النوم، وحمده على ردّ الروح التي هي في حكم المتوفاة عند النوم لتستأنف طاعته
- التوفيق لملازمة الذكر: الثناء على الله الذي تفضل بفتح باب مناجاته والإذن للعبد بذكره وحمده فور استيقاظه، وجعل بداية اليوم منفتحة على العبودية
-📚 التوثيق المعتمد
- المصدر: أخرجه الإمام الترمذي في سننه (المجلد 5، صفحة 473، رقم 3401)، وحسنه الإمام الألباني في صحيح سنن الترمذي (3/144)
- الكتاب المتداول: حصن المسلم، الباب الأول (أذكار الاستيقاظ من النوم)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فضل الذكر
-أداء شكر اليوم والليلة: مَن قاله في الصباح فقد أدّى شكر يومه كاملًا، ومَن قاله في المساء فقد أدّى شكر ليلته
-الاعتراف بالمنعم: إقرار العبد بأن كل النعم التي يتقلب فيها هو أو سائر الخلائق هي محض فضل وكرم من الله وحده
-📚 التوثيق المعتمد
-المصدر: أخرجه أبو داود (رقم 5073)، والنسائي في السنن الكبرى (رقم 9835/9832)، وابن حبان (رقم 861)، عن عبد الله بن غنام البياضي رضي الله عنه
-الكتاب المتداول: حصن المسلم، الباب 27 (أذكار الصباح والمساء)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- الاستعانة بالله لمدّ العبد بالقوة والتوفيق للثبات على ذكره الدائم، وشكره على نعمه الظاهرة والباطنة، والإتيان بالعبادات على الوجه الأكمل والأحسن الذي يرضيه
- وصية نبوية غالية: تذكير بمكانة هذا الدعاء العظيم
-يَا مُعَاذُ، وَاللَّهِ إِنِّي لَأُحِبُّكَ، وَاللَّهِ إِنِّي لَأُحِبُّكَ، فَقَالَ : أُوصِيكَ يَا مُعَاذُ لَا تَدَعَنَّ فِي دُبُرِ كُلِّ صَلَاةٍ تَقُولُ اللَّهُمَّ أَعِنِّي عَلَى ذِكْرِكَ، وَشُكْرِكَ، وَحُسْنِ عِبَادَتِكَ
-📚 التوثيق المعتمد
- المصدر: خرّجه الإمام أبو داود في سننه (حديث رقم 1522)، والإمام النسائي في السنن (الكبرى والصغرى، حديث رقم 1303)، وصححه الإمام الألباني في صحيح أبي داود (1/284)، وفي صحيح الجامع (رقم 7969)
- الكتاب المتداول: حصن المسلم، الباب 25 (الأذكار بعد السلام من الصلاة)</t>
-  </si>
-  <si>
-    <t>فضل الإحرام والتلبية تطهير من الذنوب: الطهارة والاغتسال عند الميقات يمثلان استعداداً ظاهرياً وباطنياً للوقوف بين يدي اللهتسبّح معه الكائنات: قال النبي ﷺ: ما مِن مُسلمٍ يُلبِّي إلَّا لبَّى مَن عن يمينِه أو عَن شمالِه مِن حجرٍ أو شجرٍ أو مَدرٍ، حتَّى تنقطعَ الأرضُ مِن ههُنا وَههُنا</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فضل الطواف حول الكعبة حطّ السيئات ورفع الدرجات: كل خطوة يخطوها المعتمر في الطواف لها أجر، قال ﷺ: مَنْ طَافَ بِهَذَا الْبَيْتِ أُسْبُوعاً (أي 7 أشواط) فَأَحْصَاهُ، كَانَ كَعِتْقِ رَقَبَةٍ، لا يَضَعُ قَدَماً وَلا يَرْفَعُ أُخْرَى إِلا حَطَّ اللَّهُ عَنْهُ بِهَا خَطِيئَةً، وَكَتَبَ لَهُ بِهَا حَسَنَةً
-مغفرة الذنوب: الطواف بالبيت يعود بالعبد كيوم ولدته أمه إذا تقبله الله</t>
-  </si>
-  <si>
-    <t>فضل ركعتي الطواف والشرب من زمزم
-مقام إبراهيم: الصلاة خلف المقام هي إحياء لسنة الخليل إبراهيم عليه السلام وامتثال لأمر الله: وَاتَّخِذُوا مِنْ مَقَامِ إِبْرَاهِيمَ مُصَلًّى
-الشرب من زمزم : طعام طُعم وشفاء سُقم: ماء زمزم مبارك، والدعاء عنده مستجاب، وهو نية لما شُرب له (شفاء، علم، رزق، أو مغفرة)</t>
-  </si>
-  <si>
-    <t>🤲 فضل الذكر
- أعظم سورة في القرآن: هي أم الكتاب والسبع المثاني التي لا تصح الصلاة إلا بها، وتشتمل على مجامع التوحيد والثناء والطلب
- رقية شرعية شافية: رقية مباركة تُقرأ بنية الشفاء من الأمراض البدنية، ولدغات الهوام، والهموم والكروب؛ لقول النبي ﷺ عنها: وما أدراك أنها رقية؟
-📚 التوثيق المعتمد
- المصدر: رواه البخاري (حديث رقم 2276 / 5007) ومسلم (حديث رقم 2201)، من حديث أبي سعيد الخدري رضي الله عنه
- الكتاب المتداول: حصن المسلم، باب: الرقية الشرعية من أذكار الكتاب والسنة</t>
+ الكتاب المتداول: حصن المسلم، باب دعاء الكرب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+تَقَبَّلَ اللَّهُ مِنَّا وَمِنْكُمْ صَالِحَ الأَعْمَالِ
+نَسْأَلُ اللَّهَ العَظِيمَ أَنْ يُثَبِّتَنَا عَلَى طَاعَتِهِ
+وَأَنْ يَجْعَلَنَا مِنَ الذَّاكِرِينَ اللَّهَ كَثِيرًا وَالذَّاكِرَاتِ
+بَارَكَ اللَّهُ فِي وَقْتِكُمْ وَجُهْدِكُمْ
+وَأَعَانَكُمْ عَلَى المُوَاظَبَةِ وَإِتْمَامِ الذِّكْرِ
+🤲 الحَمْدُ لِلَّهِ الَّذِي بِنِعْمَتِهِ تَتِمُّ الصَّالِحَاتُ</t>
+  </si>
+  <si>
+    <t>📖💡 اكْـتَـمَـلَ 
+🤲 الحَمْدُ لِلَّهِ الَّذِي بِنِعْمَتِهِ تَتِمُّ الصَّالِحَاتُ</t>
+  </si>
+  <si>
+    <t>📖💡 Completed
+🤲 All praise is due to Allah, by Whose grace good deeds are completed</t>
+  </si>
+  <si>
+    <t>May Allah accept from us and from you all righteous deeds
+We ask Allah the Magnificent to keep us firm upon His obedience, and to make us among the men and women who remember Allah frequently May Allah bless your time and your efforts, and assist you in perseverance and completing your remembrance (dhikr)
+🤲 All praise is due to Allah, by Whose grace good deeds are completed</t>
   </si>
 </sst>
 </file>
@@ -3021,7 +3072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
@@ -3072,16 +3123,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -3090,7 +3141,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="174" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3098,16 +3149,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -3124,16 +3175,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
@@ -3150,16 +3201,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
@@ -3168,7 +3219,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="174" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3176,22 +3227,45 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="145" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H7" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3254,16 +3328,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -3280,16 +3354,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -3306,16 +3380,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
@@ -3332,16 +3406,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
@@ -3358,16 +3432,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -3384,16 +3458,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
@@ -3410,16 +3484,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H8" s="3">
         <v>7</v>
@@ -3436,16 +3510,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H9" s="3">
         <v>8</v>
@@ -3462,16 +3536,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H10" s="3">
         <v>9</v>
@@ -3488,16 +3562,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H11" s="3">
         <v>10</v>
@@ -3514,16 +3588,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H12" s="3">
         <v>11</v>
@@ -3540,16 +3614,16 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H13" s="3">
         <v>12</v>
@@ -3566,16 +3640,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H14" s="3">
         <v>13</v>
@@ -3592,16 +3666,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H15" s="3">
         <v>14</v>
@@ -3618,16 +3692,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H16" s="3">
         <v>15</v>
@@ -3644,16 +3718,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H17" s="3">
         <v>16</v>
@@ -3670,16 +3744,16 @@
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H18" s="3">
         <v>17</v>
@@ -3696,16 +3770,16 @@
         <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H19" s="3">
         <v>18</v>
@@ -3722,16 +3796,16 @@
         <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H20" s="3">
         <v>19</v>
@@ -3748,16 +3822,16 @@
         <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H21" s="3">
         <v>20</v>
@@ -3774,16 +3848,16 @@
         <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H22" s="3">
         <v>21</v>
@@ -3800,16 +3874,16 @@
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H23" s="3">
         <v>22</v>
@@ -3829,13 +3903,13 @@
         <v>6</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H24" s="3">
         <v>23</v>
@@ -3852,16 +3926,16 @@
         <v>3</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H25" s="3">
         <v>24</v>
@@ -3878,16 +3952,16 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H26" s="3">
         <v>25</v>
@@ -3904,22 +3978,22 @@
         <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H27" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="174" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3927,16 +4001,16 @@
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H28" s="3">
         <v>27</v>
@@ -3950,25 +4024,43 @@
         <v>3</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H29" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="G30" s="4"/>
+    <row r="30" spans="1:9" ht="145" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H30" s="3">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4028,16 +4120,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -4054,16 +4146,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -4080,16 +4172,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
@@ -4106,16 +4198,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
@@ -4132,16 +4224,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -4158,16 +4250,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
@@ -4184,16 +4276,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H8" s="3">
         <v>7</v>
@@ -4210,16 +4302,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H9" s="3">
         <v>8</v>
@@ -4236,16 +4328,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H10" s="3">
         <v>9</v>
@@ -4262,16 +4354,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H11" s="3">
         <v>10</v>
@@ -4288,16 +4380,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H12" s="3">
         <v>11</v>
@@ -4314,16 +4406,16 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H13" s="3">
         <v>12</v>
@@ -4340,16 +4432,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H14" s="3">
         <v>13</v>
@@ -4366,16 +4458,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H15" s="3">
         <v>14</v>
@@ -4392,16 +4484,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H16" s="3">
         <v>15</v>
@@ -4418,16 +4510,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H17" s="3">
         <v>16</v>
@@ -4444,16 +4536,16 @@
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H18" s="3">
         <v>17</v>
@@ -4470,16 +4562,16 @@
         <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H19" s="3">
         <v>18</v>
@@ -4496,16 +4588,16 @@
         <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H20" s="3">
         <v>19</v>
@@ -4522,16 +4614,16 @@
         <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H21" s="3">
         <v>20</v>
@@ -4548,16 +4640,16 @@
         <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H22" s="3">
         <v>21</v>
@@ -4574,16 +4666,16 @@
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H23" s="3">
         <v>22</v>
@@ -4600,16 +4692,16 @@
         <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H24" s="3">
         <v>23</v>
@@ -4626,16 +4718,16 @@
         <v>3</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="H25" s="3">
         <v>24</v>
@@ -4652,16 +4744,16 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H26" s="3">
         <v>25</v>
@@ -4678,16 +4770,16 @@
         <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H27" s="3">
         <v>26</v>
@@ -4701,16 +4793,16 @@
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H28" s="3">
         <v>27</v>
@@ -4724,26 +4816,44 @@
         <v>3</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H29" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="3"/>
+    <row r="30" spans="1:9" ht="116" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H30" s="3">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4803,16 +4913,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -4829,16 +4939,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -4855,16 +4965,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
@@ -4881,16 +4991,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
@@ -4910,13 +5020,13 @@
         <v>83</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -4933,16 +5043,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
@@ -4959,16 +5069,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H8" s="3">
         <v>7</v>
@@ -4985,16 +5095,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H9" s="3">
         <v>8</v>
@@ -5011,16 +5121,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H10" s="3">
         <v>9</v>
@@ -5037,16 +5147,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H11" s="3">
         <v>10</v>
@@ -5063,16 +5173,16 @@
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H12" s="3">
         <v>11</v>
@@ -5089,16 +5199,16 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H13" s="3">
         <v>12</v>
@@ -5115,16 +5225,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H14" s="3">
         <v>13</v>
@@ -5141,16 +5251,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H15" s="3">
         <v>14</v>
@@ -5159,7 +5269,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="319" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -5167,22 +5277,22 @@
         <v>33</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="F16" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H16" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="319" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -5190,22 +5300,22 @@
         <v>33</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H17" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="319" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -5213,16 +5323,16 @@
         <v>34</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="F18" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H18" s="3">
         <v>17</v>
@@ -5236,24 +5346,44 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H19" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
+    <row r="20" spans="1:8" ht="145" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H20" s="3">
+        <v>19</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D21" s="4"/>
@@ -5331,7 +5461,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5378,16 +5508,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -5401,16 +5531,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -5424,16 +5554,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
@@ -5447,16 +5577,16 @@
         <v>33</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
@@ -5470,16 +5600,16 @@
         <v>33</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -5493,16 +5623,16 @@
         <v>34</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
@@ -5516,16 +5646,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H8" s="3">
         <v>7</v>
@@ -5539,16 +5669,16 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H9" s="3">
         <v>8</v>
@@ -5562,16 +5692,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H10" s="3">
         <v>9</v>
@@ -5585,16 +5715,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H11" s="3">
         <v>10</v>
@@ -5608,22 +5738,22 @@
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H12" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="203" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -5631,22 +5761,22 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H13" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -5654,16 +5784,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H14" s="3">
         <v>13</v>
@@ -5677,16 +5807,16 @@
         <v>7</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H15" s="3">
         <v>14</v>
@@ -5700,19 +5830,43 @@
         <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="H16" s="3">
         <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H17" s="3">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5722,7 +5876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
@@ -5746,7 +5900,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>9</v>
@@ -5769,16 +5923,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -5792,16 +5946,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -5815,19 +5969,42 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="145" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H5" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5837,7 +6014,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27959786-6F54-4A8A-B61D-623CD76AA67A}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
@@ -5875,7 +6052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5886,13 +6063,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -5906,19 +6083,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>104</v>
+        <v>375</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5926,19 +6103,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="203" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="232" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5946,30 +6123,30 @@
         <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>85</v>
+        <v>377</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="145" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="261" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -5983,19 +6160,19 @@
         <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -6003,16 +6180,39 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="G8" s="4" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="H8" s="3">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6069,16 +6269,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H2" s="3">
         <v>1</v>
@@ -6092,16 +6292,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
@@ -6115,16 +6315,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
@@ -6138,16 +6338,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
@@ -6161,16 +6361,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -6184,16 +6384,16 @@
         <v>100</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
@@ -6207,16 +6407,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="H8" s="3">
         <v>7</v>
@@ -6230,16 +6430,16 @@
         <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="H9" s="3">
         <v>8</v>
@@ -6253,16 +6453,16 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="H10" s="3">
         <v>9</v>
@@ -6276,27 +6476,44 @@
         <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="H11" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+    <row r="12" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H12" s="3">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
